--- a/examples/test_cases.xlsx
+++ b/examples/test_cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\src\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04121552-D82A-4CD5-89A4-8A2FEB76DFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA759606-B46F-452B-82F6-08D147ACAA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{16A29E05-5294-4C93-91C1-6C3B8F27AE65}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="101">
   <si>
     <t>select 1::tinyint</t>
   </si>
@@ -345,6 +345,33 @@
 select * from range(10);
 select count(*)
 from t;</t>
+  </si>
+  <si>
+    <t>HEADER=FALSE</t>
+  </si>
+  <si>
+    <t>select * from xlrange(1, header=false)</t>
+  </si>
+  <si>
+    <t>TEST DATA 1</t>
+  </si>
+  <si>
+    <t>TEST DATA 2</t>
+  </si>
+  <si>
+    <t>col1</t>
+  </si>
+  <si>
+    <t>STRICT=TRUE</t>
+  </si>
+  <si>
+    <t>select * from xlrange(1, strict=true)</t>
+  </si>
+  <si>
+    <t>STRICT=FALSE</t>
+  </si>
+  <si>
+    <t>select * from xlrange(1, strict=false)</t>
   </si>
 </sst>
 </file>
@@ -352,8 +379,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="167" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -419,14 +446,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1289,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751A3194-2367-4BAA-BC32-C926CD8293A5}">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.77734375" bestFit="1" customWidth="1"/>
@@ -1302,7 +1329,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
         <v>73</v>
@@ -2192,6 +2219,231 @@
       </c>
       <c r="G62" t="e">
         <v>#N/A</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B65" t="str" cm="1">
+        <f t="array" ref="B65:F69">_xll.DUCKDB.EXEC(B64,B1:F4)</f>
+        <v>column_0</v>
+      </c>
+      <c r="C65" t="str">
+        <v>column_1</v>
+      </c>
+      <c r="D65" t="str">
+        <v>column_2</v>
+      </c>
+      <c r="E65" t="str">
+        <v>column_3</v>
+      </c>
+      <c r="F65" t="str">
+        <v>column_4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B66" t="str">
+        <v>NUMBER_1</v>
+      </c>
+      <c r="C66" t="str">
+        <v>NUMBER_2</v>
+      </c>
+      <c r="D66" t="str">
+        <v>STRING_COL</v>
+      </c>
+      <c r="E66" t="str">
+        <v>EMPTY_COL</v>
+      </c>
+      <c r="F66" t="str">
+        <v>ERROR_COL</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B67" t="str">
+        <v>1</v>
+      </c>
+      <c r="C67" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="D67" t="str">
+        <v>abc</v>
+      </c>
+      <c r="E67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F67" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B68" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="C68" t="str">
+        <v>1</v>
+      </c>
+      <c r="D68" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F68" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B69" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="C69" t="str">
+        <v>abc</v>
+      </c>
+      <c r="D69" t="str">
+        <v>1</v>
+      </c>
+      <c r="E69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F69" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>95</v>
+      </c>
+      <c r="B71" t="s">
+        <v>96</v>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>1.2</v>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B73">
+        <v>1.2</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B74">
+        <v>1.3</v>
+      </c>
+      <c r="C74" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74" s="9">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>97</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B77" t="str" cm="1">
+        <f t="array" ref="B77">_xll.DUCKDB.EXEC(B76,B71:E74)</f>
+        <v>Binder Error: Error binding xlrange: Column #2: Invalid column name. Column names must be non-empty and valid DuckDB identifiers.
+LINE 1: select * from xlrange(1, strict=true)
+                      ^</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>99</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B80" t="str" cm="1">
+        <f t="array" ref="B80:E83">_xll.DUCKDB.EXEC(B79,B71:E74)</f>
+        <v>col1</v>
+      </c>
+      <c r="C80" t="str">
+        <v>unnamed_0</v>
+      </c>
+      <c r="D80" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="E80" t="str">
+        <v>unnamed_1</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B82">
+        <v>1.2</v>
+      </c>
+      <c r="C82" t="str">
+        <v>1</v>
+      </c>
+      <c r="D82" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B83">
+        <v>1.3</v>
+      </c>
+      <c r="C83" t="str">
+        <v>abc</v>
+      </c>
+      <c r="D83" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>46387</v>
       </c>
     </row>
   </sheetData>

--- a/examples/test_cases.xlsx
+++ b/examples/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\src\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA759606-B46F-452B-82F6-08D147ACAA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC94A30E-952F-4671-87DC-3F26E007904F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{16A29E05-5294-4C93-91C1-6C3B8F27AE65}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="TYPES" sheetId="1" r:id="rId1"/>
     <sheet name="XLRANGE" sheetId="2" r:id="rId2"/>
     <sheet name="SCALAR FUNCS" sheetId="3" r:id="rId3"/>
-    <sheet name="EXECX" sheetId="4" r:id="rId4"/>
+    <sheet name="EXECX-A-AX" sheetId="4" r:id="rId4"/>
     <sheet name="BIND" sheetId="5" r:id="rId5"/>
     <sheet name="INFO" sheetId="6" r:id="rId6"/>
     <sheet name="ASYNC" sheetId="7" r:id="rId7"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="109">
   <si>
     <t>select 1::tinyint</t>
   </si>
@@ -293,9 +293,6 @@
     <t>NUMBER_2</t>
   </si>
   <si>
-    <t>xldate</t>
-  </si>
-  <si>
     <t>date_col</t>
   </si>
   <si>
@@ -305,9 +302,6 @@
     <t>datetime_col</t>
   </si>
   <si>
-    <t>select xldate(date_col)::varchar, xltime(time_col)::varchar, xldatetime(datetime_col)::varchar from xlrange(1)</t>
-  </si>
-  <si>
     <t>create macro test_macro(x) as x;</t>
   </si>
   <si>
@@ -327,9 +321,6 @@
   </si>
   <si>
     <t>select 1;</t>
-  </si>
-  <si>
-    <t>DUCKDB.EXEC</t>
   </si>
   <si>
     <t>DUCKDB.EXEC.ASYNC</t>
@@ -372,6 +363,39 @@
   </si>
   <si>
     <t>select * from xlrange(1, strict=false)</t>
+  </si>
+  <si>
+    <t>TEST DATA 3</t>
+  </si>
+  <si>
+    <t>dup</t>
+  </si>
+  <si>
+    <t>DUCKDB.EXECA</t>
+  </si>
+  <si>
+    <t>DUCKDB.EXECA.ASYNC</t>
+  </si>
+  <si>
+    <t>DUCKDB.EXECAX.ASYNC</t>
+  </si>
+  <si>
+    <t>DUCKDB.EXECAX</t>
+  </si>
+  <si>
+    <t>xldate, xltime, xldatetime</t>
+  </si>
+  <si>
+    <t>with double</t>
+  </si>
+  <si>
+    <t>select xldate(date_col::double)::varchar, xltime(time_col::double)::varchar, xldatetime(datetime_col::double)::varchar from xlrange(1)</t>
+  </si>
+  <si>
+    <t>select xldate(date_col::integer)::varchar, xltime(time_col::integer)::varchar, xldatetime(datetime_col::integer)::varchar from xlrange(1)</t>
+  </si>
+  <si>
+    <t>with integer</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1323,7 @@
         <v>54</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
@@ -1316,7 +1340,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751A3194-2367-4BAA-BC32-C926CD8293A5}">
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.77734375" bestFit="1" customWidth="1"/>
@@ -1329,7 +1353,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
         <v>73</v>
@@ -2223,10 +2247,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2317,10 +2341,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B71" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D71" t="b">
         <v>1</v>
@@ -2367,10 +2391,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2383,10 +2407,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -2404,7 +2428,7 @@
         <v>unnamed_1</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>1</v>
       </c>
@@ -2418,7 +2442,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>1.2</v>
       </c>
@@ -2432,7 +2456,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>1.3</v>
       </c>
@@ -2444,6 +2468,99 @@
       </c>
       <c r="E83">
         <v>46387</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>98</v>
+      </c>
+      <c r="B85" t="s">
+        <v>99</v>
+      </c>
+      <c r="C85" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <v>1.2</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B88">
+        <v>1.3</v>
+      </c>
+      <c r="C88" t="s">
+        <v>57</v>
+      </c>
+      <c r="E88" s="9"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B91" t="str" cm="1">
+        <f t="array" ref="B91">_xll.DUCKDB.EXEC(B90,B85:C88)</f>
+        <v>Binder Error: table "xlrange" has duplicate column name "dup"
+LINE 1: select * from xlrange(1, strict=true)
+                      ^</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B94" t="str" cm="1">
+        <f t="array" ref="B94:C97">_xll.DUCKDB.EXEC(B93,B85:C88)</f>
+        <v>dup</v>
+      </c>
+      <c r="C94" t="str">
+        <v>dup_1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95" t="str">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B96">
+        <v>1.2</v>
+      </c>
+      <c r="C96" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B97">
+        <v>1.3</v>
+      </c>
+      <c r="C97" t="str">
+        <v>abc</v>
       </c>
     </row>
   </sheetData>
@@ -2454,10 +2571,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A836AEC-DD0A-4797-B454-6E20C81CB53A}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" customWidth="1"/>
     <col min="2" max="2" width="25.109375" customWidth="1"/>
     <col min="3" max="3" width="22.44140625" customWidth="1"/>
     <col min="4" max="4" width="24.109375" customWidth="1"/>
@@ -2469,13 +2586,13 @@
         <v>55</v>
       </c>
       <c r="B1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" t="s">
         <v>76</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>77</v>
-      </c>
-      <c r="D1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -2491,22 +2608,25 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>105</v>
+      </c>
       <c r="B5" t="str" cm="1">
         <f t="array" ref="B5:D6">_xll.DUCKDB.EXEC(B4,B1:D2)</f>
-        <v>CAST(xldate(date_col) AS VARCHAR)</v>
+        <v>CAST(xldate(CAST(date_col AS "DOUBLE")) AS VARCHAR)</v>
       </c>
       <c r="C5" t="str">
-        <v>CAST(xltime(time_col) AS VARCHAR)</v>
+        <v>CAST(xltime(CAST(time_col AS "DOUBLE")) AS VARCHAR)</v>
       </c>
       <c r="D5" t="str">
-        <v>CAST(xldatetime(datetime_col) AS VARCHAR)</v>
+        <v>CAST(xldatetime(CAST(datetime_col AS "DOUBLE")) AS VARCHAR)</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2522,6 +2642,40 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" t="str" cm="1">
+        <f t="array" ref="B9:D10">_xll.DUCKDB.EXEC(B8,A1:D2)</f>
+        <v>CAST(xldate(CAST(date_col AS INTEGER)) AS VARCHAR)</v>
+      </c>
+      <c r="C9" t="str">
+        <v>CAST(xltime(CAST(time_col AS INTEGER)) AS VARCHAR)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>CAST(xldatetime(CAST(datetime_col AS INTEGER)) AS VARCHAR)</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="9" t="str">
+        <v>2026-12-31</v>
+      </c>
+      <c r="C10" t="str">
+        <v>00:00:00</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-12-31 00:00:00</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2530,30 +2684,77 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66184BE2-F564-4E42-8CE8-BFC8C65E358F}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="str" cm="1">
-        <f t="array" ref="A3:A4">_xll.DUCKDB.EXECX(A1,A2)</f>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" t="str" cm="1">
+        <f t="array" ref="B3:B4">_xll.DUCKDB.EXECX(B1,B2)</f>
         <v>test_macro(1)</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="str" cm="1">
+        <f t="array" ref="B7:B8">_xll.DUCKDB.EXECA(,B6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" t="str" cm="1">
+        <f t="array" ref="B12:B13">_xll.DUCKDB.EXECAX(,B10,B11)</f>
+        <v>test_macro(1)</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13">
         <v>1</v>
       </c>
     </row>
@@ -2581,7 +2782,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -2605,7 +2806,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -2629,7 +2830,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -2653,7 +2854,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -2669,12 +2870,12 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -2690,7 +2891,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B25" t="e">
         <f>1/0</f>
@@ -2699,7 +2900,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -2738,20 +2939,20 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:B3">_xll.DUCKDB.EXEC(B1)</f>
+        <f t="array" ref="B2:B3">_xll.DUCKDB.EXEC.ASYNC(B1)</f>
         <v>1</v>
       </c>
     </row>
@@ -2762,10 +2963,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5:B6">_xll.DUCKDB.EXEC.ASYNC(B1)</f>
+        <f t="array" ref="B5:B6">_xll.DUCKDB.EXECX.ASYNC(,B1)</f>
         <v>1</v>
       </c>
     </row>
@@ -2776,10 +2977,10 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8:B9">_xll.DUCKDB.EXECX(,B1)</f>
+        <f t="array" ref="B8:B9">_xll.DUCKDB.EXECA.ASYNC(,B1)</f>
         <v>1</v>
       </c>
     </row>
@@ -2790,10 +2991,10 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B11" t="str" cm="1">
-        <f t="array" ref="B11:B12">_xll.DUCKDB.EXECX.ASYNC(,B1)</f>
+        <f t="array" ref="B11:B12">_xll.DUCKDB.EXECAX.ASYNC(,,B1)</f>
         <v>1</v>
       </c>
     </row>
@@ -2817,7 +3018,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="72" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">

--- a/examples/test_cases.xlsx
+++ b/examples/test_cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\src\examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\DuckDBExcelAddin\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC94A30E-952F-4671-87DC-3F26E007904F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D22DBA-1C5D-435F-A5C9-8C8B74C7DC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{16A29E05-5294-4C93-91C1-6C3B8F27AE65}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{16A29E05-5294-4C93-91C1-6C3B8F27AE65}"/>
   </bookViews>
   <sheets>
     <sheet name="TYPES" sheetId="1" r:id="rId1"/>
@@ -35,9 +35,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -66,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="113">
   <si>
     <t>select 1::tinyint</t>
   </si>
@@ -396,6 +393,18 @@
   </si>
   <si>
     <t>with integer</t>
+  </si>
+  <si>
+    <t>IGNORE_ERRORS=FALSE</t>
+  </si>
+  <si>
+    <t>select * from xlrange(1, strict=false, sample=2)</t>
+  </si>
+  <si>
+    <t>IGNORE_ERRORS=TRUE</t>
+  </si>
+  <si>
+    <t>select * from xlrange(1, strict=false, sample=2, ignore_errors=true)</t>
   </si>
 </sst>
 </file>
@@ -462,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -475,7 +484,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -796,16 +804,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5358680-0ED5-4EFA-AB03-B446D1F523DD}">
   <dimension ref="A1:B110"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="72.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.77734375" customWidth="1"/>
-    <col min="7" max="7" width="38.109375" customWidth="1"/>
+    <col min="2" max="2" width="72.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="38.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -813,18 +821,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="str" cm="1">
         <f t="array" ref="B2:B3">_xll.DUCKDB.EXEC(B1)</f>
         <v>CAST(1 AS "TINYINT")</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -832,18 +840,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="str" cm="1">
         <f t="array" ref="B6:B7">_xll.DUCKDB.EXEC(B5)</f>
         <v>CAST(1 AS "UTINYINT")</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -851,18 +859,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="str" cm="1">
         <f t="array" ref="B10:B11">_xll.DUCKDB.EXEC(B9)</f>
         <v>CAST(1 AS SMALLINT)</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -870,18 +878,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="str" cm="1">
         <f t="array" ref="B14:B15">_xll.DUCKDB.EXEC(B13)</f>
         <v>CAST(1 AS "USMALLINT")</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -889,18 +897,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="str" cm="1">
         <f t="array" ref="B18:B19">_xll.DUCKDB.EXEC(B17)</f>
         <v>CAST(1 AS INTEGER)</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -908,18 +916,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="str" cm="1">
         <f t="array" ref="B22:B23">_xll.DUCKDB.EXEC(B21)</f>
         <v>CAST(1 AS "UINTEGER")</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B23" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -927,18 +935,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="str" cm="1">
         <f t="array" ref="B26:B27">_xll.DUCKDB.EXEC(B25)</f>
         <v>CAST(1 AS BIGINT)</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -946,18 +954,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="str" cm="1">
         <f t="array" ref="B30:B31">_xll.DUCKDB.EXEC(B29)</f>
         <v>CAST(1 AS "UBIGINT")</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B31" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -965,18 +973,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="str" cm="1">
         <f t="array" ref="B34:B35">_xll.DUCKDB.EXEC(B33)</f>
         <v>CAST(1 AS "HUGEINT")</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B35" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -984,18 +992,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="str" cm="1">
         <f t="array" ref="B38:B39">_xll.DUCKDB.EXEC(B37)</f>
         <v>CAST(1 AS "UHUGEINT")</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -1003,18 +1011,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="str" cm="1">
         <f t="array" ref="B42:B43">_xll.DUCKDB.EXEC(B41)</f>
         <v>CAST('t' AS BOOLEAN)</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -1022,18 +1030,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="str" cm="1">
         <f t="array" ref="B46:B47">_xll.DUCKDB.EXEC(B45)</f>
         <v>'abc'</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="str">
         <v>abc</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>16</v>
       </c>
@@ -1041,18 +1049,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="str" cm="1">
         <f t="array" ref="B50:B51">_xll.DUCKDB.EXEC(B49)</f>
         <v>CAST(1.2 AS FLOAT)</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" s="2">
         <v>1.2000000476837158</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -1060,18 +1068,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="str" cm="1">
         <f t="array" ref="B54:B55">_xll.DUCKDB.EXEC(B53)</f>
         <v>CAST(1.2 AS "DOUBLE")</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B55" s="2">
         <v>1.2</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>28</v>
       </c>
@@ -1079,18 +1087,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="str" cm="1">
         <f t="array" ref="B58:B59">_xll.DUCKDB.EXEC(B57)</f>
         <v>CAST(1.2 AS DECIMAL(4, 2))</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B59" s="2">
         <v>1.2</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>30</v>
       </c>
@@ -1098,18 +1106,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="str" cm="1">
         <f t="array" ref="B62:B63">_xll.DUCKDB.EXEC(B61)</f>
         <v>CAST(1.2 AS DECIMAL(9, 2))</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B63" s="2">
         <v>1.2</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>32</v>
       </c>
@@ -1117,18 +1125,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="str" cm="1">
         <f t="array" ref="B66:B67">_xll.DUCKDB.EXEC(B65)</f>
         <v>CAST(1.2 AS DECIMAL(18, 2))</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B67" s="2">
         <v>1.2</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>34</v>
       </c>
@@ -1136,18 +1144,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="str" cm="1">
         <f t="array" ref="B70:B71">_xll.DUCKDB.EXEC(B69)</f>
         <v>CAST(1.2 AS DECIMAL(38, 2))</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B71" s="2">
         <v>1.2</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>36</v>
       </c>
@@ -1155,18 +1163,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B74" s="2" t="str" cm="1">
         <f t="array" ref="B74:B75">_xll.DUCKDB.EXEC(B73)</f>
         <v>CAST('2026-12-31' AS "DATE")</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B75" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>38</v>
       </c>
@@ -1174,18 +1182,18 @@
         <v>39</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B78" s="2" t="str" cm="1">
         <f t="array" ref="B78:B79">_xll.DUCKDB.EXEC(B77)</f>
         <v>CAST('09:30:45' AS TIME)</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B79" s="5">
         <v>0.39635416666666667</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>40</v>
       </c>
@@ -1193,18 +1201,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B82" s="2" t="str" cm="1">
         <f t="array" ref="B82:B83">_xll.DUCKDB.EXEC(B81)</f>
         <v>CAST('09:30:45+07:00' AS "TIME WITH TIME ZONE")</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B83" s="5">
         <v>0.39635416666666667</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>42</v>
       </c>
@@ -1212,18 +1220,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B86" s="2" t="str" cm="1">
         <f t="array" ref="B86:B87">_xll.DUCKDB.EXEC(B85)</f>
         <v>CAST('2026-12-31 09:30:45' AS TIMESTAMP)</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B87" s="6">
         <v>46387.396354166667</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>44</v>
       </c>
@@ -1231,18 +1239,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B90" s="2" t="str" cm="1">
         <f t="array" ref="B90:B91">_xll.DUCKDB.EXEC(B89)</f>
         <v>CAST('2026-12-31 09:30:45+07:00' AS "TIMESTAMP WITH TIME ZONE")</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B91" s="6">
         <v>46387.104687500003</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>46</v>
       </c>
@@ -1250,18 +1258,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B94" s="2" t="str" cm="1">
         <f t="array" ref="B94:B95">_xll.DUCKDB.EXEC(B93)</f>
         <v>CAST('2026-12-31 09:30:45' AS "TIMESTAMP_S")</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B95" s="6">
         <v>46387.396354166667</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>48</v>
       </c>
@@ -1269,18 +1277,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B98" s="2" t="str" cm="1">
         <f t="array" ref="B98:B99">_xll.DUCKDB.EXEC(B97)</f>
         <v>CAST('2026-12-31 09:30:45' AS "TIMESTAMP_MS")</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B99" s="6">
         <v>46387.396354166667</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>50</v>
       </c>
@@ -1288,18 +1296,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B102" s="2" t="str" cm="1">
         <f t="array" ref="B102:B103">_xll.DUCKDB.EXEC(B101)</f>
         <v>CAST('2026-12-31 09:30:45' AS "TIMESTAMP_NS")</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B103" s="6">
         <v>46387.396354166667</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>52</v>
       </c>
@@ -1307,18 +1315,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B106" s="2" t="str" cm="1">
         <f t="array" ref="B106:B107">_xll.DUCKDB.EXEC(B105)</f>
         <v>NULL</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B107" s="2" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>54</v>
       </c>
@@ -1326,10 +1334,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B110" s="2" t="str" cm="1">
         <f t="array" ref="B110">_xll.DUCKDB.EXEC(B109)</f>
-        <v>Error fetching data: Column my_column: Unsupported DuckDB type. Convert the value to VARCHAR before returning it to Excel</v>
+        <v>Error fetching data: Column my_column: Unsupported DuckDB type. Convert the value to VARCHAR before returning it to Excel.</v>
       </c>
     </row>
   </sheetData>
@@ -1340,18 +1348,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751A3194-2367-4BAA-BC32-C926CD8293A5}">
-  <dimension ref="A1:G97"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G106"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>91</v>
       </c>
@@ -1371,7 +1379,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>1</v>
       </c>
@@ -1386,7 +1394,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1.2</v>
       </c>
@@ -1397,7 +1405,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1.3</v>
       </c>
@@ -1408,7 +1416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -1416,7 +1424,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" t="str" cm="1">
         <f t="array" ref="B7:F8">_xll.DUCKDB.EXEC(B6,$B$1:$F$2)</f>
         <v>NUMBER_1</v>
@@ -1434,7 +1442,7 @@
         <v>ERROR_COL</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1</v>
       </c>
@@ -1451,12 +1459,12 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" t="str" cm="1">
         <f t="array" ref="B11:G16">_xll.DUCKDB.EXEC(B10,$B$1:$F$2)</f>
         <v>column_name</v>
@@ -1477,7 +1485,7 @@
         <v>extra</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" t="str">
         <v>NUMBER_1</v>
       </c>
@@ -1497,7 +1505,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" t="str">
         <v>NUMBER_2</v>
       </c>
@@ -1517,7 +1525,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" t="str">
         <v>STRING_COL</v>
       </c>
@@ -1537,7 +1545,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" t="str">
         <v>EMPTY_COL</v>
       </c>
@@ -1557,7 +1565,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
         <v>ERROR_COL</v>
       </c>
@@ -1577,7 +1585,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -1585,7 +1593,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" t="str" cm="1">
         <f t="array" ref="B19:F21">_xll.DUCKDB.EXEC(B18,$B$1:$F$3)</f>
         <v>NUMBER_1</v>
@@ -1603,7 +1611,7 @@
         <v>ERROR_COL</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>1</v>
       </c>
@@ -1620,7 +1628,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>1.2</v>
       </c>
@@ -1637,12 +1645,12 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" t="str" cm="1">
         <f t="array" ref="B24:G29">_xll.DUCKDB.EXEC(B23,$B$1:$F$3)</f>
         <v>column_name</v>
@@ -1663,7 +1671,7 @@
         <v>extra</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>65</v>
       </c>
@@ -1686,7 +1694,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B26" t="str">
         <v>NUMBER_2</v>
       </c>
@@ -1706,7 +1714,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B27" t="str">
         <v>STRING_COL</v>
       </c>
@@ -1726,7 +1734,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B28" t="str">
         <v>EMPTY_COL</v>
       </c>
@@ -1746,7 +1754,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B29" t="str">
         <v>ERROR_COL</v>
       </c>
@@ -1766,7 +1774,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>67</v>
       </c>
@@ -1774,7 +1782,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B32" t="str" cm="1">
         <f t="array" ref="B32:F35">_xll.DUCKDB.EXEC(B31,$B$1:$F$4)</f>
         <v>NUMBER_1</v>
@@ -1792,7 +1800,7 @@
         <v>ERROR_COL</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>1</v>
       </c>
@@ -1809,7 +1817,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>1.2</v>
       </c>
@@ -1826,7 +1834,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>1.3</v>
       </c>
@@ -1843,12 +1851,12 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B37" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B38" t="str" cm="1">
         <f t="array" ref="B38:G43">_xll.DUCKDB.EXEC(B37,$B$1:$F$4)</f>
         <v>column_name</v>
@@ -1869,7 +1877,7 @@
         <v>extra</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
       <c r="B39" t="str">
         <v>NUMBER_1</v>
@@ -1890,7 +1898,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>66</v>
       </c>
@@ -1913,7 +1921,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B41" t="str">
         <v>STRING_COL</v>
       </c>
@@ -1933,7 +1941,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B42" t="str">
         <v>EMPTY_COL</v>
       </c>
@@ -1953,7 +1961,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B43" t="str">
         <v>ERROR_COL</v>
       </c>
@@ -1973,7 +1981,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>68</v>
       </c>
@@ -1981,13 +1989,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B46" t="str" cm="1">
         <f t="array" ref="B46">_xll.DUCKDB.EXEC(B45,$B$1:$F$4)</f>
-        <v>Invalid Input Error: Error scanning xlrange: Column NUMBER_1, row 3: Failed to convert to INTEGER</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>Invalid Input Error: Error scanning xlrange: Column NUMBER_1, row 3: Failed to convert value to INTEGER.</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>69</v>
       </c>
@@ -1995,7 +2003,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B49" t="str" cm="1">
         <f t="array" ref="B49:G54">_xll.DUCKDB.EXEC(B48,$B$1:$F$4)</f>
         <v>column_name</v>
@@ -2016,7 +2024,7 @@
         <v>extra</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B50" t="str">
         <v>NUMBER_1</v>
       </c>
@@ -2036,7 +2044,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B51" t="str">
         <v>NUMBER_2</v>
       </c>
@@ -2056,7 +2064,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B52" t="str">
         <v>STRING_COL</v>
       </c>
@@ -2076,7 +2084,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B53" t="str">
         <v>EMPTY_COL</v>
       </c>
@@ -2096,7 +2104,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B54" t="str">
         <v>ERROR_COL</v>
       </c>
@@ -2116,7 +2124,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>71</v>
       </c>
@@ -2124,7 +2132,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B57" t="str" cm="1">
         <f t="array" ref="B57:G62">_xll.DUCKDB.EXEC(B56,$B$1:$F$4)</f>
         <v>column_name</v>
@@ -2145,7 +2153,7 @@
         <v>extra</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B58" t="str">
         <v>NUMBER_1</v>
       </c>
@@ -2165,7 +2173,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B59" t="str">
         <v>NUMBER_2</v>
       </c>
@@ -2185,7 +2193,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B60" t="str">
         <v>STRING_COL</v>
       </c>
@@ -2205,7 +2213,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B61" t="str">
         <v>EMPTY_COL</v>
       </c>
@@ -2225,7 +2233,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B62" t="str">
         <v>ERROR_COL</v>
       </c>
@@ -2245,7 +2253,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>89</v>
       </c>
@@ -2253,7 +2261,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B65" t="str" cm="1">
         <f t="array" ref="B65:F69">_xll.DUCKDB.EXEC(B64,B1:F4)</f>
         <v>column_0</v>
@@ -2271,7 +2279,7 @@
         <v>column_4</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B66" t="str">
         <v>NUMBER_1</v>
       </c>
@@ -2288,7 +2296,7 @@
         <v>ERROR_COL</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B67" t="str">
         <v>1</v>
       </c>
@@ -2305,7 +2313,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B68" t="str">
         <v>1.2</v>
       </c>
@@ -2322,7 +2330,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B69" t="str">
         <v>1.3</v>
       </c>
@@ -2339,7 +2347,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>92</v>
       </c>
@@ -2350,7 +2358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B72">
         <v>1</v>
       </c>
@@ -2364,7 +2372,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>1.2</v>
       </c>
@@ -2375,7 +2383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>1.3</v>
       </c>
@@ -2389,7 +2397,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>94</v>
       </c>
@@ -2397,7 +2405,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B77" t="str" cm="1">
         <f t="array" ref="B77">_xll.DUCKDB.EXEC(B76,B71:E74)</f>
         <v>Binder Error: Error binding xlrange: Column #2: Invalid column name. Column names must be non-empty and valid DuckDB identifiers.
@@ -2405,7 +2413,7 @@
                       ^</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>96</v>
       </c>
@@ -2413,7 +2421,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B80" t="str" cm="1">
         <f t="array" ref="B80:E83">_xll.DUCKDB.EXEC(B79,B71:E74)</f>
         <v>col1</v>
@@ -2428,7 +2436,7 @@
         <v>unnamed_1</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B81">
         <v>1</v>
       </c>
@@ -2442,7 +2450,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B82">
         <v>1.2</v>
       </c>
@@ -2456,7 +2464,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B83">
         <v>1.3</v>
       </c>
@@ -2470,7 +2478,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>98</v>
       </c>
@@ -2481,7 +2489,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B86">
         <v>1</v>
       </c>
@@ -2489,7 +2497,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B87">
         <v>1.2</v>
       </c>
@@ -2497,7 +2505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B88">
         <v>1.3</v>
       </c>
@@ -2506,7 +2514,7 @@
       </c>
       <c r="E88" s="9"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -2514,7 +2522,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B91" t="str" cm="1">
         <f t="array" ref="B91">_xll.DUCKDB.EXEC(B90,B85:C88)</f>
         <v>Binder Error: table "xlrange" has duplicate column name "dup"
@@ -2522,7 +2530,7 @@
                       ^</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -2530,7 +2538,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B94" t="str" cm="1">
         <f t="array" ref="B94:C97">_xll.DUCKDB.EXEC(B93,B85:C88)</f>
         <v>dup</v>
@@ -2539,7 +2547,7 @@
         <v>dup_1</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B95">
         <v>1</v>
       </c>
@@ -2547,7 +2555,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B96">
         <v>1.2</v>
       </c>
@@ -2555,12 +2563,67 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B97">
         <v>1.3</v>
       </c>
       <c r="C97" t="str">
         <v>abc</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>109</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B100" t="str" cm="1">
+        <f t="array" ref="B100">_xll.DUCKDB.EXEC(B99,B85:C88)</f>
+        <v>Invalid Input Error: Error scanning xlrange: Column dup_1, row 4: Failed to convert value to DOUBLE.</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>111</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B103" t="str" cm="1">
+        <f t="array" ref="B103:C106">_xll.DUCKDB.EXEC(B102,B85:C88)</f>
+        <v>dup</v>
+      </c>
+      <c r="C103" t="str">
+        <v>dup_1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B105">
+        <v>1.2</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B106">
+        <v>1.3</v>
+      </c>
+      <c r="C106" t="e">
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -2571,17 +2634,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A836AEC-DD0A-4797-B454-6E20C81CB53A}">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -2595,18 +2658,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B2" s="9">
         <v>46387</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>0.39635416666666667</v>
       </c>
       <c r="D2" s="6">
         <v>46387.396354166667</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -2614,7 +2677,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>105</v>
       </c>
@@ -2629,21 +2692,18 @@
         <v>CAST(xldatetime(CAST(datetime_col AS "DOUBLE")) AS VARCHAR)</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="str">
         <v>2026-12-31</v>
       </c>
-      <c r="C6" s="12" t="str">
+      <c r="C6" s="11" t="str">
         <v>09:30:45</v>
       </c>
       <c r="D6" s="6" t="str">
         <v>2026-12-31 09:30:45</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G7" s="10"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>104</v>
       </c>
@@ -2651,7 +2711,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>108</v>
       </c>
@@ -2666,7 +2726,7 @@
         <v>CAST(xldatetime(CAST(datetime_col AS INTEGER)) AS VARCHAR)</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="str">
         <v>2026-12-31</v>
       </c>
@@ -2685,13 +2745,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66184BE2-F564-4E42-8CE8-BFC8C65E358F}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>86</v>
       </c>
@@ -2699,23 +2759,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3:B4">_xll.DUCKDB.EXECX(B1,B2)</f>
         <v>test_macro(1)</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>100</v>
       </c>
@@ -2723,18 +2783,18 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="str" cm="1">
         <f t="array" ref="B7:B8">_xll.DUCKDB.EXECA(,B6)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>103</v>
       </c>
@@ -2742,18 +2802,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="str" cm="1">
         <f t="array" ref="B12:B13">_xll.DUCKDB.EXECAX(,B10,B11)</f>
         <v>test_macro(1)</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1</v>
       </c>
@@ -2766,13 +2826,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D42E5724-67A3-4259-906B-37F92D367239}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>73</v>
       </c>
@@ -2780,23 +2840,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3:B4">_xll.DUCKDB.EXEC(B2,B1)</f>
         <v>$1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -2804,23 +2864,23 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8:B9">_xll.DUCKDB.EXEC(B7,B6)</f>
         <v>$1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1.2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -2828,23 +2888,23 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="str" cm="1">
         <f t="array" ref="B12:B13">_xll.DUCKDB.EXEC(B11,B10)</f>
         <v>$1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="str">
         <v>abc</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2852,44 +2912,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" t="str" cm="1">
         <f t="array" ref="B17:B18">_xll.DUCKDB.EXEC(B16,B15)</f>
         <v>$1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" t="str" cm="1">
         <f t="array" ref="B22:B23">_xll.DUCKDB.EXEC(B21,B20)</f>
         <v>$1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B23" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -2898,15 +2958,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" t="str" cm="1">
         <f t="array" ref="B27">_xll.DUCKDB.EXEC(B26,B25)</f>
-        <v>Error: Parameter binding failed</v>
+        <v>Error: Parameter binding failed.</v>
       </c>
     </row>
   </sheetData>
@@ -2917,15 +2977,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C8C1CB2-5A89-4EE9-B7B8-26D912A856F1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" ref="A1">_xll.DUCKDB.INFO()</f>
-        <v>Add-in version: v0.5.0
+        <v>Add-in version: v1.5.0
 DuckDB version: v1.5.5</v>
       </c>
     </row>
@@ -2937,17 +2997,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE0166A-6705-4BE6-BC5D-3DDB4234D0EA}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -2956,12 +3016,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -2970,12 +3030,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>101</v>
       </c>
@@ -2984,12 +3044,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>102</v>
       </c>
@@ -2998,7 +3058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1</v>
       </c>
@@ -3011,23 +3071,23 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65879F08-AA5E-452D-9515-58424370F18B}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.33203125" customWidth="1"/>
+    <col min="1" max="1" width="31.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2:A3">_xll.DUCKDB.EXEC(A1)</f>
         <v>count_star()</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>10</v>
       </c>

--- a/examples/test_cases.xlsx
+++ b/examples/test_cases.xlsx
@@ -5,22 +5,24 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\DuckDBExcelAddin\examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Users\daily\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D22DBA-1C5D-435F-A5C9-8C8B74C7DC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2735A30-046D-4057-AB9E-A1C6EE595CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{16A29E05-5294-4C93-91C1-6C3B8F27AE65}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{16A29E05-5294-4C93-91C1-6C3B8F27AE65}"/>
   </bookViews>
   <sheets>
-    <sheet name="TYPES" sheetId="1" r:id="rId1"/>
-    <sheet name="XLRANGE" sheetId="2" r:id="rId2"/>
-    <sheet name="SCALAR FUNCS" sheetId="3" r:id="rId3"/>
-    <sheet name="EXECX-A-AX" sheetId="4" r:id="rId4"/>
-    <sheet name="BIND" sheetId="5" r:id="rId5"/>
-    <sheet name="INFO" sheetId="6" r:id="rId6"/>
-    <sheet name="ASYNC" sheetId="7" r:id="rId7"/>
-    <sheet name="MULTI STMTS" sheetId="9" r:id="rId8"/>
+    <sheet name="VALUES" sheetId="1" r:id="rId1"/>
+    <sheet name="INFERENCE" sheetId="10" r:id="rId2"/>
+    <sheet name="TYPE DOWNGRADE" sheetId="11" r:id="rId3"/>
+    <sheet name="XLRANGE" sheetId="2" r:id="rId4"/>
+    <sheet name="SCALAR FUNCS" sheetId="3" r:id="rId5"/>
+    <sheet name="EXECX-A-AX" sheetId="4" r:id="rId6"/>
+    <sheet name="BIND" sheetId="5" r:id="rId7"/>
+    <sheet name="INFO" sheetId="6" r:id="rId8"/>
+    <sheet name="MULTI STMTS" sheetId="9" r:id="rId9"/>
+    <sheet name="ASYNC" sheetId="7" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,10 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="113">
-  <si>
-    <t>select 1::tinyint</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="220">
   <si>
     <t>TINYINT</t>
   </si>
@@ -74,33 +73,18 @@
     <t>UTINYINT</t>
   </si>
   <si>
-    <t>select 1::utinyint</t>
-  </si>
-  <si>
     <t>SMALLINT</t>
   </si>
   <si>
     <t>USMALLINT</t>
   </si>
   <si>
-    <t>select 1::smallint</t>
-  </si>
-  <si>
-    <t>select 1::usmallint</t>
-  </si>
-  <si>
     <t>INTEGER</t>
   </si>
   <si>
     <t>UINTEGER</t>
   </si>
   <si>
-    <t>select 1::integer</t>
-  </si>
-  <si>
-    <t>select 1::uinteger</t>
-  </si>
-  <si>
     <t>select true</t>
   </si>
   <si>
@@ -129,12 +113,6 @@
   </si>
   <si>
     <t>UBIGINT</t>
-  </si>
-  <si>
-    <t>select 1::bigint</t>
-  </si>
-  <si>
-    <t>select 1::ubigint</t>
   </si>
   <si>
     <t>HUGEINT</t>
@@ -405,17 +383,364 @@
   </si>
   <si>
     <t>select * from xlrange(1, strict=false, sample=2, ignore_errors=true)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   1    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      1.0   </t>
+  </si>
+  <si>
+    <t>Test case</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      1.2   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     2147483648     </t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>on</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>OFF</t>
+  </si>
+  <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   TRUE   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   FALSE   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   true   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   false   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ON   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   OFF   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   on   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   off   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   T   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   F   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   t   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   f   </t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       NULL          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">       null          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">       N/A          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">       n/a          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    abc    </t>
+  </si>
+  <si>
+    <t>Expected Value</t>
+  </si>
+  <si>
+    <t>Actual Value</t>
+  </si>
+  <si>
+    <t>Value Test Result</t>
+  </si>
+  <si>
+    <t>Value Test SQL</t>
+  </si>
+  <si>
+    <t>Expected Inferred Type</t>
+  </si>
+  <si>
+    <t>Actual Inferred Type</t>
+  </si>
+  <si>
+    <t>Inferred Type Test Result</t>
+  </si>
+  <si>
+    <t>Inferred Type Test SQL</t>
+  </si>
+  <si>
+    <t>Integer</t>
+  </si>
+  <si>
+    <t>Integer stored as text</t>
+  </si>
+  <si>
+    <t>Integer stored as text with leading and trailing space</t>
+  </si>
+  <si>
+    <t>Double</t>
+  </si>
+  <si>
+    <t>Double stored as text</t>
+  </si>
+  <si>
+    <t>Double stored as text with leading and trailing space</t>
+  </si>
+  <si>
+    <t>True/false</t>
+  </si>
+  <si>
+    <t>True/false in text</t>
+  </si>
+  <si>
+    <t>True/false in text with leading and trailing space</t>
+  </si>
+  <si>
+    <t>Empty/ NULL</t>
+  </si>
+  <si>
+    <t>Empty/ NULL as text</t>
+  </si>
+  <si>
+    <t>Empty/ NULL as text with leading and trailing space</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Text with leading and trailing space</t>
+  </si>
+  <si>
+    <t>Number over INT32 limit</t>
+  </si>
+  <si>
+    <t>Number over INT32 limit with leading and trailing space</t>
+  </si>
+  <si>
+    <t>Text (all space)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       </t>
+  </si>
+  <si>
+    <t>Test Number</t>
+  </si>
+  <si>
+    <t>Test Case</t>
+  </si>
+  <si>
+    <t>Excel Value</t>
+  </si>
+  <si>
+    <t>Sample Size</t>
+  </si>
+  <si>
+    <t>select column_type from (describe (from xlrange(1, header=false, sample=?))) where column_name = 'column_0';</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NONE</t>
+  </si>
+  <si>
+    <t>NIL</t>
+  </si>
+  <si>
+    <t>INF</t>
+  </si>
+  <si>
+    <t>NaN</t>
+  </si>
+  <si>
+    <t>-1</t>
+  </si>
+  <si>
+    <t>-1.0</t>
+  </si>
+  <si>
+    <t>1e1</t>
+  </si>
+  <si>
+    <t>-1e1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   1e1    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   -1    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      -1.0   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   -1e1    </t>
+  </si>
+  <si>
+    <t>-1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      -1.2   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      1.2e-2   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      -1.2e-2   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     -2147483649     </t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>Testcase</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>select false</t>
+  </si>
+  <si>
+    <t>select 127::tinyint</t>
+  </si>
+  <si>
+    <t>select (-128)::tinyint</t>
+  </si>
+  <si>
+    <t>select 255::utinyint</t>
+  </si>
+  <si>
+    <t>select 32767::smallint</t>
+  </si>
+  <si>
+    <t>select (-32768)::smallint</t>
+  </si>
+  <si>
+    <t>select 2147483647::integer</t>
+  </si>
+  <si>
+    <t>select (-2147483648)::integer</t>
+  </si>
+  <si>
+    <t>select 65535::usmallint</t>
+  </si>
+  <si>
+    <t>select 4294967295::uinteger</t>
+  </si>
+  <si>
+    <t>select (-1)::hugeint</t>
+  </si>
+  <si>
+    <t>select 18446744073709551615::ubigint</t>
+  </si>
+  <si>
+    <t>select 9223372036854775807::bigint</t>
+  </si>
+  <si>
+    <t>select (-9223372036854775808)::bigint</t>
+  </si>
+  <si>
+    <t>Test result</t>
+  </si>
+  <si>
+    <t>select column_type from (describe (from xlrange(1, header=false, sample=1))) where column_name = 'column_1';</t>
+  </si>
+  <si>
+    <t>select column_1 from xlrange(1, header=false, sample=1)</t>
+  </si>
+  <si>
+    <t>Actual Type</t>
+  </si>
+  <si>
+    <t>Boolean</t>
+  </si>
+  <si>
+    <t>Varchar</t>
+  </si>
+  <si>
+    <t>def</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,18 +762,38 @@
       <family val="3"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -459,7 +804,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -467,33 +812,111 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -803,550 +1226,3842 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5358680-0ED5-4EFA-AB03-B446D1F523DD}">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="72.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
-    <col min="7" max="7" width="38.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="38.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="str" cm="1">
-        <f t="array" ref="B2:B3">_xll.DUCKDB.EXEC(B1)</f>
-        <v>CAST(1 AS "TINYINT")</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="13">
+        <v>127</v>
+      </c>
+      <c r="D2" s="2" cm="1">
+        <f t="array" ref="D2">INDEX(_xll.DUCKDB.EXEC(B2),2)</f>
+        <v>127</v>
+      </c>
+      <c r="E2" s="11" t="str">
+        <f>IF(ISNA(C2),IF(ISNA(D2),"PASS","FAIL"),IFERROR(IF(C2=D2,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="13">
+        <v>-128</v>
+      </c>
+      <c r="D3" s="2" cm="1">
+        <f t="array" ref="D3">INDEX(_xll.DUCKDB.EXEC(B3),2)</f>
+        <v>-128</v>
+      </c>
+      <c r="E3" s="11" t="str">
+        <f t="shared" ref="E3:E35" si="0">IF(ISNA(C3),IF(ISNA(D3),"PASS","FAIL"),IFERROR(IF(C3=D3,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="13">
+        <v>255</v>
+      </c>
+      <c r="D4" s="2" cm="1">
+        <f t="array" ref="D4">INDEX(_xll.DUCKDB.EXEC(B4),2)</f>
+        <v>255</v>
+      </c>
+      <c r="E4" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="13">
+        <v>32767</v>
+      </c>
+      <c r="D5" s="2" cm="1">
+        <f t="array" ref="D5">INDEX(_xll.DUCKDB.EXEC(B5),2)</f>
+        <v>32767</v>
+      </c>
+      <c r="E5" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="13">
+        <v>-32768</v>
+      </c>
+      <c r="D6" s="2" cm="1">
+        <f t="array" ref="D6">INDEX(_xll.DUCKDB.EXEC(B6),2)</f>
+        <v>-32768</v>
+      </c>
+      <c r="E6" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="str" cm="1">
-        <f t="array" ref="B6:B7">_xll.DUCKDB.EXEC(B5)</f>
-        <v>CAST(1 AS "UTINYINT")</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="13">
+        <v>65535</v>
+      </c>
+      <c r="D7" s="2" cm="1">
+        <f t="array" ref="D7">INDEX(_xll.DUCKDB.EXEC(B7),2)</f>
+        <v>65535</v>
+      </c>
+      <c r="E7" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" s="13">
+        <v>2147483647</v>
+      </c>
+      <c r="D8" s="2" cm="1">
+        <f t="array" ref="D8">INDEX(_xll.DUCKDB.EXEC(B8),2)</f>
+        <v>2147483647</v>
+      </c>
+      <c r="E8" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="13">
+        <v>-2147483648</v>
+      </c>
+      <c r="D9" s="2" cm="1">
+        <f t="array" ref="D9">INDEX(_xll.DUCKDB.EXEC(B9),2)</f>
+        <v>-2147483648</v>
+      </c>
+      <c r="E9" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C10" s="13">
+        <v>4294967295</v>
+      </c>
+      <c r="D10" s="2" cm="1">
+        <f t="array" ref="D10">INDEX(_xll.DUCKDB.EXEC(B10),2)</f>
+        <v>4294967295</v>
+      </c>
+      <c r="E10" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C11" s="13">
+        <v>9.2233720368547758E+18</v>
+      </c>
+      <c r="D11" s="2" cm="1">
+        <f t="array" ref="D11">INDEX(_xll.DUCKDB.EXEC(B11),2)</f>
+        <v>9.2233720368547758E+18</v>
+      </c>
+      <c r="E11" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="13">
+        <v>-9.2233720368547758E+18</v>
+      </c>
+      <c r="D12" s="2" cm="1">
+        <f t="array" ref="D12">INDEX(_xll.DUCKDB.EXEC(B12),2)</f>
+        <v>-9.2233720368547758E+18</v>
+      </c>
+      <c r="E12" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C13" s="13">
+        <v>1.8446744073709552E+19</v>
+      </c>
+      <c r="D13" s="2" cm="1">
+        <f t="array" ref="D13">INDEX(_xll.DUCKDB.EXEC(B13),2)</f>
+        <v>1.8446744073709552E+19</v>
+      </c>
+      <c r="E13" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="13">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" cm="1">
+        <f t="array" ref="D14">INDEX(_xll.DUCKDB.EXEC(B14),2)</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="13">
+        <v>-1</v>
+      </c>
+      <c r="D15" s="2" cm="1">
+        <f t="array" ref="D15">INDEX(_xll.DUCKDB.EXEC(B15),2)</f>
+        <v>-1</v>
+      </c>
+      <c r="E15" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="13">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" cm="1">
+        <f t="array" ref="D16">INDEX(_xll.DUCKDB.EXEC(B16),2)</f>
+        <v>1</v>
+      </c>
+      <c r="E16" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="str" cm="1">
-        <f t="array" ref="B10:B11">_xll.DUCKDB.EXEC(B9)</f>
-        <v>CAST(1 AS SMALLINT)</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="C17" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="b" cm="1">
+        <f t="array" ref="D17">INDEX(_xll.DUCKDB.EXEC(B17),2)</f>
+        <v>1</v>
+      </c>
+      <c r="E17" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="str" cm="1">
-        <f t="array" ref="B14:B15">_xll.DUCKDB.EXEC(B13)</f>
-        <v>CAST(1 AS "USMALLINT")</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B18" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="b" cm="1">
+        <f t="array" ref="D18">INDEX(_xll.DUCKDB.EXEC(B18),2)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B19" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="2" t="str" cm="1">
+        <f t="array" ref="D19">INDEX(_xll.DUCKDB.EXEC(B19),2)</f>
+        <v>abc</v>
+      </c>
+      <c r="E19" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="str" cm="1">
-        <f t="array" ref="B18:B19">_xll.DUCKDB.EXEC(B17)</f>
-        <v>CAST(1 AS INTEGER)</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="D20" s="2" cm="1">
+        <f t="array" ref="D20">INDEX(_xll.DUCKDB.EXEC(B20),2)</f>
+        <v>1.2000000476837158</v>
+      </c>
+      <c r="E20" s="11" t="str">
+        <f>IF(ISNA(C20),IF(ISNA(D20),"PASS","FAIL"),IFERROR(IF(ABS(C20-D20)&lt;0.0000001,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="str" cm="1">
-        <f t="array" ref="B22:B23">_xll.DUCKDB.EXEC(B21)</f>
-        <v>CAST(1 AS "UINTEGER")</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="D21" s="2" cm="1">
+        <f t="array" ref="D21">INDEX(_xll.DUCKDB.EXEC(B21),2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="E21" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="D22" s="2" cm="1">
+        <f t="array" ref="D22">INDEX(_xll.DUCKDB.EXEC(B22),2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="E22" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="D23" s="2" cm="1">
+        <f t="array" ref="D23">INDEX(_xll.DUCKDB.EXEC(B23),2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="E23" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="D24" s="2" cm="1">
+        <f t="array" ref="D24">INDEX(_xll.DUCKDB.EXEC(B24),2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="E24" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="str" cm="1">
-        <f t="array" ref="B26:B27">_xll.DUCKDB.EXEC(B25)</f>
-        <v>CAST(1 AS BIGINT)</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="D25" s="2" cm="1">
+        <f t="array" ref="D25">INDEX(_xll.DUCKDB.EXEC(B25),2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="E25" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="15">
+        <v>46387</v>
+      </c>
+      <c r="D26" s="3" cm="1">
+        <f t="array" ref="D26">INDEX(_xll.DUCKDB.EXEC(B26),2)</f>
+        <v>46387</v>
+      </c>
+      <c r="E26" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="16">
+        <v>0.39635416666666667</v>
+      </c>
+      <c r="D27" s="14" cm="1">
+        <f t="array" ref="D27">INDEX(_xll.DUCKDB.EXEC(B27),2)</f>
+        <v>0.39635416666666667</v>
+      </c>
+      <c r="E27" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="16">
+        <v>0.39635416666666667</v>
+      </c>
+      <c r="D28" s="14" cm="1">
+        <f t="array" ref="D28">INDEX(_xll.DUCKDB.EXEC(B28),2)</f>
+        <v>0.39635416666666667</v>
+      </c>
+      <c r="E28" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="str" cm="1">
-        <f t="array" ref="B30:B31">_xll.DUCKDB.EXEC(B29)</f>
-        <v>CAST(1 AS "UBIGINT")</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="17">
+        <v>46387.396354166667</v>
+      </c>
+      <c r="D29" s="4" cm="1">
+        <f t="array" ref="D29">INDEX(_xll.DUCKDB.EXEC(B29),2)</f>
+        <v>46387.396354166667</v>
+      </c>
+      <c r="E29" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="17">
+        <v>46387.104687500003</v>
+      </c>
+      <c r="D30" s="4" cm="1">
+        <f t="array" ref="D30">INDEX(_xll.DUCKDB.EXEC(B30),2)</f>
+        <v>46387.104687500003</v>
+      </c>
+      <c r="E30" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="17">
+        <v>46387.396354166667</v>
+      </c>
+      <c r="D31" s="4" cm="1">
+        <f t="array" ref="D31">INDEX(_xll.DUCKDB.EXEC(B31),2)</f>
+        <v>46387.396354166667</v>
+      </c>
+      <c r="E31" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="17">
+        <v>46387.396354166667</v>
+      </c>
+      <c r="D32" s="4" cm="1">
+        <f t="array" ref="D32">INDEX(_xll.DUCKDB.EXEC(B32),2)</f>
+        <v>46387.396354166667</v>
+      </c>
+      <c r="E32" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="str" cm="1">
-        <f t="array" ref="B34:B35">_xll.DUCKDB.EXEC(B33)</f>
-        <v>CAST(1 AS "HUGEINT")</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>25</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="str" cm="1">
-        <f t="array" ref="B38:B39">_xll.DUCKDB.EXEC(B37)</f>
-        <v>CAST(1 AS "UHUGEINT")</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="str" cm="1">
-        <f t="array" ref="B42:B43">_xll.DUCKDB.EXEC(B41)</f>
-        <v>CAST('t' AS BOOLEAN)</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>14</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="str" cm="1">
-        <f t="array" ref="B46:B47">_xll.DUCKDB.EXEC(B45)</f>
-        <v>'abc'</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="str">
-        <v>abc</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>16</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="str" cm="1">
-        <f t="array" ref="B50:B51">_xll.DUCKDB.EXEC(B49)</f>
-        <v>CAST(1.2 AS FLOAT)</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="2">
-        <v>1.2000000476837158</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>18</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="str" cm="1">
-        <f t="array" ref="B54:B55">_xll.DUCKDB.EXEC(B53)</f>
-        <v>CAST(1.2 AS "DOUBLE")</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B55" s="2">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>28</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B58" s="2" t="str" cm="1">
-        <f t="array" ref="B58:B59">_xll.DUCKDB.EXEC(B57)</f>
-        <v>CAST(1.2 AS DECIMAL(4, 2))</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B59" s="2">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>30</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="str" cm="1">
-        <f t="array" ref="B62:B63">_xll.DUCKDB.EXEC(B61)</f>
-        <v>CAST(1.2 AS DECIMAL(9, 2))</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B63" s="2">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>32</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B66" s="2" t="str" cm="1">
-        <f t="array" ref="B66:B67">_xll.DUCKDB.EXEC(B65)</f>
-        <v>CAST(1.2 AS DECIMAL(18, 2))</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B67" s="2">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>34</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B70" s="2" t="str" cm="1">
-        <f t="array" ref="B70:B71">_xll.DUCKDB.EXEC(B69)</f>
-        <v>CAST(1.2 AS DECIMAL(38, 2))</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B71" s="2">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>36</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B74" s="2" t="str" cm="1">
-        <f t="array" ref="B74:B75">_xll.DUCKDB.EXEC(B73)</f>
-        <v>CAST('2026-12-31' AS "DATE")</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B75" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>38</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B78" s="2" t="str" cm="1">
-        <f t="array" ref="B78:B79">_xll.DUCKDB.EXEC(B77)</f>
-        <v>CAST('09:30:45' AS TIME)</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B79" s="5">
-        <v>0.39635416666666667</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>40</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B82" s="2" t="str" cm="1">
-        <f t="array" ref="B82:B83">_xll.DUCKDB.EXEC(B81)</f>
-        <v>CAST('09:30:45+07:00' AS "TIME WITH TIME ZONE")</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B83" s="5">
-        <v>0.39635416666666667</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
         <v>42</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B33" s="13" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B86" s="2" t="str" cm="1">
-        <f t="array" ref="B86:B87">_xll.DUCKDB.EXEC(B85)</f>
-        <v>CAST('2026-12-31 09:30:45' AS TIMESTAMP)</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B87" s="6">
+      <c r="C33" s="17">
         <v>46387.396354166667</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="D33" s="4" cm="1">
+        <f t="array" ref="D33">INDEX(_xll.DUCKDB.EXEC(B33),2)</f>
+        <v>46387.396354166667</v>
+      </c>
+      <c r="E33" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>44</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B34" s="13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B90" s="2" t="str" cm="1">
-        <f t="array" ref="B90:B91">_xll.DUCKDB.EXEC(B89)</f>
-        <v>CAST('2026-12-31 09:30:45+07:00' AS "TIMESTAMP WITH TIME ZONE")</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B91" s="6">
-        <v>46387.104687500003</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="C34" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D34" s="2" t="e" cm="1">
+        <f t="array" ref="D34">INDEX(_xll.DUCKDB.EXEC(B34),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E34" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>46</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B94" s="2" t="str" cm="1">
-        <f t="array" ref="B94:B95">_xll.DUCKDB.EXEC(B93)</f>
-        <v>CAST('2026-12-31 09:30:45' AS "TIMESTAMP_S")</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B95" s="6">
-        <v>46387.396354166667</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>48</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B98" s="2" t="str" cm="1">
-        <f t="array" ref="B98:B99">_xll.DUCKDB.EXEC(B97)</f>
-        <v>CAST('2026-12-31 09:30:45' AS "TIMESTAMP_MS")</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B99" s="6">
-        <v>46387.396354166667</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>50</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B102" s="2" t="str" cm="1">
-        <f t="array" ref="B102:B103">_xll.DUCKDB.EXEC(B101)</f>
-        <v>CAST('2026-12-31 09:30:45' AS "TIMESTAMP_NS")</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B103" s="6">
-        <v>46387.396354166667</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>52</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B106" s="2" t="str" cm="1">
-        <f t="array" ref="B106:B107">_xll.DUCKDB.EXEC(B105)</f>
-        <v>NULL</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B107" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>54</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B110" s="2" t="str" cm="1">
-        <f t="array" ref="B110">_xll.DUCKDB.EXEC(B109)</f>
+      <c r="B35" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D35" s="2" t="str" cm="1">
+        <f t="array" ref="D35">_xll.DUCKDB.EXEC(B35)</f>
         <v>Error fetching data: Column my_column: Unsupported DuckDB type. Convert the value to VARCHAR before returning it to Excel.</v>
       </c>
+      <c r="E35" s="11" t="str">
+        <f>IF(ISNA(C35),IF(ISNA(D35),"PASS","FAIL"),IFERROR(IF(C35=LEFT(D35,LEN(C35)),"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E2:E35">
+    <cfRule type="cellIs" dxfId="3" priority="1" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE0166A-6705-4BE6-BC5D-3DDB4234D0EA}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" t="str" cm="1">
+        <f t="array" ref="B2:B3">_xll.DUCKDB.EXEC.ASYNC(B1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="str" cm="1">
+        <f t="array" ref="B5:B6">_xll.DUCKDB.EXECX.ASYNC(,B1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" t="str" cm="1">
+        <f t="array" ref="B8:B9">_xll.DUCKDB.EXECA.ASYNC(,B1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="str" cm="1">
+        <f t="array" ref="B11:B12">_xll.DUCKDB.EXECAX.ASYNC(,,B1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596BDC2F-78D8-495C-B354-FBB81CDDC292}">
+  <dimension ref="A1:K76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="43.28515625" customWidth="1"/>
+    <col min="5" max="5" width="20" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="21.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="22">
+        <v>1</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="25" t="str" cm="1">
+        <f t="array" ref="F2">INDEX(_xll.DUCKDB.EXEC($D$2,B2:C2),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G2" s="25" t="str">
+        <f>IF(E2=F2,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="I2" s="22">
+        <f>C2</f>
+        <v>1</v>
+      </c>
+      <c r="J2" s="22" cm="1">
+        <f t="array" ref="J2">INDEX(_xll.DUCKDB.EXEC($H$2,B2:C2),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K2" s="25" t="str">
+        <f>IF(ISNA(I2),IF(ISNA(J2),"PASS","FAIL"),IFERROR(IF(I2=J2,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25">
+        <v>2</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="22">
+        <v>-1</v>
+      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="25" t="str" cm="1">
+        <f t="array" ref="F3">INDEX(_xll.DUCKDB.EXEC($D$2,B3:C3),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G3" s="25" t="str">
+        <f>IF(E3=F3,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="22">
+        <f>C3</f>
+        <v>-1</v>
+      </c>
+      <c r="J3" s="22" cm="1">
+        <f t="array" ref="J3">INDEX(_xll.DUCKDB.EXEC($H$2,B3:C3),2)</f>
+        <v>-1</v>
+      </c>
+      <c r="K3" s="25" t="str">
+        <f>IF(ISNA(I3),IF(ISNA(J3),"PASS","FAIL"),IFERROR(IF(I3=J3,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="25">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="27">
+        <v>2</v>
+      </c>
+      <c r="D4" s="26"/>
+      <c r="E4" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="25" t="str" cm="1">
+        <f t="array" ref="F4">INDEX(_xll.DUCKDB.EXEC($D$2,B4:C4),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G4" s="25" t="str">
+        <f t="shared" ref="G4:G43" si="0">IF(E4=F4,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H4" s="26"/>
+      <c r="I4" s="22">
+        <f>C4</f>
+        <v>2</v>
+      </c>
+      <c r="J4" s="22" cm="1">
+        <f t="array" ref="J4">INDEX(_xll.DUCKDB.EXEC($H$2,B4:C4),2)</f>
+        <v>2</v>
+      </c>
+      <c r="K4" s="25" t="str">
+        <f t="shared" ref="K4:K71" si="1">IF(ISNA(I4),IF(ISNA(J4),"PASS","FAIL"),IFERROR(IF(I4=J4,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="25">
+        <v>4</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="27">
+        <v>-2</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="25" t="str" cm="1">
+        <f t="array" ref="F5">INDEX(_xll.DUCKDB.EXEC($D$2,B5:C5),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G5" s="25" t="str">
+        <f t="shared" ref="G5" si="2">IF(E5=F5,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H5" s="26"/>
+      <c r="I5" s="22">
+        <f>C5</f>
+        <v>-2</v>
+      </c>
+      <c r="J5" s="22" cm="1">
+        <f t="array" ref="J5">INDEX(_xll.DUCKDB.EXEC($H$2,B5:C5),2)</f>
+        <v>-2</v>
+      </c>
+      <c r="K5" s="25" t="str">
+        <f t="shared" ref="K5" si="3">IF(ISNA(I5),IF(ISNA(J5),"PASS","FAIL"),IFERROR(IF(I5=J5,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="25">
+        <v>5</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="25" t="str" cm="1">
+        <f t="array" ref="F6">INDEX(_xll.DUCKDB.EXEC($D$2,B6:C6),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G6" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H6" s="26"/>
+      <c r="I6" s="22">
+        <v>1</v>
+      </c>
+      <c r="J6" s="22" cm="1">
+        <f t="array" ref="J6">INDEX(_xll.DUCKDB.EXEC($H$2,B6:C6),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K6" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="25">
+        <v>6</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="25" t="str" cm="1">
+        <f t="array" ref="F7">INDEX(_xll.DUCKDB.EXEC($D$2,B7:C7),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G7" s="25" t="str">
+        <f t="shared" ref="G7" si="4">IF(E7=F7,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H7" s="26"/>
+      <c r="I7" s="22">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="22" cm="1">
+        <f t="array" ref="J7">INDEX(_xll.DUCKDB.EXEC($H$2,B7:C7),2)</f>
+        <v>-1</v>
+      </c>
+      <c r="K7" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>7</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="26"/>
+      <c r="E8" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="25" t="str" cm="1">
+        <f t="array" ref="F8">INDEX(_xll.DUCKDB.EXEC($D$2,B8:C8),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G8" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H8" s="26"/>
+      <c r="I8" s="22">
+        <v>1</v>
+      </c>
+      <c r="J8" s="22" cm="1">
+        <f t="array" ref="J8">INDEX(_xll.DUCKDB.EXEC($H$2,B8:C8),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K8" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="25">
+        <v>8</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="25" t="str" cm="1">
+        <f t="array" ref="F9">INDEX(_xll.DUCKDB.EXEC($D$2,B9:C9),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G9" s="25" t="str">
+        <f t="shared" ref="G9" si="5">IF(E9=F9,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H9" s="26"/>
+      <c r="I9" s="22">
+        <v>-1</v>
+      </c>
+      <c r="J9" s="22" cm="1">
+        <f t="array" ref="J9">INDEX(_xll.DUCKDB.EXEC($H$2,B9:C9),2)</f>
+        <v>-1</v>
+      </c>
+      <c r="K9" s="25" t="str">
+        <f t="shared" ref="K9:K10" si="6">IF(ISNA(I9),IF(ISNA(J9),"PASS","FAIL"),IFERROR(IF(I9=J9,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="25">
+        <v>9</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="26"/>
+      <c r="E10" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="25" t="str" cm="1">
+        <f t="array" ref="F10">INDEX(_xll.DUCKDB.EXEC($D$2,B10:C10),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G10" s="25" t="str">
+        <f t="shared" ref="G10:G11" si="7">IF(E10=F10,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H10" s="26"/>
+      <c r="I10" s="22">
+        <v>10</v>
+      </c>
+      <c r="J10" s="22" cm="1">
+        <f t="array" ref="J10">INDEX(_xll.DUCKDB.EXEC($H$2,B10:C10),2)</f>
+        <v>10</v>
+      </c>
+      <c r="K10" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="25">
+        <v>10</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="25" t="str" cm="1">
+        <f t="array" ref="F11">INDEX(_xll.DUCKDB.EXEC($D$2,B11:C11),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G11" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>PASS</v>
+      </c>
+      <c r="H11" s="26"/>
+      <c r="I11" s="22">
+        <v>-10</v>
+      </c>
+      <c r="J11" s="22" cm="1">
+        <f t="array" ref="J11">INDEX(_xll.DUCKDB.EXEC($H$2,B11:C11),2)</f>
+        <v>-10</v>
+      </c>
+      <c r="K11" s="25" t="str">
+        <f t="shared" ref="K11" si="8">IF(ISNA(I11),IF(ISNA(J11),"PASS","FAIL"),IFERROR(IF(I11=J11,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="25">
+        <v>11</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="25" t="str" cm="1">
+        <f t="array" ref="F12">INDEX(_xll.DUCKDB.EXEC($D$2,B12:C12),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G12" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H12" s="26"/>
+      <c r="I12" s="22">
+        <v>1</v>
+      </c>
+      <c r="J12" s="22" cm="1">
+        <f t="array" ref="J12">INDEX(_xll.DUCKDB.EXEC($H$2,B12:C12),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K12" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="25">
+        <v>12</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="26"/>
+      <c r="E13" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="25" t="str" cm="1">
+        <f t="array" ref="F13">INDEX(_xll.DUCKDB.EXEC($D$2,B13:C13),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G13" s="25" t="str">
+        <f t="shared" ref="G13" si="9">IF(E13=F13,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H13" s="26"/>
+      <c r="I13" s="22">
+        <v>-1</v>
+      </c>
+      <c r="J13" s="22" cm="1">
+        <f t="array" ref="J13">INDEX(_xll.DUCKDB.EXEC($H$2,B13:C13),2)</f>
+        <v>-1</v>
+      </c>
+      <c r="K13" s="25" t="str">
+        <f t="shared" ref="K13" si="10">IF(ISNA(I13),IF(ISNA(J13),"PASS","FAIL"),IFERROR(IF(I13=J13,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="25">
+        <v>13</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="25" t="str" cm="1">
+        <f t="array" ref="F14">INDEX(_xll.DUCKDB.EXEC($D$2,B14:C14),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G14" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H14" s="26"/>
+      <c r="I14" s="22">
+        <v>1</v>
+      </c>
+      <c r="J14" s="22" cm="1">
+        <f t="array" ref="J14">INDEX(_xll.DUCKDB.EXEC($H$2,B14:C14),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="25">
+        <v>14</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="26"/>
+      <c r="E15" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="25" t="str" cm="1">
+        <f t="array" ref="F15">INDEX(_xll.DUCKDB.EXEC($D$2,B15:C15),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G15" s="25" t="str">
+        <f t="shared" ref="G15" si="11">IF(E15=F15,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H15" s="26"/>
+      <c r="I15" s="22">
+        <v>-1</v>
+      </c>
+      <c r="J15" s="22" cm="1">
+        <f t="array" ref="J15">INDEX(_xll.DUCKDB.EXEC($H$2,B15:C15),2)</f>
+        <v>-1</v>
+      </c>
+      <c r="K15" s="25" t="str">
+        <f t="shared" ref="K15" si="12">IF(ISNA(I15),IF(ISNA(J15),"PASS","FAIL"),IFERROR(IF(I15=J15,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="25">
+        <v>15</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16" s="26"/>
+      <c r="E16" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="25" t="str" cm="1">
+        <f t="array" ref="F16">INDEX(_xll.DUCKDB.EXEC($D$2,B16:C16),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G16" s="25" t="str">
+        <f t="shared" ref="G16" si="13">IF(E16=F16,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H16" s="26"/>
+      <c r="I16" s="22">
+        <v>10</v>
+      </c>
+      <c r="J16" s="22" cm="1">
+        <f t="array" ref="J16">INDEX(_xll.DUCKDB.EXEC($H$2,B16:C16),2)</f>
+        <v>10</v>
+      </c>
+      <c r="K16" s="25" t="str">
+        <f t="shared" ref="K16" si="14">IF(ISNA(I16),IF(ISNA(J16),"PASS","FAIL"),IFERROR(IF(I16=J16,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="25">
+        <v>16</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" s="26"/>
+      <c r="E17" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="25" t="str" cm="1">
+        <f t="array" ref="F17">INDEX(_xll.DUCKDB.EXEC($D$2,B17:C17),2)</f>
+        <v>INTEGER</v>
+      </c>
+      <c r="G17" s="25" t="str">
+        <f t="shared" ref="G17" si="15">IF(E17=F17,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H17" s="26"/>
+      <c r="I17" s="22">
+        <v>-10</v>
+      </c>
+      <c r="J17" s="22" cm="1">
+        <f t="array" ref="J17">INDEX(_xll.DUCKDB.EXEC($H$2,B17:C17),2)</f>
+        <v>-10</v>
+      </c>
+      <c r="K17" s="25" t="str">
+        <f t="shared" ref="K17" si="16">IF(ISNA(I17),IF(ISNA(J17),"PASS","FAIL"),IFERROR(IF(I17=J17,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="25">
+        <v>17</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="C18" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="D18" s="26"/>
+      <c r="E18" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="25" t="str" cm="1">
+        <f t="array" ref="F18">INDEX(_xll.DUCKDB.EXEC($D$2,B18:C18),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G18" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H18" s="26"/>
+      <c r="I18" s="22">
+        <f>C18</f>
+        <v>1.2</v>
+      </c>
+      <c r="J18" s="22" cm="1">
+        <f t="array" ref="J18">INDEX(_xll.DUCKDB.EXEC($H$2,B18:C18),2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="K18" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="25">
+        <v>18</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" s="22">
+        <v>-1.2</v>
+      </c>
+      <c r="D19" s="26"/>
+      <c r="E19" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="25" t="str" cm="1">
+        <f t="array" ref="F19">INDEX(_xll.DUCKDB.EXEC($D$2,B19:C19),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G19" s="25" t="str">
+        <f t="shared" ref="G19" si="17">IF(E19=F19,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H19" s="26"/>
+      <c r="I19" s="22">
+        <f>C19</f>
+        <v>-1.2</v>
+      </c>
+      <c r="J19" s="22" cm="1">
+        <f t="array" ref="J19">INDEX(_xll.DUCKDB.EXEC($H$2,B19:C19),2)</f>
+        <v>-1.2</v>
+      </c>
+      <c r="K19" s="25" t="str">
+        <f t="shared" ref="K19" si="18">IF(ISNA(I19),IF(ISNA(J19),"PASS","FAIL"),IFERROR(IF(I19=J19,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>19</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="26"/>
+      <c r="E20" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="25" t="str" cm="1">
+        <f t="array" ref="F20">INDEX(_xll.DUCKDB.EXEC($D$2,B20:C20),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G20" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H20" s="26"/>
+      <c r="I20" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="J20" s="22" cm="1">
+        <f t="array" ref="J20">INDEX(_xll.DUCKDB.EXEC($H$2,B20:C20),2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="K20" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>20</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" s="26"/>
+      <c r="E21" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="25" t="str" cm="1">
+        <f t="array" ref="F21">INDEX(_xll.DUCKDB.EXEC($D$2,B21:C21),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G21" s="25" t="str">
+        <f t="shared" ref="G21" si="19">IF(E21=F21,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H21" s="26"/>
+      <c r="I21" s="22">
+        <v>-1.2</v>
+      </c>
+      <c r="J21" s="22" cm="1">
+        <f t="array" ref="J21">INDEX(_xll.DUCKDB.EXEC($H$2,B21:C21),2)</f>
+        <v>-1.2</v>
+      </c>
+      <c r="K21" s="25" t="str">
+        <f t="shared" ref="K21" si="20">IF(ISNA(I21),IF(ISNA(J21),"PASS","FAIL"),IFERROR(IF(I21=J21,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>21</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" s="26"/>
+      <c r="E22" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="25" t="str" cm="1">
+        <f t="array" ref="F22">INDEX(_xll.DUCKDB.EXEC($D$2,B22:C22),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G22" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H22" s="26"/>
+      <c r="I22" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="J22" s="22" cm="1">
+        <f t="array" ref="J22">INDEX(_xll.DUCKDB.EXEC($H$2,B22:C22),2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="K22" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>22</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" s="26"/>
+      <c r="E23" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="25" t="str" cm="1">
+        <f t="array" ref="F23">INDEX(_xll.DUCKDB.EXEC($D$2,B23:C23),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G23" s="25" t="str">
+        <f t="shared" ref="G23:G24" si="21">IF(E23=F23,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H23" s="26"/>
+      <c r="I23" s="22">
+        <v>-1.2</v>
+      </c>
+      <c r="J23" s="22" cm="1">
+        <f t="array" ref="J23">INDEX(_xll.DUCKDB.EXEC($H$2,B23:C23),2)</f>
+        <v>-1.2</v>
+      </c>
+      <c r="K23" s="25" t="str">
+        <f t="shared" ref="K23:K24" si="22">IF(ISNA(I23),IF(ISNA(J23),"PASS","FAIL"),IFERROR(IF(I23=J23,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>23</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D24" s="26"/>
+      <c r="E24" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="25" t="str" cm="1">
+        <f t="array" ref="F24">INDEX(_xll.DUCKDB.EXEC($D$2,B24:C24),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G24" s="25" t="str">
+        <f t="shared" si="21"/>
+        <v>PASS</v>
+      </c>
+      <c r="H24" s="26"/>
+      <c r="I24" s="22">
+        <v>1.2E-2</v>
+      </c>
+      <c r="J24" s="22" cm="1">
+        <f t="array" ref="J24">INDEX(_xll.DUCKDB.EXEC($H$2,B24:C24),2)</f>
+        <v>1.2E-2</v>
+      </c>
+      <c r="K24" s="25" t="str">
+        <f t="shared" si="22"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="25" t="str" cm="1">
+        <f t="array" ref="F25">INDEX(_xll.DUCKDB.EXEC($D$2,B25:C25),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G25" s="25" t="str">
+        <f t="shared" ref="G25" si="23">IF(E25=F25,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H25" s="26"/>
+      <c r="I25" s="22">
+        <v>-1.2E-2</v>
+      </c>
+      <c r="J25" s="22" cm="1">
+        <f t="array" ref="J25">INDEX(_xll.DUCKDB.EXEC($H$2,B25:C25),2)</f>
+        <v>-1.2E-2</v>
+      </c>
+      <c r="K25" s="25" t="str">
+        <f t="shared" ref="K25" si="24">IF(ISNA(I25),IF(ISNA(J25),"PASS","FAIL"),IFERROR(IF(I25=J25,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>25</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="22">
+        <v>2147483648</v>
+      </c>
+      <c r="D26" s="26"/>
+      <c r="E26" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="25" t="str" cm="1">
+        <f t="array" ref="F26">INDEX(_xll.DUCKDB.EXEC($D$2,B26:C26),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G26" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H26" s="26"/>
+      <c r="I26" s="22">
+        <f>C26</f>
+        <v>2147483648</v>
+      </c>
+      <c r="J26" s="22" cm="1">
+        <f t="array" ref="J26">INDEX(_xll.DUCKDB.EXEC($H$2,B26:C26),2)</f>
+        <v>2147483648</v>
+      </c>
+      <c r="K26" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>26</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" s="22">
+        <v>-2147483649</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="25" t="str" cm="1">
+        <f t="array" ref="F27">INDEX(_xll.DUCKDB.EXEC($D$2,B27:C27),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G27" s="25" t="str">
+        <f t="shared" ref="G27" si="25">IF(E27=F27,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H27" s="26"/>
+      <c r="I27" s="22">
+        <f>C27</f>
+        <v>-2147483649</v>
+      </c>
+      <c r="J27" s="22" cm="1">
+        <f t="array" ref="J27">INDEX(_xll.DUCKDB.EXEC($H$2,B27:C27),2)</f>
+        <v>-2147483649</v>
+      </c>
+      <c r="K27" s="25" t="str">
+        <f t="shared" ref="K27" si="26">IF(ISNA(I27),IF(ISNA(J27),"PASS","FAIL"),IFERROR(IF(I27=J27,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>27</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="26"/>
+      <c r="E28" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="25" t="str" cm="1">
+        <f t="array" ref="F28">INDEX(_xll.DUCKDB.EXEC($D$2,B28:C28),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G28" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H28" s="26"/>
+      <c r="I28" s="22">
+        <v>2147483648</v>
+      </c>
+      <c r="J28" s="22" cm="1">
+        <f t="array" ref="J28">INDEX(_xll.DUCKDB.EXEC($H$2,B28:C28),2)</f>
+        <v>2147483648</v>
+      </c>
+      <c r="K28" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>28</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D29" s="26"/>
+      <c r="E29" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="25" t="str" cm="1">
+        <f t="array" ref="F29">INDEX(_xll.DUCKDB.EXEC($D$2,B29:C29),2)</f>
+        <v>DOUBLE</v>
+      </c>
+      <c r="G29" s="25" t="str">
+        <f t="shared" ref="G29" si="27">IF(E29=F29,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H29" s="26"/>
+      <c r="I29" s="22">
+        <v>-2147483649</v>
+      </c>
+      <c r="J29" s="22" cm="1">
+        <f t="array" ref="J29">INDEX(_xll.DUCKDB.EXEC($H$2,B29:C29),2)</f>
+        <v>-2147483649</v>
+      </c>
+      <c r="K29" s="25" t="str">
+        <f t="shared" ref="K29" si="28">IF(ISNA(I29),IF(ISNA(J29),"PASS","FAIL"),IFERROR(IF(I29=J29,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>29</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" s="26"/>
+      <c r="E30" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="25" t="str" cm="1">
+        <f t="array" ref="F30">INDEX(_xll.DUCKDB.EXEC($D$2,B30:C30),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G30" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H30" s="26"/>
+      <c r="I30" s="22" t="b">
+        <f>C30</f>
+        <v>1</v>
+      </c>
+      <c r="J30" s="22" t="b" cm="1">
+        <f t="array" ref="J30">INDEX(_xll.DUCKDB.EXEC($H$2,B30:C30),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K30" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>30</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" s="26"/>
+      <c r="E31" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="25" t="str" cm="1">
+        <f t="array" ref="F31">INDEX(_xll.DUCKDB.EXEC($D$2,B31:C31),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G31" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H31" s="26"/>
+      <c r="I31" s="22" t="b">
+        <f>C31</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="22" t="b" cm="1">
+        <f t="array" ref="J31">INDEX(_xll.DUCKDB.EXEC($H$2,B31:C31),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
+        <v>31</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="26"/>
+      <c r="E32" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="25" t="str" cm="1">
+        <f t="array" ref="F32">INDEX(_xll.DUCKDB.EXEC($D$2,B32:C32),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G32" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H32" s="26"/>
+      <c r="I32" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" s="22" t="b" cm="1">
+        <f t="array" ref="J32">INDEX(_xll.DUCKDB.EXEC($H$2,B32:C32),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K32" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="25">
+        <v>32</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" s="26"/>
+      <c r="E33" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="25" t="str" cm="1">
+        <f t="array" ref="F33">INDEX(_xll.DUCKDB.EXEC($D$2,B33:C33),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G33" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H33" s="26"/>
+      <c r="I33" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" s="22" t="b" cm="1">
+        <f t="array" ref="J33">INDEX(_xll.DUCKDB.EXEC($H$2,B33:C33),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="25">
+        <v>33</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" s="26"/>
+      <c r="E34" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="25" t="str" cm="1">
+        <f t="array" ref="F34">INDEX(_xll.DUCKDB.EXEC($D$2,B34:C34),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G34" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H34" s="26"/>
+      <c r="I34" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" s="22" t="b" cm="1">
+        <f t="array" ref="J34">INDEX(_xll.DUCKDB.EXEC($H$2,B34:C34),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K34" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>34</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" s="26"/>
+      <c r="E35" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="25" t="str" cm="1">
+        <f t="array" ref="F35">INDEX(_xll.DUCKDB.EXEC($D$2,B35:C35),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G35" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H35" s="26"/>
+      <c r="I35" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" s="22" t="b" cm="1">
+        <f t="array" ref="J35">INDEX(_xll.DUCKDB.EXEC($H$2,B35:C35),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>35</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" s="26"/>
+      <c r="E36" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="25" t="str" cm="1">
+        <f t="array" ref="F36">INDEX(_xll.DUCKDB.EXEC($D$2,B36:C36),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G36" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H36" s="26"/>
+      <c r="I36" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" s="22" t="b" cm="1">
+        <f t="array" ref="J36">INDEX(_xll.DUCKDB.EXEC($H$2,B36:C36),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K36" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>36</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" s="26"/>
+      <c r="E37" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="25" t="str" cm="1">
+        <f t="array" ref="F37">INDEX(_xll.DUCKDB.EXEC($D$2,B37:C37),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G37" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H37" s="26"/>
+      <c r="I37" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" s="22" t="b" cm="1">
+        <f t="array" ref="J37">INDEX(_xll.DUCKDB.EXEC($H$2,B37:C37),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>37</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D38" s="26"/>
+      <c r="E38" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="25" t="str" cm="1">
+        <f t="array" ref="F38">INDEX(_xll.DUCKDB.EXEC($D$2,B38:C38),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G38" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H38" s="26"/>
+      <c r="I38" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" s="22" t="b" cm="1">
+        <f t="array" ref="J38">INDEX(_xll.DUCKDB.EXEC($H$2,B38:C38),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K38" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>38</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" s="26"/>
+      <c r="E39" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="25" t="str" cm="1">
+        <f t="array" ref="F39">INDEX(_xll.DUCKDB.EXEC($D$2,B39:C39),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G39" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H39" s="26"/>
+      <c r="I39" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" s="22" t="b" cm="1">
+        <f t="array" ref="J39">INDEX(_xll.DUCKDB.EXEC($H$2,B39:C39),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>39</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="26"/>
+      <c r="E40" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" s="25" t="str" cm="1">
+        <f t="array" ref="F40">INDEX(_xll.DUCKDB.EXEC($D$2,B40:C40),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G40" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H40" s="26"/>
+      <c r="I40" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" s="22" t="b" cm="1">
+        <f t="array" ref="J40">INDEX(_xll.DUCKDB.EXEC($H$2,B40:C40),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K40" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>40</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D41" s="26"/>
+      <c r="E41" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" s="25" t="str" cm="1">
+        <f t="array" ref="F41">INDEX(_xll.DUCKDB.EXEC($D$2,B41:C41),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G41" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H41" s="26"/>
+      <c r="I41" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" s="22" t="b" cm="1">
+        <f t="array" ref="J41">INDEX(_xll.DUCKDB.EXEC($H$2,B41:C41),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>41</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42" s="26"/>
+      <c r="E42" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" s="25" t="str" cm="1">
+        <f t="array" ref="F42">INDEX(_xll.DUCKDB.EXEC($D$2,B42:C42),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G42" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H42" s="26"/>
+      <c r="I42" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" s="22" t="b" cm="1">
+        <f t="array" ref="J42">INDEX(_xll.DUCKDB.EXEC($H$2,B42:C42),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K42" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>42</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43" s="26"/>
+      <c r="E43" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="25" t="str" cm="1">
+        <f t="array" ref="F43">INDEX(_xll.DUCKDB.EXEC($D$2,B43:C43),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G43" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H43" s="26"/>
+      <c r="I43" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" s="22" t="b" cm="1">
+        <f t="array" ref="J43">INDEX(_xll.DUCKDB.EXEC($H$2,B43:C43),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>43</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="26"/>
+      <c r="E44" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="25" t="str" cm="1">
+        <f t="array" ref="F44">INDEX(_xll.DUCKDB.EXEC($D$2,B44:C44),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G44" s="25" t="str">
+        <f t="shared" ref="G44:G55" si="29">IF(E44=F44,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H44" s="26"/>
+      <c r="I44" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" s="22" t="b" cm="1">
+        <f t="array" ref="J44">INDEX(_xll.DUCKDB.EXEC($H$2,B44:C44),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K44" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>44</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D45" s="26"/>
+      <c r="E45" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="25" t="str" cm="1">
+        <f t="array" ref="F45">INDEX(_xll.DUCKDB.EXEC($D$2,B45:C45),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G45" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v>PASS</v>
+      </c>
+      <c r="H45" s="26"/>
+      <c r="I45" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" s="22" t="b" cm="1">
+        <f t="array" ref="J45">INDEX(_xll.DUCKDB.EXEC($H$2,B45:C45),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>45</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D46" s="26"/>
+      <c r="E46" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" s="25" t="str" cm="1">
+        <f t="array" ref="F46">INDEX(_xll.DUCKDB.EXEC($D$2,B46:C46),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G46" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v>PASS</v>
+      </c>
+      <c r="H46" s="26"/>
+      <c r="I46" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" s="22" t="b" cm="1">
+        <f t="array" ref="J46">INDEX(_xll.DUCKDB.EXEC($H$2,B46:C46),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K46" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="25">
+        <v>46</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" s="26"/>
+      <c r="E47" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="25" t="str" cm="1">
+        <f t="array" ref="F47">INDEX(_xll.DUCKDB.EXEC($D$2,B47:C47),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G47" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v>PASS</v>
+      </c>
+      <c r="H47" s="26"/>
+      <c r="I47" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" s="22" t="b" cm="1">
+        <f t="array" ref="J47">INDEX(_xll.DUCKDB.EXEC($H$2,B47:C47),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="25">
+        <v>47</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="D48" s="26"/>
+      <c r="E48" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="25" t="str" cm="1">
+        <f t="array" ref="F48">INDEX(_xll.DUCKDB.EXEC($D$2,B48:C48),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G48" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v>PASS</v>
+      </c>
+      <c r="H48" s="26"/>
+      <c r="I48" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" s="22" t="b" cm="1">
+        <f t="array" ref="J48">INDEX(_xll.DUCKDB.EXEC($H$2,B48:C48),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K48" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="25">
+        <v>48</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="26"/>
+      <c r="E49" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" s="25" t="str" cm="1">
+        <f t="array" ref="F49">INDEX(_xll.DUCKDB.EXEC($D$2,B49:C49),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G49" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v>PASS</v>
+      </c>
+      <c r="H49" s="26"/>
+      <c r="I49" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" s="22" t="b" cm="1">
+        <f t="array" ref="J49">INDEX(_xll.DUCKDB.EXEC($H$2,B49:C49),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="25">
+        <v>49</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="D50" s="26"/>
+      <c r="E50" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" s="25" t="str" cm="1">
+        <f t="array" ref="F50">INDEX(_xll.DUCKDB.EXEC($D$2,B50:C50),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G50" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v>PASS</v>
+      </c>
+      <c r="H50" s="26"/>
+      <c r="I50" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" s="22" t="b" cm="1">
+        <f t="array" ref="J50">INDEX(_xll.DUCKDB.EXEC($H$2,B50:C50),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K50" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="25">
+        <v>50</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D51" s="26"/>
+      <c r="E51" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" s="25" t="str" cm="1">
+        <f t="array" ref="F51">INDEX(_xll.DUCKDB.EXEC($D$2,B51:C51),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G51" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v>PASS</v>
+      </c>
+      <c r="H51" s="26"/>
+      <c r="I51" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" s="22" t="b" cm="1">
+        <f t="array" ref="J51">INDEX(_xll.DUCKDB.EXEC($H$2,B51:C51),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="25">
+        <v>51</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D52" s="26"/>
+      <c r="E52" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F52" s="25" t="str" cm="1">
+        <f t="array" ref="F52">INDEX(_xll.DUCKDB.EXEC($D$2,B52:C52),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G52" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v>PASS</v>
+      </c>
+      <c r="H52" s="26"/>
+      <c r="I52" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" s="22" t="b" cm="1">
+        <f t="array" ref="J52">INDEX(_xll.DUCKDB.EXEC($H$2,B52:C52),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K52" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="25">
+        <v>52</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D53" s="26"/>
+      <c r="E53" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" s="25" t="str" cm="1">
+        <f t="array" ref="F53">INDEX(_xll.DUCKDB.EXEC($D$2,B53:C53),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G53" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v>PASS</v>
+      </c>
+      <c r="H53" s="26"/>
+      <c r="I53" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" s="22" t="b" cm="1">
+        <f t="array" ref="J53">INDEX(_xll.DUCKDB.EXEC($H$2,B53:C53),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="25">
+        <v>53</v>
+      </c>
+      <c r="B54" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D54" s="26"/>
+      <c r="E54" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" s="25" t="str" cm="1">
+        <f t="array" ref="F54">INDEX(_xll.DUCKDB.EXEC($D$2,B54:C54),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G54" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v>PASS</v>
+      </c>
+      <c r="H54" s="26"/>
+      <c r="I54" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" s="22" t="b" cm="1">
+        <f t="array" ref="J54">INDEX(_xll.DUCKDB.EXEC($H$2,B54:C54),2)</f>
+        <v>1</v>
+      </c>
+      <c r="K54" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="25">
+        <v>54</v>
+      </c>
+      <c r="B55" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D55" s="26"/>
+      <c r="E55" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="25" t="str" cm="1">
+        <f t="array" ref="F55">INDEX(_xll.DUCKDB.EXEC($D$2,B55:C55),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+      <c r="G55" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v>PASS</v>
+      </c>
+      <c r="H55" s="26"/>
+      <c r="I55" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" s="22" t="b" cm="1">
+        <f t="array" ref="J55">INDEX(_xll.DUCKDB.EXEC($H$2,B55:C55),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="25">
+        <v>55</v>
+      </c>
+      <c r="B56" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="C56" s="22"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="25" t="str" cm="1">
+        <f t="array" ref="F56">INDEX(_xll.DUCKDB.EXEC($D$2,B56:C56),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G56" s="25" t="str">
+        <f t="shared" ref="G56" si="30">IF(E56=F56,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H56" s="26"/>
+      <c r="I56" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J56" s="22" t="e" cm="1">
+        <f t="array" ref="J56">INDEX(_xll.DUCKDB.EXEC($H$2,B56:C56),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K56" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="25">
+        <v>56</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" s="26"/>
+      <c r="E57" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="25" t="str" cm="1">
+        <f t="array" ref="F57">INDEX(_xll.DUCKDB.EXEC($D$2,B57:C57),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G57" s="25" t="str">
+        <f t="shared" ref="G57:G64" si="31">IF(E57=F57,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H57" s="26"/>
+      <c r="I57" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J57" s="22" t="e" cm="1">
+        <f t="array" ref="J57">INDEX(_xll.DUCKDB.EXEC($H$2,B57:C57),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K57" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="25">
+        <v>57</v>
+      </c>
+      <c r="B58" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="D58" s="26"/>
+      <c r="E58" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="25" t="str" cm="1">
+        <f t="array" ref="F58">INDEX(_xll.DUCKDB.EXEC($D$2,B58:C58),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G58" s="25" t="str">
+        <f t="shared" si="31"/>
+        <v>PASS</v>
+      </c>
+      <c r="H58" s="26"/>
+      <c r="I58" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J58" s="22" t="e" cm="1">
+        <f t="array" ref="J58">INDEX(_xll.DUCKDB.EXEC($H$2,B58:C58),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K58" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="25">
+        <v>58</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="D59" s="26"/>
+      <c r="E59" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="25" t="str" cm="1">
+        <f t="array" ref="F59">INDEX(_xll.DUCKDB.EXEC($D$2,B59:C59),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G59" s="25" t="str">
+        <f t="shared" si="31"/>
+        <v>PASS</v>
+      </c>
+      <c r="H59" s="26"/>
+      <c r="I59" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J59" s="22" t="e" cm="1">
+        <f t="array" ref="J59">INDEX(_xll.DUCKDB.EXEC($H$2,B59:C59),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K59" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="25">
+        <v>59</v>
+      </c>
+      <c r="B60" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="D60" s="26"/>
+      <c r="E60" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="25" t="str" cm="1">
+        <f t="array" ref="F60">INDEX(_xll.DUCKDB.EXEC($D$2,B60:C60),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G60" s="25" t="str">
+        <f t="shared" si="31"/>
+        <v>PASS</v>
+      </c>
+      <c r="H60" s="26"/>
+      <c r="I60" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J60" s="22" t="e" cm="1">
+        <f t="array" ref="J60">INDEX(_xll.DUCKDB.EXEC($H$2,B60:C60),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K60" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="25">
+        <v>60</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D61" s="26"/>
+      <c r="E61" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="25" t="str" cm="1">
+        <f t="array" ref="F61">INDEX(_xll.DUCKDB.EXEC($D$2,B61:C61),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G61" s="25" t="str">
+        <f t="shared" si="31"/>
+        <v>PASS</v>
+      </c>
+      <c r="H61" s="26"/>
+      <c r="I61" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J61" s="22" t="e" cm="1">
+        <f t="array" ref="J61">INDEX(_xll.DUCKDB.EXEC($H$2,B61:C61),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K61" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="25">
+        <v>61</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D62" s="26"/>
+      <c r="E62" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="25" t="str" cm="1">
+        <f t="array" ref="F62">INDEX(_xll.DUCKDB.EXEC($D$2,B62:C62),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G62" s="25" t="str">
+        <f t="shared" si="31"/>
+        <v>PASS</v>
+      </c>
+      <c r="H62" s="26"/>
+      <c r="I62" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J62" s="22" t="e" cm="1">
+        <f t="array" ref="J62">INDEX(_xll.DUCKDB.EXEC($H$2,B62:C62),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K62" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="25">
+        <v>62</v>
+      </c>
+      <c r="B63" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C63" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D63" s="26"/>
+      <c r="E63" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="25" t="str" cm="1">
+        <f t="array" ref="F63">INDEX(_xll.DUCKDB.EXEC($D$2,B63:C63),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G63" s="25" t="str">
+        <f t="shared" si="31"/>
+        <v>PASS</v>
+      </c>
+      <c r="H63" s="26"/>
+      <c r="I63" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J63" s="22" t="e" cm="1">
+        <f t="array" ref="J63">INDEX(_xll.DUCKDB.EXEC($H$2,B63:C63),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K63" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="25">
+        <v>63</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D64" s="26"/>
+      <c r="E64" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="25" t="str" cm="1">
+        <f t="array" ref="F64">INDEX(_xll.DUCKDB.EXEC($D$2,B64:C64),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G64" s="25" t="str">
+        <f t="shared" si="31"/>
+        <v>PASS</v>
+      </c>
+      <c r="H64" s="26"/>
+      <c r="I64" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J64" s="22" t="e" cm="1">
+        <f t="array" ref="J64">INDEX(_xll.DUCKDB.EXEC($H$2,B64:C64),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K64" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="25">
+        <v>64</v>
+      </c>
+      <c r="B65" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="C65" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D65" s="26"/>
+      <c r="E65" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="25" t="str" cm="1">
+        <f t="array" ref="F65">INDEX(_xll.DUCKDB.EXEC($D$2,B65:C65),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G65" s="25" t="str">
+        <f t="shared" ref="G65:G68" si="32">IF(E65=F65,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H65" s="26"/>
+      <c r="I65" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J65" s="22" t="e" cm="1">
+        <f t="array" ref="J65">INDEX(_xll.DUCKDB.EXEC($H$2,B65:C65),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K65" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="25">
+        <v>65</v>
+      </c>
+      <c r="B66" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="C66" s="22" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="D66" s="26"/>
+      <c r="E66" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="25" t="str" cm="1">
+        <f t="array" ref="F66">INDEX(_xll.DUCKDB.EXEC($D$2,B66:C66),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G66" s="25" t="str">
+        <f t="shared" si="32"/>
+        <v>PASS</v>
+      </c>
+      <c r="H66" s="26"/>
+      <c r="I66" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J66" s="22" t="e" cm="1">
+        <f t="array" ref="J66">INDEX(_xll.DUCKDB.EXEC($H$2,B66:C66),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K66" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="25">
+        <v>66</v>
+      </c>
+      <c r="B67" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="C67" s="22" t="e">
+        <v>#REF!</v>
+      </c>
+      <c r="D67" s="26"/>
+      <c r="E67" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="25" t="str" cm="1">
+        <f t="array" ref="F67">INDEX(_xll.DUCKDB.EXEC($D$2,B67:C67),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G67" s="25" t="str">
+        <f t="shared" si="32"/>
+        <v>PASS</v>
+      </c>
+      <c r="H67" s="26"/>
+      <c r="I67" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J67" s="22" t="e" cm="1">
+        <f t="array" ref="J67">INDEX(_xll.DUCKDB.EXEC($H$2,B67:C67),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K67" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="25">
+        <v>67</v>
+      </c>
+      <c r="B68" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="C68" s="22" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D68" s="26"/>
+      <c r="E68" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="25" t="str" cm="1">
+        <f t="array" ref="F68">INDEX(_xll.DUCKDB.EXEC($D$2,B68:C68),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G68" s="25" t="str">
+        <f t="shared" si="32"/>
+        <v>PASS</v>
+      </c>
+      <c r="H68" s="26"/>
+      <c r="I68" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J68" s="22" t="e" cm="1">
+        <f t="array" ref="J68">INDEX(_xll.DUCKDB.EXEC($H$2,B68:C68),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K68" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="25">
+        <v>68</v>
+      </c>
+      <c r="B69" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C69" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D69" s="26"/>
+      <c r="E69" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="25" t="str" cm="1">
+        <f t="array" ref="F69">INDEX(_xll.DUCKDB.EXEC($D$2,B69:C69),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G69" s="25" t="str">
+        <f t="shared" ref="G69:G71" si="33">IF(E69=F69,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H69" s="26"/>
+      <c r="I69" s="22" t="str">
+        <f>C69</f>
+        <v>abc</v>
+      </c>
+      <c r="J69" s="22" t="str" cm="1">
+        <f t="array" ref="J69">INDEX(_xll.DUCKDB.EXEC($H$2,B69:C69),2)</f>
+        <v>abc</v>
+      </c>
+      <c r="K69" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="25">
+        <v>69</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="D70" s="26"/>
+      <c r="E70" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="25" t="str" cm="1">
+        <f t="array" ref="F70">INDEX(_xll.DUCKDB.EXEC($D$2,B70:C70),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G70" s="25" t="str">
+        <f t="shared" ref="G70" si="34">IF(E70=F70,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H70" s="26"/>
+      <c r="I70" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J70" s="22" t="e" cm="1">
+        <f t="array" ref="J70">INDEX(_xll.DUCKDB.EXEC($H$2,B70:C70),2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K70" s="25" t="str">
+        <f t="shared" ref="K70" si="35">IF(ISNA(I70),IF(ISNA(J70),"PASS","FAIL"),IFERROR(IF(I70=J70,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="25">
+        <v>70</v>
+      </c>
+      <c r="B71" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="C71" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D71" s="26"/>
+      <c r="E71" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" s="25" t="str" cm="1">
+        <f t="array" ref="F71">INDEX(_xll.DUCKDB.EXEC($D$2,B71:C71),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G71" s="25" t="str">
+        <f t="shared" si="33"/>
+        <v>PASS</v>
+      </c>
+      <c r="H71" s="26"/>
+      <c r="I71" s="22" t="str">
+        <f>C71</f>
+        <v xml:space="preserve">    abc    </v>
+      </c>
+      <c r="J71" s="22" t="str" cm="1">
+        <f t="array" ref="J71">INDEX(_xll.DUCKDB.EXEC($H$2,B71:C71),2)</f>
+        <v xml:space="preserve">    abc    </v>
+      </c>
+      <c r="K71" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="25">
+        <v>71</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C72" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="D72" s="26"/>
+      <c r="E72" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="25" t="str" cm="1">
+        <f t="array" ref="F72">INDEX(_xll.DUCKDB.EXEC($D$2,B72:C72),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G72" s="25" t="str">
+        <f t="shared" ref="G72:G76" si="36">IF(E72=F72,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="H72" s="26"/>
+      <c r="I72" s="22" t="str">
+        <f t="shared" ref="I72:I76" si="37">C72</f>
+        <v>NA</v>
+      </c>
+      <c r="J72" s="22" t="str" cm="1">
+        <f t="array" ref="J72">INDEX(_xll.DUCKDB.EXEC($H$2,B72:C72),2)</f>
+        <v>NA</v>
+      </c>
+      <c r="K72" s="25" t="str">
+        <f t="shared" ref="K72:K76" si="38">IF(ISNA(I72),IF(ISNA(J72),"PASS","FAIL"),IFERROR(IF(I72=J72,"PASS","FAIL"),"FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="25">
+        <v>72</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C73" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="D73" s="26"/>
+      <c r="E73" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" s="25" t="str" cm="1">
+        <f t="array" ref="F73">INDEX(_xll.DUCKDB.EXEC($D$2,B73:C73),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G73" s="25" t="str">
+        <f t="shared" si="36"/>
+        <v>PASS</v>
+      </c>
+      <c r="H73" s="26"/>
+      <c r="I73" s="22" t="str">
+        <f t="shared" si="37"/>
+        <v>NONE</v>
+      </c>
+      <c r="J73" s="22" t="str" cm="1">
+        <f t="array" ref="J73">INDEX(_xll.DUCKDB.EXEC($H$2,B73:C73),2)</f>
+        <v>NONE</v>
+      </c>
+      <c r="K73" s="25" t="str">
+        <f t="shared" si="38"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="25">
+        <v>73</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C74" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="D74" s="26"/>
+      <c r="E74" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" s="25" t="str" cm="1">
+        <f t="array" ref="F74">INDEX(_xll.DUCKDB.EXEC($D$2,B74:C74),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G74" s="25" t="str">
+        <f t="shared" si="36"/>
+        <v>PASS</v>
+      </c>
+      <c r="H74" s="26"/>
+      <c r="I74" s="22" t="str">
+        <f t="shared" si="37"/>
+        <v>NIL</v>
+      </c>
+      <c r="J74" s="22" t="str" cm="1">
+        <f t="array" ref="J74">INDEX(_xll.DUCKDB.EXEC($H$2,B74:C74),2)</f>
+        <v>NIL</v>
+      </c>
+      <c r="K74" s="25" t="str">
+        <f t="shared" si="38"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="25">
+        <v>74</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C75" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="D75" s="26"/>
+      <c r="E75" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" s="25" t="str" cm="1">
+        <f t="array" ref="F75">INDEX(_xll.DUCKDB.EXEC($D$2,B75:C75),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G75" s="25" t="str">
+        <f t="shared" si="36"/>
+        <v>PASS</v>
+      </c>
+      <c r="H75" s="26"/>
+      <c r="I75" s="22" t="str">
+        <f t="shared" si="37"/>
+        <v>INF</v>
+      </c>
+      <c r="J75" s="22" t="str" cm="1">
+        <f t="array" ref="J75">INDEX(_xll.DUCKDB.EXEC($H$2,B75:C75),2)</f>
+        <v>INF</v>
+      </c>
+      <c r="K75" s="25" t="str">
+        <f t="shared" si="38"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="25">
+        <v>75</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C76" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="D76" s="26"/>
+      <c r="E76" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="25" t="str" cm="1">
+        <f t="array" ref="F76">INDEX(_xll.DUCKDB.EXEC($D$2,B76:C76),2)</f>
+        <v>VARCHAR</v>
+      </c>
+      <c r="G76" s="25" t="str">
+        <f t="shared" si="36"/>
+        <v>PASS</v>
+      </c>
+      <c r="H76" s="26"/>
+      <c r="I76" s="22" t="str">
+        <f t="shared" si="37"/>
+        <v>NaN</v>
+      </c>
+      <c r="J76" s="22" t="str" cm="1">
+        <f t="array" ref="J76">INDEX(_xll.DUCKDB.EXEC($H$2,B76:C76),2)</f>
+        <v>NaN</v>
+      </c>
+      <c r="K76" s="25" t="str">
+        <f t="shared" si="38"/>
+        <v>PASS</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:D76"/>
+    <mergeCell ref="H2:H76"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G2:G76 K2:K76">
+    <cfRule type="cellIs" dxfId="1" priority="1" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{024A1C93-13C0-441A-AD81-7C8033CD328B}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="24">
+        <v>2</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="E2" s="24" t="str" cm="1">
+        <f t="array" ref="E2">INDEX(_xll.DUCKDB.EXEC($D$2,B2:B3,C2),2)</f>
+        <v>INTEGER</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="23"/>
+      <c r="B3" s="22">
+        <v>1</v>
+      </c>
+      <c r="C3" s="24"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="24"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="22">
+        <v>1</v>
+      </c>
+      <c r="C4" s="24">
+        <v>2</v>
+      </c>
+      <c r="D4" s="22"/>
+      <c r="E4" s="24" t="str" cm="1">
+        <f t="array" ref="E4">INDEX(_xll.DUCKDB.EXEC($D$2,B4:B5,C4),2)</f>
+        <v>INTEGER</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="23"/>
+      <c r="B5" s="22">
+        <v>2</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="24"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="22">
+        <v>1</v>
+      </c>
+      <c r="C6" s="24">
+        <v>2</v>
+      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="24" t="str" cm="1">
+        <f t="array" ref="E6">INDEX(_xll.DUCKDB.EXEC($D$2,B6:B7,C6),2)</f>
+        <v>INTEGER</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="23"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="24"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="22"/>
+      <c r="C8" s="24">
+        <v>2</v>
+      </c>
+      <c r="D8" s="22"/>
+      <c r="E8" s="24" t="str" cm="1">
+        <f t="array" ref="E8">INDEX(_xll.DUCKDB.EXEC($D$2,B8:B9,C8),2)</f>
+        <v>DOUBLE</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="23"/>
+      <c r="B9" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="C9" s="24"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="24"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="C10" s="24">
+        <v>2</v>
+      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="24" t="str" cm="1">
+        <f t="array" ref="E10">INDEX(_xll.DUCKDB.EXEC($D$2,B10:B11,C10),2)</f>
+        <v>DOUBLE</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="23"/>
+      <c r="B11" s="22">
+        <v>1.3</v>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="24"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="C12" s="24">
+        <v>2</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="24" t="str" cm="1">
+        <f t="array" ref="E12">INDEX(_xll.DUCKDB.EXEC($D$2,B12:B13,C12),2)</f>
+        <v>DOUBLE</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="23"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="24"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" s="22"/>
+      <c r="C14" s="24">
+        <v>2</v>
+      </c>
+      <c r="D14" s="22"/>
+      <c r="E14" s="24" t="str" cm="1">
+        <f t="array" ref="E14">INDEX(_xll.DUCKDB.EXEC($D$2,B14:B15,C14),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="23"/>
+      <c r="B15" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15" s="24"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="24"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="C16" s="24">
+        <v>2</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="24" t="str" cm="1">
+        <f t="array" ref="E16">INDEX(_xll.DUCKDB.EXEC($D$2,B16:B17,C16),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="23"/>
+      <c r="B17" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="24"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="24"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="C18" s="24">
+        <v>2</v>
+      </c>
+      <c r="D18" s="22"/>
+      <c r="E18" s="24" t="str" cm="1">
+        <f t="array" ref="E18">INDEX(_xll.DUCKDB.EXEC($D$2,B18:B19,C18),2)</f>
+        <v>BOOLEAN</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="23"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="24"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B20" s="22"/>
+      <c r="C20" s="24">
+        <v>2</v>
+      </c>
+      <c r="D20" s="22"/>
+      <c r="E20" s="24" t="str" cm="1">
+        <f t="array" ref="E20">INDEX(_xll.DUCKDB.EXEC($D$2,B20:B21,C20),2)</f>
+        <v>VARCHAR</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="23"/>
+      <c r="B21" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="24"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="24"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="24">
+        <v>2</v>
+      </c>
+      <c r="D22" s="22"/>
+      <c r="E22" s="24" t="str" cm="1">
+        <f t="array" ref="E22">INDEX(_xll.DUCKDB.EXEC($D$2,B22:B23,C22),2)</f>
+        <v>VARCHAR</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="23"/>
+      <c r="B23" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C23" s="24"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="24"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="24">
+        <v>2</v>
+      </c>
+      <c r="D24" s="22"/>
+      <c r="E24" s="24" t="str" cm="1">
+        <f t="array" ref="E24">INDEX(_xll.DUCKDB.EXEC($D$2,B24:B25,C24),2)</f>
+        <v>VARCHAR</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="23"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751A3194-2367-4BAA-BC32-C926CD8293A5}">
   <dimension ref="A1:G106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1361,22 +5076,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1387,7 +5102,7 @@
         <v>1.2</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F2" t="e">
         <f>1/0</f>
@@ -1410,7 +5125,7 @@
         <v>1.3</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1418,10 +5133,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1460,8 +5175,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
-        <v>61</v>
+      <c r="B10" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1587,10 +5302,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1646,8 +5361,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
-        <v>61</v>
+      <c r="B23" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1672,8 +5387,8 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>65</v>
+      <c r="A25" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="B25" t="str">
         <v>NUMBER_1</v>
@@ -1776,10 +5491,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1852,8 +5567,8 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="7" t="s">
-        <v>61</v>
+      <c r="B37" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1878,7 +5593,7 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
+      <c r="A39" s="6"/>
       <c r="B39" t="str">
         <v>NUMBER_1</v>
       </c>
@@ -1899,8 +5614,8 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
-        <v>66</v>
+      <c r="A40" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="B40" t="str">
         <v>NUMBER_2</v>
@@ -1983,10 +5698,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>68</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1997,10 +5712,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>70</v>
+        <v>61</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2126,10 +5841,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>71</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>72</v>
+        <v>63</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2255,10 +5970,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>89</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>90</v>
+        <v>81</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2349,10 +6064,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D71" t="b">
         <v>1</v>
@@ -2388,21 +6103,21 @@
         <v>1.3</v>
       </c>
       <c r="C74" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
-      <c r="E74" s="9">
+      <c r="E74" s="7">
         <v>46387</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>94</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>95</v>
+        <v>86</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2415,10 +6130,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>96</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>97</v>
+        <v>88</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2480,13 +6195,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C85" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2510,16 +6225,16 @@
         <v>1.3</v>
       </c>
       <c r="C88" t="s">
-        <v>57</v>
-      </c>
-      <c r="E88" s="9"/>
+        <v>49</v>
+      </c>
+      <c r="E88" s="7"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>94</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>95</v>
+        <v>86</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2532,10 +6247,10 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>96</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>97</v>
+        <v>88</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2573,10 +6288,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>109</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>110</v>
+        <v>101</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2587,10 +6302,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>111</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>112</v>
+        <v>103</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2632,7 +6347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A836AEC-DD0A-4797-B454-6E20C81CB53A}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2646,40 +6361,40 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="9">
+      <c r="B2" s="7">
         <v>46387</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="8">
         <v>0.39635416666666667</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="4">
         <v>46387.396354166667</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>106</v>
+        <v>96</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B5" t="str" cm="1">
         <f t="array" ref="B5:D6">_xll.DUCKDB.EXEC(B4,B1:D2)</f>
@@ -2693,27 +6408,27 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="str">
+      <c r="B6" s="7" t="str">
         <v>2026-12-31</v>
       </c>
-      <c r="C6" s="11" t="str">
+      <c r="C6" s="9" t="str">
         <v>09:30:45</v>
       </c>
-      <c r="D6" s="6" t="str">
+      <c r="D6" s="4" t="str">
         <v>2026-12-31 09:30:45</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>107</v>
+        <v>96</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B9" t="str" cm="1">
         <f t="array" ref="B9:D10">_xll.DUCKDB.EXEC(B8,A1:D2)</f>
@@ -2727,7 +6442,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="str">
+      <c r="B10" s="7" t="str">
         <v>2026-12-31</v>
       </c>
       <c r="C10" t="str">
@@ -2742,7 +6457,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66184BE2-F564-4E42-8CE8-BFC8C65E358F}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2753,15 +6468,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="7" t="s">
         <v>78</v>
       </c>
+      <c r="B1" s="5" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
-        <v>79</v>
+      <c r="B2" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2777,10 +6492,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>84</v>
+        <v>92</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2796,15 +6511,15 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>78</v>
+        <v>95</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
-        <v>79</v>
+      <c r="B11" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2823,7 +6538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D42E5724-67A3-4259-906B-37F92D367239}">
   <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2834,15 +6549,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B1">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
-        <v>80</v>
+      <c r="B2" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2858,15 +6573,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B6">
         <v>1.2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
-        <v>80</v>
+      <c r="B7" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2882,15 +6597,15 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
-        <v>80</v>
+      <c r="B11" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2906,15 +6621,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B15" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
-        <v>80</v>
+      <c r="B16" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2930,12 +6645,12 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>80</v>
+      <c r="B21" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2951,7 +6666,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B25" t="e">
         <f>1/0</f>
@@ -2959,8 +6674,8 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
-        <v>80</v>
+      <c r="B26" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2974,7 +6689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C8C1CB2-5A89-4EE9-B7B8-26D912A856F1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2985,7 +6700,7 @@
     <row r="1" spans="1:1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" ref="A1">_xll.DUCKDB.INFO()</f>
-        <v>Add-in version: v1.5.0
+        <v>Add-in version: v1.5.1
 DuckDB version: v1.5.5</v>
       </c>
     </row>
@@ -2994,81 +6709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE0166A-6705-4BE6-BC5D-3DDB4234D0EA}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:B3">_xll.DUCKDB.EXEC.ASYNC(B1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5:B6">_xll.DUCKDB.EXECX.ASYNC(,B1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8:B9">_xll.DUCKDB.EXECA.ASYNC(,B1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" t="str" cm="1">
-        <f t="array" ref="B11:B12">_xll.DUCKDB.EXECAX.ASYNC(,,B1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65879F08-AA5E-452D-9515-58424370F18B}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3077,8 +6718,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>88</v>
+      <c r="A1" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">

--- a/examples/test_cases.xlsx
+++ b/examples/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\src\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C776F617-B8CA-40CE-ACFA-DAE5AF8DE0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DBFA4A-07B2-4C30-B183-275F3CE3EED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{16A29E05-5294-4C93-91C1-6C3B8F27AE65}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="262">
   <si>
     <t>TINYINT</t>
   </si>
@@ -1117,23 +1117,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1144,20 +1147,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1170,6 +1164,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2994,8 +2994,8 @@
     <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" ref="A1">_xll.DUCKDB.INFO()</f>
-        <v>Add-in version: v1.6.0
-DuckDB version: v1.5.5</v>
+        <v>Add-in version: v1.7.0
+DuckDB version: v1.5.6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -4175,7 +4175,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596BDC2F-78D8-495C-B354-FBB81CDDC292}">
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
@@ -4191,7 +4191,7 @@
     <col min="11" max="11" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>252</v>
       </c>
@@ -4226,7 +4226,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -4265,8 +4265,12 @@
         <f>IF(ISNA(I2),IF(ISNA(J2),"PASS","FAIL"),IFERROR(IF(I2=J2,"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N2" t="str" cm="1">
+        <f t="array" ref="N2:N3">_xll.DUCKDB.EXEC($H$2,B2:C2)</f>
+        <v>column_1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -4301,8 +4305,11 @@
         <f>IF(ISNA(I3),IF(ISNA(J3),"PASS","FAIL"),IFERROR(IF(I3=J3,"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -4337,8 +4344,11 @@
         <f t="shared" ref="K4:K63" si="1">IF(ISNA(I4),IF(ISNA(J4),"PASS","FAIL"),IFERROR(IF(I4=J4,"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -4374,7 +4384,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -4408,8 +4418,12 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N6" t="str" cm="1">
+        <f t="array" ref="N6:N7">_xll.DUCKDB.EXEC(N4,B2:C2)</f>
+        <v>column_1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -4443,8 +4457,11 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -4479,7 +4496,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -4514,7 +4531,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -4549,7 +4566,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -4584,7 +4601,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -4619,7 +4636,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -4654,7 +4671,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -4689,7 +4706,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -4724,7 +4741,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -6731,13 +6748,13 @@
       <c r="A2" s="51">
         <v>1</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="53" t="s">
         <v>104</v>
       </c>
       <c r="C2" s="8">
         <v>1</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="62" t="s">
         <v>242</v>
       </c>
       <c r="E2" s="51" t="s">
@@ -6747,16 +6764,16 @@
         <f t="array" ref="F2">INDEX(_xll.DUCKDB.EXEC($D$2,C2:C3,#REF!),2)</f>
         <v>INTEGER</v>
       </c>
-      <c r="G2" s="53" t="str">
+      <c r="G2" s="54" t="str">
         <f>IF(E2=F2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="51"/>
-      <c r="B3" s="57"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="61"/>
+      <c r="D3" s="62"/>
       <c r="E3" s="51"/>
       <c r="F3" s="51"/>
       <c r="G3" s="55"/>
@@ -6765,11 +6782,11 @@
       <c r="A4" s="51">
         <v>2</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="53" t="s">
         <v>104</v>
       </c>
       <c r="C4" s="8"/>
-      <c r="D4" s="61"/>
+      <c r="D4" s="62"/>
       <c r="E4" s="51" t="s">
         <v>4</v>
       </c>
@@ -6777,67 +6794,67 @@
         <f t="array" ref="F4">INDEX(_xll.DUCKDB.EXEC($D$2,C4:C5,#REF!),2)</f>
         <v>INTEGER</v>
       </c>
-      <c r="G4" s="53" t="str">
+      <c r="G4" s="54" t="str">
         <f>IF(E4=F4,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="51"/>
-      <c r="B5" s="57"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="27">
         <v>1</v>
       </c>
-      <c r="D5" s="61"/>
+      <c r="D5" s="62"/>
       <c r="E5" s="51"/>
       <c r="F5" s="51"/>
       <c r="G5" s="55"/>
     </row>
     <row r="6" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="56">
+      <c r="A6" s="64">
         <v>3</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="63" t="s">
         <v>104</v>
       </c>
       <c r="C6" s="27">
         <v>1</v>
       </c>
-      <c r="D6" s="61"/>
-      <c r="E6" s="56" t="s">
+      <c r="D6" s="62"/>
+      <c r="E6" s="64" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="51" t="str" cm="1">
         <f t="array" ref="F6">INDEX(_xll.DUCKDB.EXEC($D$2,C6:C7,#REF!),2)</f>
         <v>INTEGER</v>
       </c>
-      <c r="G6" s="59" t="str">
+      <c r="G6" s="60" t="str">
         <f>IF(E6=F6,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="56"/>
-      <c r="B7" s="58"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="63"/>
       <c r="C7" s="27">
         <v>2</v>
       </c>
-      <c r="D7" s="61"/>
-      <c r="E7" s="56"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="64"/>
       <c r="F7" s="51"/>
-      <c r="G7" s="60"/>
+      <c r="G7" s="61"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="51">
         <v>4</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="53" t="s">
         <v>107</v>
       </c>
       <c r="C8" s="8">
         <v>1.2</v>
       </c>
-      <c r="D8" s="61"/>
+      <c r="D8" s="62"/>
       <c r="E8" s="51" t="s">
         <v>12</v>
       </c>
@@ -6845,16 +6862,16 @@
         <f t="array" ref="F8">INDEX(_xll.DUCKDB.EXEC($D$2,C8:C9,#REF!),2)</f>
         <v>DOUBLE</v>
       </c>
-      <c r="G8" s="53" t="str">
+      <c r="G8" s="54" t="str">
         <f>IF(E8=F8,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="51"/>
-      <c r="B9" s="57"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="61"/>
+      <c r="D9" s="62"/>
       <c r="E9" s="51"/>
       <c r="F9" s="51"/>
       <c r="G9" s="55"/>
@@ -6863,11 +6880,11 @@
       <c r="A10" s="51">
         <v>5</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="53" t="s">
         <v>107</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="61"/>
+      <c r="D10" s="62"/>
       <c r="E10" s="51" t="s">
         <v>12</v>
       </c>
@@ -6875,18 +6892,18 @@
         <f t="array" ref="F10">INDEX(_xll.DUCKDB.EXEC($D$2,C10:C11,#REF!),2)</f>
         <v>DOUBLE</v>
       </c>
-      <c r="G10" s="53" t="str">
+      <c r="G10" s="54" t="str">
         <f>IF(E10=F10,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="51"/>
-      <c r="B11" s="57"/>
+      <c r="B11" s="53"/>
       <c r="C11" s="8">
         <v>1.2</v>
       </c>
-      <c r="D11" s="61"/>
+      <c r="D11" s="62"/>
       <c r="E11" s="51"/>
       <c r="F11" s="51"/>
       <c r="G11" s="55"/>
@@ -6895,13 +6912,13 @@
       <c r="A12" s="51">
         <v>6</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="53" t="s">
         <v>107</v>
       </c>
       <c r="C12" s="8">
         <v>1.2</v>
       </c>
-      <c r="D12" s="61"/>
+      <c r="D12" s="62"/>
       <c r="E12" s="51" t="s">
         <v>12</v>
       </c>
@@ -6909,18 +6926,18 @@
         <f t="array" ref="F12">INDEX(_xll.DUCKDB.EXEC($D$2,C12:C13,#REF!),2)</f>
         <v>DOUBLE</v>
       </c>
-      <c r="G12" s="53" t="str">
+      <c r="G12" s="54" t="str">
         <f>IF(E12=F12,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="51"/>
-      <c r="B13" s="57"/>
+      <c r="B13" s="53"/>
       <c r="C13" s="8">
         <v>3.4</v>
       </c>
-      <c r="D13" s="61"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="51"/>
       <c r="F13" s="51"/>
       <c r="G13" s="55"/>
@@ -6929,13 +6946,13 @@
       <c r="A14" s="51">
         <v>7</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="53" t="s">
         <v>163</v>
       </c>
       <c r="C14" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="51" t="s">
         <v>7</v>
       </c>
@@ -6943,16 +6960,16 @@
         <f t="array" ref="F14">INDEX(_xll.DUCKDB.EXEC($D$2,C14:C15,#REF!),2)</f>
         <v>BOOLEAN</v>
       </c>
-      <c r="G14" s="53" t="str">
+      <c r="G14" s="54" t="str">
         <f>IF(E14=F14,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="51"/>
-      <c r="B15" s="57"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="61"/>
+      <c r="D15" s="62"/>
       <c r="E15" s="51"/>
       <c r="F15" s="51"/>
       <c r="G15" s="55"/>
@@ -6961,13 +6978,13 @@
       <c r="A16" s="51">
         <v>8</v>
       </c>
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="53" t="s">
         <v>163</v>
       </c>
       <c r="C16" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="51" t="s">
         <v>7</v>
       </c>
@@ -6975,16 +6992,16 @@
         <f t="array" ref="F16">INDEX(_xll.DUCKDB.EXEC($D$2,C16:C17,#REF!),2)</f>
         <v>BOOLEAN</v>
       </c>
-      <c r="G16" s="53" t="str">
+      <c r="G16" s="54" t="str">
         <f>IF(E16=F16,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="51"/>
-      <c r="B17" s="57"/>
+      <c r="B17" s="53"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="61"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="51"/>
       <c r="F17" s="51"/>
       <c r="G17" s="55"/>
@@ -6993,13 +7010,13 @@
       <c r="A18" s="51">
         <v>9</v>
       </c>
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="53" t="s">
         <v>163</v>
       </c>
       <c r="C18" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="D18" s="61"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="51" t="s">
         <v>7</v>
       </c>
@@ -7007,18 +7024,18 @@
         <f t="array" ref="F18">INDEX(_xll.DUCKDB.EXEC($D$2,C18:C19,#REF!),2)</f>
         <v>BOOLEAN</v>
       </c>
-      <c r="G18" s="53" t="str">
+      <c r="G18" s="54" t="str">
         <f>IF(E18=F18,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="51"/>
-      <c r="B19" s="57"/>
+      <c r="B19" s="53"/>
       <c r="C19" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D19" s="61"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="51"/>
       <c r="F19" s="51"/>
       <c r="G19" s="55"/>
@@ -7027,13 +7044,13 @@
       <c r="A20" s="51">
         <v>10</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="53" t="s">
         <v>163</v>
       </c>
       <c r="C20" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="D20" s="61"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="51" t="s">
         <v>7</v>
       </c>
@@ -7041,18 +7058,18 @@
         <f t="array" ref="F20">INDEX(_xll.DUCKDB.EXEC($D$2,C20:C21,#REF!),2)</f>
         <v>BOOLEAN</v>
       </c>
-      <c r="G20" s="53" t="str">
+      <c r="G20" s="54" t="str">
         <f>IF(E20=F20,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="51"/>
-      <c r="B21" s="57"/>
+      <c r="B21" s="53"/>
       <c r="C21" s="25">
         <v>1</v>
       </c>
-      <c r="D21" s="61"/>
+      <c r="D21" s="62"/>
       <c r="E21" s="51"/>
       <c r="F21" s="51"/>
       <c r="G21" s="55"/>
@@ -7061,13 +7078,13 @@
       <c r="A22" s="51">
         <v>11</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="53" t="s">
         <v>163</v>
       </c>
       <c r="C22" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D22" s="61"/>
+      <c r="D22" s="62"/>
       <c r="E22" s="51" t="s">
         <v>7</v>
       </c>
@@ -7075,18 +7092,18 @@
         <f t="array" ref="F22">INDEX(_xll.DUCKDB.EXEC($D$2,C22:C23,#REF!),2)</f>
         <v>BOOLEAN</v>
       </c>
-      <c r="G22" s="53" t="str">
+      <c r="G22" s="54" t="str">
         <f>IF(E22=F22,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="51"/>
-      <c r="B23" s="57"/>
+      <c r="B23" s="53"/>
       <c r="C23" s="25">
         <v>0</v>
       </c>
-      <c r="D23" s="61"/>
+      <c r="D23" s="62"/>
       <c r="E23" s="51"/>
       <c r="F23" s="51"/>
       <c r="G23" s="55"/>
@@ -7095,13 +7112,13 @@
       <c r="A24" s="51">
         <v>12</v>
       </c>
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="53" t="s">
         <v>164</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="61"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="51" t="s">
         <v>8</v>
       </c>
@@ -7109,16 +7126,16 @@
         <f t="array" ref="F24">INDEX(_xll.DUCKDB.EXEC($D$2,C24:C25,#REF!),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G24" s="53" t="str">
+      <c r="G24" s="54" t="str">
         <f>IF(E24=F24,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="51"/>
-      <c r="B25" s="57"/>
+      <c r="B25" s="53"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="61"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="51"/>
       <c r="F25" s="51"/>
       <c r="G25" s="55"/>
@@ -7127,11 +7144,11 @@
       <c r="A26" s="51">
         <v>13</v>
       </c>
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="53" t="s">
         <v>164</v>
       </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="61"/>
+      <c r="D26" s="62"/>
       <c r="E26" s="51" t="s">
         <v>8</v>
       </c>
@@ -7139,18 +7156,18 @@
         <f t="array" ref="F26">INDEX(_xll.DUCKDB.EXEC($D$2,C26:C27,#REF!),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G26" s="53" t="str">
+      <c r="G26" s="54" t="str">
         <f>IF(E26=F26,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="51"/>
-      <c r="B27" s="57"/>
+      <c r="B27" s="53"/>
       <c r="C27" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="61"/>
+      <c r="D27" s="62"/>
       <c r="E27" s="51"/>
       <c r="F27" s="51"/>
       <c r="G27" s="55"/>
@@ -7159,13 +7176,13 @@
       <c r="A28" s="51">
         <v>14</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="53" t="s">
         <v>164</v>
       </c>
       <c r="C28" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="61"/>
+      <c r="D28" s="62"/>
       <c r="E28" s="51" t="s">
         <v>8</v>
       </c>
@@ -7173,33 +7190,33 @@
         <f t="array" ref="F28">INDEX(_xll.DUCKDB.EXEC($D$2,C28:C29,#REF!),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G28" s="59" t="str">
+      <c r="G28" s="60" t="str">
         <f>IF(E28=F28,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="51"/>
-      <c r="B29" s="57"/>
+      <c r="B29" s="53"/>
       <c r="C29" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="61"/>
+      <c r="D29" s="62"/>
       <c r="E29" s="51"/>
       <c r="F29" s="51"/>
-      <c r="G29" s="60"/>
+      <c r="G29" s="61"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="51">
         <v>15</v>
       </c>
-      <c r="B30" s="57" t="s">
+      <c r="B30" s="53" t="s">
         <v>168</v>
       </c>
       <c r="C30" s="8">
         <v>1</v>
       </c>
-      <c r="D30" s="61"/>
+      <c r="D30" s="62"/>
       <c r="E30" s="51" t="s">
         <v>12</v>
       </c>
@@ -7207,123 +7224,123 @@
         <f t="array" ref="F30">INDEX(_xll.DUCKDB.EXEC($D$2,C30:C31,#REF!),2)</f>
         <v>DOUBLE</v>
       </c>
-      <c r="G30" s="53" t="str">
+      <c r="G30" s="54" t="str">
         <f>IF(E30=F30,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="51"/>
-      <c r="B31" s="57"/>
+      <c r="B31" s="53"/>
       <c r="C31" s="10">
         <v>1.2</v>
       </c>
-      <c r="D31" s="61"/>
+      <c r="D31" s="62"/>
       <c r="E31" s="51"/>
       <c r="F31" s="51"/>
       <c r="G31" s="55"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="53">
+      <c r="A32" s="54">
         <v>16</v>
       </c>
-      <c r="B32" s="62" t="s">
+      <c r="B32" s="56" t="s">
         <v>170</v>
       </c>
       <c r="C32" s="8">
         <v>1</v>
       </c>
-      <c r="D32" s="61"/>
-      <c r="E32" s="53" t="s">
+      <c r="D32" s="62"/>
+      <c r="E32" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="53" t="str" cm="1">
+      <c r="F32" s="54" t="str" cm="1">
         <f t="array" ref="F32">INDEX(_xll.DUCKDB.EXEC($D$2,C32:C34,#REF!),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G32" s="53" t="str">
+      <c r="G32" s="54" t="str">
         <f>IF(E32=F32,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="54"/>
-      <c r="B33" s="63"/>
+      <c r="A33" s="59"/>
+      <c r="B33" s="57"/>
       <c r="C33" s="10">
         <v>1.2</v>
       </c>
-      <c r="D33" s="61"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="59"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="55"/>
-      <c r="B34" s="64"/>
+      <c r="B34" s="58"/>
       <c r="C34" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="61"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="55"/>
       <c r="F34" s="55"/>
-      <c r="G34" s="54"/>
+      <c r="G34" s="59"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="53">
+      <c r="A35" s="54">
         <v>17</v>
       </c>
-      <c r="B35" s="62" t="s">
+      <c r="B35" s="56" t="s">
         <v>170</v>
       </c>
       <c r="C35" s="8">
         <v>1</v>
       </c>
-      <c r="D35" s="61"/>
-      <c r="E35" s="53" t="s">
+      <c r="D35" s="62"/>
+      <c r="E35" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="53" t="str" cm="1">
+      <c r="F35" s="54" t="str" cm="1">
         <f t="array" ref="F35">INDEX(_xll.DUCKDB.EXEC($D$2,C35:C37,#REF!),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G35" s="53" t="str">
+      <c r="G35" s="54" t="str">
         <f>IF(E35=F35,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="54"/>
-      <c r="B36" s="63"/>
+      <c r="A36" s="59"/>
+      <c r="B36" s="57"/>
       <c r="C36" s="10">
         <v>1.2</v>
       </c>
-      <c r="D36" s="61"/>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
+      <c r="D36" s="62"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="55"/>
-      <c r="B37" s="64"/>
+      <c r="B37" s="58"/>
       <c r="C37" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="D37" s="61"/>
+      <c r="D37" s="62"/>
       <c r="E37" s="55"/>
       <c r="F37" s="55"/>
-      <c r="G37" s="54"/>
+      <c r="G37" s="59"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="51">
         <v>18</v>
       </c>
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="53" t="s">
         <v>169</v>
       </c>
       <c r="C38" s="8">
         <v>1</v>
       </c>
-      <c r="D38" s="61"/>
+      <c r="D38" s="62"/>
       <c r="E38" s="51" t="s">
         <v>8</v>
       </c>
@@ -7331,18 +7348,18 @@
         <f t="array" ref="F38">INDEX(_xll.DUCKDB.EXEC($D$2,C38:C39,#REF!),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G38" s="53" t="str">
+      <c r="G38" s="54" t="str">
         <f>IF(E38=F38,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="51"/>
-      <c r="B39" s="57"/>
+      <c r="B39" s="53"/>
       <c r="C39" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D39" s="61"/>
+      <c r="D39" s="62"/>
       <c r="E39" s="51"/>
       <c r="F39" s="51"/>
       <c r="G39" s="55"/>
@@ -7351,13 +7368,13 @@
       <c r="A40" s="51">
         <v>19</v>
       </c>
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="53" t="s">
         <v>169</v>
       </c>
       <c r="C40" s="8">
         <v>1</v>
       </c>
-      <c r="D40" s="61"/>
+      <c r="D40" s="62"/>
       <c r="E40" s="51" t="s">
         <v>8</v>
       </c>
@@ -7365,18 +7382,18 @@
         <f t="array" ref="F40">INDEX(_xll.DUCKDB.EXEC($D$2,C40:C41,#REF!),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G40" s="53" t="str">
+      <c r="G40" s="54" t="str">
         <f>IF(E40=F40,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="51"/>
-      <c r="B41" s="57"/>
+      <c r="B41" s="53"/>
       <c r="C41" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D41" s="61"/>
+      <c r="D41" s="62"/>
       <c r="E41" s="51"/>
       <c r="F41" s="51"/>
       <c r="G41" s="55"/>
@@ -7385,13 +7402,13 @@
       <c r="A42" s="51">
         <v>20</v>
       </c>
-      <c r="B42" s="57" t="s">
+      <c r="B42" s="53" t="s">
         <v>171</v>
       </c>
       <c r="C42" s="8">
         <v>1.2</v>
       </c>
-      <c r="D42" s="61"/>
+      <c r="D42" s="62"/>
       <c r="E42" s="51" t="s">
         <v>8</v>
       </c>
@@ -7399,18 +7416,18 @@
         <f t="array" ref="F42">INDEX(_xll.DUCKDB.EXEC($D$2,C42:C43,#REF!),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G42" s="53" t="str">
+      <c r="G42" s="54" t="str">
         <f>IF(E42=F42,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="51"/>
-      <c r="B43" s="57"/>
+      <c r="B43" s="53"/>
       <c r="C43" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D43" s="61"/>
+      <c r="D43" s="62"/>
       <c r="E43" s="51"/>
       <c r="F43" s="51"/>
       <c r="G43" s="55"/>
@@ -7419,13 +7436,13 @@
       <c r="A44" s="51">
         <v>21</v>
       </c>
-      <c r="B44" s="57" t="s">
+      <c r="B44" s="53" t="s">
         <v>171</v>
       </c>
       <c r="C44" s="8">
         <v>1</v>
       </c>
-      <c r="D44" s="61"/>
+      <c r="D44" s="62"/>
       <c r="E44" s="51" t="s">
         <v>8</v>
       </c>
@@ -7433,56 +7450,74 @@
         <f t="array" ref="F44">INDEX(_xll.DUCKDB.EXEC($D$2,C44:C45,#REF!),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G44" s="53" t="str">
+      <c r="G44" s="54" t="str">
         <f>IF(E44=F44,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="51"/>
-      <c r="B45" s="57"/>
+      <c r="B45" s="53"/>
       <c r="C45" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D45" s="61"/>
+      <c r="D45" s="62"/>
       <c r="E45" s="51"/>
       <c r="F45" s="51"/>
       <c r="G45" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="106">
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="F24:F25"/>
@@ -7507,56 +7542,38 @@
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
   </mergeCells>
   <conditionalFormatting sqref="G14">
     <cfRule type="cellIs" dxfId="193" priority="601" stopIfTrue="1" operator="equal">
@@ -7772,7 +7789,7 @@
       <c r="A2" s="51">
         <v>1</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C2" s="8">
@@ -7781,170 +7798,170 @@
       <c r="D2" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E2" s="68">
-        <v>1</v>
-      </c>
-      <c r="F2" s="70" cm="1">
+      <c r="E2" s="66">
+        <v>1</v>
+      </c>
+      <c r="F2" s="68" cm="1">
         <f t="array" ref="F2">INDEX(_xll.DUCKDB.EXEC($D$2,C2:C3,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G2" s="53" t="str">
+      <c r="G2" s="54" t="str">
         <f>IF(E2=F2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="51"/>
-      <c r="B3" s="57"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="8">
         <v>1</v>
       </c>
       <c r="D3" s="52"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="70"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="68"/>
       <c r="G3" s="55"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="51">
         <v>2</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C4" s="8">
         <v>1</v>
       </c>
       <c r="D4" s="52"/>
-      <c r="E4" s="68">
-        <v>1</v>
-      </c>
-      <c r="F4" s="69" cm="1">
+      <c r="E4" s="66">
+        <v>1</v>
+      </c>
+      <c r="F4" s="67" cm="1">
         <f t="array" ref="F4">INDEX(_xll.DUCKDB.EXEC($D$2,C4:C5,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G4" s="53" t="str">
+      <c r="G4" s="54" t="str">
         <f>IF(E4=F4,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="51"/>
-      <c r="B5" s="57"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="11" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="52"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="69"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="67"/>
       <c r="G5" s="55"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="51">
         <v>3</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C6" s="8">
         <v>1</v>
       </c>
       <c r="D6" s="52"/>
-      <c r="E6" s="68">
-        <v>1</v>
-      </c>
-      <c r="F6" s="69" cm="1">
+      <c r="E6" s="66">
+        <v>1</v>
+      </c>
+      <c r="F6" s="67" cm="1">
         <f t="array" ref="F6">INDEX(_xll.DUCKDB.EXEC($D$2,C6:C7,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="53" t="str">
+      <c r="G6" s="54" t="str">
         <f>IF(E6=F6,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="51"/>
-      <c r="B7" s="57"/>
+      <c r="B7" s="53"/>
       <c r="C7" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D7" s="52"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="69"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="67"/>
       <c r="G7" s="55"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="51">
         <v>4</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C8" s="8">
         <v>1</v>
       </c>
       <c r="D8" s="52"/>
-      <c r="E8" s="68">
+      <c r="E8" s="66">
         <v>10</v>
       </c>
-      <c r="F8" s="69" cm="1">
+      <c r="F8" s="67" cm="1">
         <f t="array" ref="F8">INDEX(_xll.DUCKDB.EXEC($D$2,C8:C9,#REF!),3)</f>
         <v>10</v>
       </c>
-      <c r="G8" s="53" t="str">
+      <c r="G8" s="54" t="str">
         <f>IF(E8=F8,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="51"/>
-      <c r="B9" s="57"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="11" t="s">
         <v>132</v>
       </c>
       <c r="D9" s="52"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="69"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="67"/>
       <c r="G9" s="55"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="51">
         <v>5</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C10" s="8">
         <v>1</v>
       </c>
       <c r="D10" s="52"/>
-      <c r="E10" s="68">
+      <c r="E10" s="66">
         <v>10</v>
       </c>
-      <c r="F10" s="69" cm="1">
+      <c r="F10" s="67" cm="1">
         <f t="array" ref="F10">INDEX(_xll.DUCKDB.EXEC($D$2,C10:C11,#REF!),3)</f>
         <v>10</v>
       </c>
-      <c r="G10" s="53" t="str">
+      <c r="G10" s="54" t="str">
         <f>IF(E10=F10,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="51"/>
-      <c r="B11" s="57"/>
+      <c r="B11" s="53"/>
       <c r="C11" s="11" t="s">
         <v>180</v>
       </c>
       <c r="D11" s="52"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="69"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="67"/>
       <c r="G11" s="55"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="51">
         <v>6</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C12" s="8">
@@ -7954,31 +7971,31 @@
       <c r="E12" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F12" s="67" t="str" cm="1">
+      <c r="F12" s="65" t="str" cm="1">
         <f t="array" ref="F12">_xll.DUCKDB.EXEC($D$2,C12:C13,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G12" s="53" t="str">
+      <c r="G12" s="54" t="str">
         <f>IF(ISNA(E12),IF(ISNA(F12),"PASS","FAIL"),IFERROR(IF(E12=LEFT(F12,LEN(E12)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="51"/>
-      <c r="B13" s="57"/>
+      <c r="B13" s="53"/>
       <c r="C13" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="52"/>
       <c r="E13" s="51"/>
-      <c r="F13" s="67"/>
+      <c r="F13" s="65"/>
       <c r="G13" s="55"/>
     </row>
     <row r="14" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="51">
         <v>7</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C14" s="8">
@@ -7988,31 +8005,31 @@
       <c r="E14" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F14" s="67" t="str" cm="1">
+      <c r="F14" s="65" t="str" cm="1">
         <f t="array" ref="F14">_xll.DUCKDB.EXEC($D$2,C14:C15,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G14" s="53" t="str">
+      <c r="G14" s="54" t="str">
         <f>IF(ISNA(E14),IF(ISNA(F14),"PASS","FAIL"),IFERROR(IF(E14=LEFT(F14,LEN(E14)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="51"/>
-      <c r="B15" s="57"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="8">
         <v>1.2</v>
       </c>
       <c r="D15" s="52"/>
       <c r="E15" s="51"/>
-      <c r="F15" s="67"/>
+      <c r="F15" s="65"/>
       <c r="G15" s="55"/>
     </row>
     <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="51">
         <v>8</v>
       </c>
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C16" s="8">
@@ -8022,31 +8039,31 @@
       <c r="E16" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F16" s="67" t="str" cm="1">
+      <c r="F16" s="65" t="str" cm="1">
         <f t="array" ref="F16">_xll.DUCKDB.EXEC($D$2,C16:C17,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G16" s="53" t="str">
+      <c r="G16" s="54" t="str">
         <f>IF(ISNA(E16),IF(ISNA(F16),"PASS","FAIL"),IFERROR(IF(E16=LEFT(F16,LEN(E16)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="51"/>
-      <c r="B17" s="57"/>
+      <c r="B17" s="53"/>
       <c r="C17" s="11" t="s">
         <v>67</v>
       </c>
       <c r="D17" s="52"/>
       <c r="E17" s="51"/>
-      <c r="F17" s="67"/>
+      <c r="F17" s="65"/>
       <c r="G17" s="55"/>
     </row>
     <row r="18" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="51">
         <v>9</v>
       </c>
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C18" s="8">
@@ -8056,31 +8073,31 @@
       <c r="E18" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F18" s="67" t="str" cm="1">
+      <c r="F18" s="65" t="str" cm="1">
         <f t="array" ref="F18">_xll.DUCKDB.EXEC($D$2,C18:C19,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G18" s="53" t="str">
+      <c r="G18" s="54" t="str">
         <f>IF(ISNA(E18),IF(ISNA(F18),"PASS","FAIL"),IFERROR(IF(E18=LEFT(F18,LEN(E18)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="51"/>
-      <c r="B19" s="57"/>
+      <c r="B19" s="53"/>
       <c r="C19" s="11" t="s">
         <v>177</v>
       </c>
       <c r="D19" s="52"/>
       <c r="E19" s="51"/>
-      <c r="F19" s="67"/>
+      <c r="F19" s="65"/>
       <c r="G19" s="55"/>
     </row>
     <row r="20" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="51">
         <v>10</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C20" s="8">
@@ -8090,31 +8107,31 @@
       <c r="E20" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F20" s="67" t="str" cm="1">
+      <c r="F20" s="65" t="str" cm="1">
         <f t="array" ref="F20">_xll.DUCKDB.EXEC($D$2,C20:C21,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G20" s="53" t="str">
+      <c r="G20" s="54" t="str">
         <f>IF(ISNA(E20),IF(ISNA(F20),"PASS","FAIL"),IFERROR(IF(E20=LEFT(F20,LEN(E20)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="51"/>
-      <c r="B21" s="57"/>
+      <c r="B21" s="53"/>
       <c r="C21" s="11" t="s">
         <v>181</v>
       </c>
       <c r="D21" s="52"/>
       <c r="E21" s="51"/>
-      <c r="F21" s="67"/>
+      <c r="F21" s="65"/>
       <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="51">
         <v>11</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C22" s="8">
@@ -8124,31 +8141,31 @@
       <c r="E22" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="67" t="str" cm="1">
+      <c r="F22" s="65" t="str" cm="1">
         <f t="array" ref="F22">_xll.DUCKDB.EXEC($D$2,C22:C23,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G22" s="53" t="str">
+      <c r="G22" s="54" t="str">
         <f>IF(ISNA(E22),IF(ISNA(F22),"PASS","FAIL"),IFERROR(IF(E22=LEFT(F22,LEN(E22)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="51"/>
-      <c r="B23" s="57"/>
+      <c r="B23" s="53"/>
       <c r="C23" s="8" t="b">
         <v>1</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="51"/>
-      <c r="F23" s="67"/>
+      <c r="F23" s="65"/>
       <c r="G23" s="55"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="51">
         <v>12</v>
       </c>
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C24" s="8">
@@ -8158,31 +8175,31 @@
       <c r="E24" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F24" s="67" t="str" cm="1">
+      <c r="F24" s="65" t="str" cm="1">
         <f t="array" ref="F24">_xll.DUCKDB.EXEC($D$2,C24:C25,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G24" s="53" t="str">
+      <c r="G24" s="54" t="str">
         <f>IF(ISNA(E24),IF(ISNA(F24),"PASS","FAIL"),IFERROR(IF(E24=LEFT(F24,LEN(E24)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="51"/>
-      <c r="B25" s="57"/>
+      <c r="B25" s="53"/>
       <c r="C25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="D25" s="52"/>
       <c r="E25" s="51"/>
-      <c r="F25" s="67"/>
+      <c r="F25" s="65"/>
       <c r="G25" s="55"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="51">
         <v>13</v>
       </c>
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C26" s="8">
@@ -8192,31 +8209,31 @@
       <c r="E26" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F26" s="67" t="str" cm="1">
+      <c r="F26" s="65" t="str" cm="1">
         <f t="array" ref="F26">_xll.DUCKDB.EXEC($D$2,C26:C27,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G26" s="53" t="str">
+      <c r="G26" s="54" t="str">
         <f>IF(ISNA(E26),IF(ISNA(F26),"PASS","FAIL"),IFERROR(IF(E26=LEFT(F26,LEN(E26)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="51"/>
-      <c r="B27" s="57"/>
+      <c r="B27" s="53"/>
       <c r="C27" s="11" t="s">
         <v>73</v>
       </c>
       <c r="D27" s="52"/>
       <c r="E27" s="51"/>
-      <c r="F27" s="67"/>
+      <c r="F27" s="65"/>
       <c r="G27" s="55"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="51">
         <v>14</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C28" s="8">
@@ -8226,31 +8243,31 @@
       <c r="E28" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F28" s="67" t="str" cm="1">
+      <c r="F28" s="65" t="str" cm="1">
         <f t="array" ref="F28">_xll.DUCKDB.EXEC($D$2,C28:C29,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G28" s="53" t="str">
+      <c r="G28" s="54" t="str">
         <f>IF(ISNA(E28),IF(ISNA(F28),"PASS","FAIL"),IFERROR(IF(E28=LEFT(F28,LEN(E28)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="51"/>
-      <c r="B29" s="57"/>
+      <c r="B29" s="53"/>
       <c r="C29" s="11" t="s">
         <v>76</v>
       </c>
       <c r="D29" s="52"/>
       <c r="E29" s="51"/>
-      <c r="F29" s="67"/>
+      <c r="F29" s="65"/>
       <c r="G29" s="55"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="51">
         <v>15</v>
       </c>
-      <c r="B30" s="57" t="s">
+      <c r="B30" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C30" s="8">
@@ -8260,31 +8277,31 @@
       <c r="E30" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F30" s="67" t="str" cm="1">
+      <c r="F30" s="65" t="str" cm="1">
         <f t="array" ref="F30">_xll.DUCKDB.EXEC($D$2,C30:C31,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G30" s="53" t="str">
+      <c r="G30" s="54" t="str">
         <f>IF(ISNA(E30),IF(ISNA(F30),"PASS","FAIL"),IFERROR(IF(E30=LEFT(F30,LEN(E30)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="51"/>
-      <c r="B31" s="57"/>
+      <c r="B31" s="53"/>
       <c r="C31" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D31" s="52"/>
       <c r="E31" s="51"/>
-      <c r="F31" s="67"/>
+      <c r="F31" s="65"/>
       <c r="G31" s="55"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="51">
         <v>16</v>
       </c>
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C32" s="8">
@@ -8294,31 +8311,31 @@
       <c r="E32" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F32" s="67" t="str" cm="1">
+      <c r="F32" s="65" t="str" cm="1">
         <f t="array" ref="F32">_xll.DUCKDB.EXEC($D$2,C32:C33,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G32" s="53" t="str">
+      <c r="G32" s="54" t="str">
         <f>IF(ISNA(E32),IF(ISNA(F32),"PASS","FAIL"),IFERROR(IF(E32=LEFT(F32,LEN(E32)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="51"/>
-      <c r="B33" s="57"/>
+      <c r="B33" s="53"/>
       <c r="C33" s="11" t="s">
         <v>178</v>
       </c>
       <c r="D33" s="52"/>
       <c r="E33" s="51"/>
-      <c r="F33" s="67"/>
+      <c r="F33" s="65"/>
       <c r="G33" s="55"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="51">
         <v>17</v>
       </c>
-      <c r="B34" s="57" t="s">
+      <c r="B34" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C34" s="8">
@@ -8328,31 +8345,31 @@
       <c r="E34" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F34" s="67" t="str" cm="1">
+      <c r="F34" s="65" t="str" cm="1">
         <f t="array" ref="F34">_xll.DUCKDB.EXEC($D$2,C34:C35,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G34" s="53" t="str">
+      <c r="G34" s="54" t="str">
         <f>IF(ISNA(E34),IF(ISNA(F34),"PASS","FAIL"),IFERROR(IF(E34=LEFT(F34,LEN(E34)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="51"/>
-      <c r="B35" s="57"/>
+      <c r="B35" s="53"/>
       <c r="C35" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D35" s="52"/>
       <c r="E35" s="51"/>
-      <c r="F35" s="67"/>
+      <c r="F35" s="65"/>
       <c r="G35" s="55"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="51">
         <v>18</v>
       </c>
-      <c r="B36" s="57" t="s">
+      <c r="B36" s="53" t="s">
         <v>179</v>
       </c>
       <c r="C36" s="8">
@@ -8362,269 +8379,269 @@
       <c r="E36" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F36" s="67" t="str" cm="1">
+      <c r="F36" s="65" t="str" cm="1">
         <f t="array" ref="F36">_xll.DUCKDB.EXEC($D$2,C36:C37,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G36" s="53" t="str">
+      <c r="G36" s="54" t="str">
         <f>IF(ISNA(E36),IF(ISNA(F36),"PASS","FAIL"),IFERROR(IF(E36=LEFT(F36,LEN(E36)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="51"/>
-      <c r="B37" s="57"/>
+      <c r="B37" s="53"/>
       <c r="C37" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="51"/>
-      <c r="F37" s="67"/>
+      <c r="F37" s="65"/>
       <c r="G37" s="55"/>
     </row>
     <row r="38" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="51">
         <v>19</v>
       </c>
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C38" s="8">
         <v>1.2</v>
       </c>
       <c r="D38" s="52"/>
-      <c r="E38" s="68">
+      <c r="E38" s="66">
         <v>3.4</v>
       </c>
-      <c r="F38" s="70" cm="1">
+      <c r="F38" s="68" cm="1">
         <f t="array" ref="F38">INDEX(_xll.DUCKDB.EXEC($D$2,C38:C39,#REF!),3)</f>
         <v>3.4</v>
       </c>
-      <c r="G38" s="53" t="str">
+      <c r="G38" s="54" t="str">
         <f>IF(E38=F38,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="51"/>
-      <c r="B39" s="57"/>
+      <c r="B39" s="53"/>
       <c r="C39" s="8">
         <v>3.4</v>
       </c>
       <c r="D39" s="52"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="70"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="68"/>
       <c r="G39" s="55"/>
     </row>
     <row r="40" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="51">
         <v>20</v>
       </c>
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C40" s="8">
         <v>1.2</v>
       </c>
       <c r="D40" s="52"/>
-      <c r="E40" s="68">
-        <v>1</v>
-      </c>
-      <c r="F40" s="70" cm="1">
+      <c r="E40" s="66">
+        <v>1</v>
+      </c>
+      <c r="F40" s="68" cm="1">
         <f t="array" ref="F40">INDEX(_xll.DUCKDB.EXEC($D$2,C40:C41,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G40" s="53" t="str">
+      <c r="G40" s="54" t="str">
         <f>IF(E40=F40,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="51"/>
-      <c r="B41" s="57"/>
+      <c r="B41" s="53"/>
       <c r="C41" s="8">
         <v>1</v>
       </c>
       <c r="D41" s="52"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="70"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="68"/>
       <c r="G41" s="55"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="51">
         <v>21</v>
       </c>
-      <c r="B42" s="57" t="s">
+      <c r="B42" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C42" s="8">
         <v>1.2</v>
       </c>
       <c r="D42" s="52"/>
-      <c r="E42" s="68">
-        <v>1</v>
-      </c>
-      <c r="F42" s="69" cm="1">
+      <c r="E42" s="66">
+        <v>1</v>
+      </c>
+      <c r="F42" s="67" cm="1">
         <f t="array" ref="F42">INDEX(_xll.DUCKDB.EXEC($D$2,C42:C43,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G42" s="53" t="str">
+      <c r="G42" s="54" t="str">
         <f>IF(E42=F42,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="51"/>
-      <c r="B43" s="57"/>
+      <c r="B43" s="53"/>
       <c r="C43" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D43" s="52"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="69"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="67"/>
       <c r="G43" s="55"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="51">
         <v>22</v>
       </c>
-      <c r="B44" s="57" t="s">
+      <c r="B44" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C44" s="8">
         <v>1.2</v>
       </c>
       <c r="D44" s="52"/>
-      <c r="E44" s="68">
+      <c r="E44" s="66">
         <v>3.4</v>
       </c>
-      <c r="F44" s="69" cm="1">
+      <c r="F44" s="67" cm="1">
         <f t="array" ref="F44">INDEX(_xll.DUCKDB.EXEC($D$2,C44:C45,#REF!),3)</f>
         <v>3.4</v>
       </c>
-      <c r="G44" s="53" t="str">
+      <c r="G44" s="54" t="str">
         <f>IF(E44=F44,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="51"/>
-      <c r="B45" s="57"/>
+      <c r="B45" s="53"/>
       <c r="C45" s="11" t="s">
         <v>184</v>
       </c>
       <c r="D45" s="52"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="69"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="67"/>
       <c r="G45" s="55"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="51">
         <v>23</v>
       </c>
-      <c r="B46" s="57" t="s">
+      <c r="B46" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C46" s="8">
         <v>1.2</v>
       </c>
       <c r="D46" s="52"/>
-      <c r="E46" s="68">
+      <c r="E46" s="66">
         <v>10</v>
       </c>
-      <c r="F46" s="69" cm="1">
+      <c r="F46" s="67" cm="1">
         <f t="array" ref="F46">INDEX(_xll.DUCKDB.EXEC($D$2,C46:C47,#REF!),3)</f>
         <v>10</v>
       </c>
-      <c r="G46" s="53" t="str">
+      <c r="G46" s="54" t="str">
         <f>IF(E46=F46,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="51"/>
-      <c r="B47" s="57"/>
+      <c r="B47" s="53"/>
       <c r="C47" s="11" t="s">
         <v>132</v>
       </c>
       <c r="D47" s="52"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="69"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="67"/>
       <c r="G47" s="55"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="51">
         <v>24</v>
       </c>
-      <c r="B48" s="57" t="s">
+      <c r="B48" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C48" s="8">
         <v>1.2</v>
       </c>
       <c r="D48" s="52"/>
-      <c r="E48" s="68">
+      <c r="E48" s="66">
         <v>0.1</v>
       </c>
-      <c r="F48" s="69" cm="1">
+      <c r="F48" s="67" cm="1">
         <f t="array" ref="F48">INDEX(_xll.DUCKDB.EXEC($D$2,C48:C49,#REF!),3)</f>
         <v>0.1</v>
       </c>
-      <c r="G48" s="53" t="str">
+      <c r="G48" s="54" t="str">
         <f>IF(E48=F48,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="51"/>
-      <c r="B49" s="57"/>
+      <c r="B49" s="53"/>
       <c r="C49" s="11" t="s">
         <v>185</v>
       </c>
       <c r="D49" s="52"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="69"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="67"/>
       <c r="G49" s="55"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="51">
         <v>25</v>
       </c>
-      <c r="B50" s="57" t="s">
+      <c r="B50" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C50" s="8">
         <v>1.2</v>
       </c>
       <c r="D50" s="52"/>
-      <c r="E50" s="68">
+      <c r="E50" s="66">
         <v>0.1</v>
       </c>
-      <c r="F50" s="69" cm="1">
+      <c r="F50" s="67" cm="1">
         <f t="array" ref="F50">INDEX(_xll.DUCKDB.EXEC($D$2,C50:C51,#REF!),3)</f>
         <v>0.1</v>
       </c>
-      <c r="G50" s="53" t="str">
+      <c r="G50" s="54" t="str">
         <f>IF(E50=F50,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="51"/>
-      <c r="B51" s="57"/>
+      <c r="B51" s="53"/>
       <c r="C51" s="11" t="s">
         <v>186</v>
       </c>
       <c r="D51" s="52"/>
-      <c r="E51" s="68"/>
-      <c r="F51" s="69"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="67"/>
       <c r="G51" s="55"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="51">
         <v>26</v>
       </c>
-      <c r="B52" s="57" t="s">
+      <c r="B52" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C52" s="8">
@@ -8634,31 +8651,31 @@
       <c r="E52" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F52" s="67" t="str" cm="1">
+      <c r="F52" s="65" t="str" cm="1">
         <f t="array" ref="F52">_xll.DUCKDB.EXEC($D$2,C52:C53,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G52" s="53" t="str">
+      <c r="G52" s="54" t="str">
         <f>IF(ISNA(E52),IF(ISNA(F52),"PASS","FAIL"),IFERROR(IF(E52=LEFT(F52,LEN(E52)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="51"/>
-      <c r="B53" s="57"/>
+      <c r="B53" s="53"/>
       <c r="C53" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D53" s="52"/>
       <c r="E53" s="51"/>
-      <c r="F53" s="67"/>
+      <c r="F53" s="65"/>
       <c r="G53" s="55"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="51">
         <v>27</v>
       </c>
-      <c r="B54" s="57" t="s">
+      <c r="B54" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C54" s="8">
@@ -8668,31 +8685,31 @@
       <c r="E54" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F54" s="67" t="str" cm="1">
+      <c r="F54" s="65" t="str" cm="1">
         <f t="array" ref="F54">_xll.DUCKDB.EXEC($D$2,C54:C55,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G54" s="53" t="str">
+      <c r="G54" s="54" t="str">
         <f>IF(ISNA(E54),IF(ISNA(F54),"PASS","FAIL"),IFERROR(IF(E54=LEFT(F54,LEN(E54)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="51"/>
-      <c r="B55" s="57"/>
+      <c r="B55" s="53"/>
       <c r="C55" s="8" t="b">
         <v>1</v>
       </c>
       <c r="D55" s="52"/>
       <c r="E55" s="51"/>
-      <c r="F55" s="67"/>
+      <c r="F55" s="65"/>
       <c r="G55" s="55"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="51">
         <v>28</v>
       </c>
-      <c r="B56" s="57" t="s">
+      <c r="B56" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C56" s="8">
@@ -8702,31 +8719,31 @@
       <c r="E56" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F56" s="67" t="str" cm="1">
+      <c r="F56" s="65" t="str" cm="1">
         <f t="array" ref="F56">_xll.DUCKDB.EXEC($D$2,C56:C57,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G56" s="53" t="str">
+      <c r="G56" s="54" t="str">
         <f>IF(ISNA(E56),IF(ISNA(F56),"PASS","FAIL"),IFERROR(IF(E56=LEFT(F56,LEN(E56)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="51"/>
-      <c r="B57" s="57"/>
+      <c r="B57" s="53"/>
       <c r="C57" s="11" t="s">
         <v>70</v>
       </c>
       <c r="D57" s="52"/>
       <c r="E57" s="51"/>
-      <c r="F57" s="67"/>
+      <c r="F57" s="65"/>
       <c r="G57" s="55"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="51">
         <v>29</v>
       </c>
-      <c r="B58" s="57" t="s">
+      <c r="B58" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C58" s="8">
@@ -8736,31 +8753,31 @@
       <c r="E58" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F58" s="67" t="str" cm="1">
+      <c r="F58" s="65" t="str" cm="1">
         <f t="array" ref="F58">_xll.DUCKDB.EXEC($D$2,C58:C59,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G58" s="53" t="str">
+      <c r="G58" s="54" t="str">
         <f>IF(ISNA(E58),IF(ISNA(F58),"PASS","FAIL"),IFERROR(IF(E58=LEFT(F58,LEN(E58)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="51"/>
-      <c r="B59" s="57"/>
+      <c r="B59" s="53"/>
       <c r="C59" s="11" t="s">
         <v>73</v>
       </c>
       <c r="D59" s="52"/>
       <c r="E59" s="51"/>
-      <c r="F59" s="67"/>
+      <c r="F59" s="65"/>
       <c r="G59" s="55"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="51">
         <v>30</v>
       </c>
-      <c r="B60" s="57" t="s">
+      <c r="B60" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C60" s="8">
@@ -8770,31 +8787,31 @@
       <c r="E60" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F60" s="67" t="str" cm="1">
+      <c r="F60" s="65" t="str" cm="1">
         <f t="array" ref="F60">_xll.DUCKDB.EXEC($D$2,C60:C61,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G60" s="53" t="str">
+      <c r="G60" s="54" t="str">
         <f>IF(ISNA(E60),IF(ISNA(F60),"PASS","FAIL"),IFERROR(IF(E60=LEFT(F60,LEN(E60)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="51"/>
-      <c r="B61" s="57"/>
+      <c r="B61" s="53"/>
       <c r="C61" s="11" t="s">
         <v>76</v>
       </c>
       <c r="D61" s="52"/>
       <c r="E61" s="51"/>
-      <c r="F61" s="67"/>
+      <c r="F61" s="65"/>
       <c r="G61" s="55"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="51">
         <v>31</v>
       </c>
-      <c r="B62" s="57" t="s">
+      <c r="B62" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C62" s="8">
@@ -8804,31 +8821,31 @@
       <c r="E62" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F62" s="67" t="str" cm="1">
+      <c r="F62" s="65" t="str" cm="1">
         <f t="array" ref="F62">_xll.DUCKDB.EXEC($D$2,C62:C63,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G62" s="53" t="str">
+      <c r="G62" s="54" t="str">
         <f>IF(ISNA(E62),IF(ISNA(F62),"PASS","FAIL"),IFERROR(IF(E62=LEFT(F62,LEN(E62)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="51"/>
-      <c r="B63" s="57"/>
+      <c r="B63" s="53"/>
       <c r="C63" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="51"/>
-      <c r="F63" s="67"/>
+      <c r="F63" s="65"/>
       <c r="G63" s="55"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="51">
         <v>32</v>
       </c>
-      <c r="B64" s="57" t="s">
+      <c r="B64" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C64" s="8">
@@ -8838,31 +8855,31 @@
       <c r="E64" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F64" s="67" t="str" cm="1">
+      <c r="F64" s="65" t="str" cm="1">
         <f t="array" ref="F64">_xll.DUCKDB.EXEC($D$2,C64:C65,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G64" s="53" t="str">
+      <c r="G64" s="54" t="str">
         <f>IF(ISNA(E64),IF(ISNA(F64),"PASS","FAIL"),IFERROR(IF(E64=LEFT(F64,LEN(E64)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="51"/>
-      <c r="B65" s="57"/>
+      <c r="B65" s="53"/>
       <c r="C65" s="11" t="s">
         <v>178</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="51"/>
-      <c r="F65" s="67"/>
+      <c r="F65" s="65"/>
       <c r="G65" s="55"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="51">
         <v>33</v>
       </c>
-      <c r="B66" s="57" t="s">
+      <c r="B66" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C66" s="8">
@@ -8872,31 +8889,31 @@
       <c r="E66" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F66" s="67" t="str" cm="1">
+      <c r="F66" s="65" t="str" cm="1">
         <f t="array" ref="F66">_xll.DUCKDB.EXEC($D$2,C66:C67,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G66" s="53" t="str">
+      <c r="G66" s="54" t="str">
         <f>IF(ISNA(E66),IF(ISNA(F66),"PASS","FAIL"),IFERROR(IF(E66=LEFT(F66,LEN(E66)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="51"/>
-      <c r="B67" s="57"/>
+      <c r="B67" s="53"/>
       <c r="C67" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D67" s="52"/>
       <c r="E67" s="51"/>
-      <c r="F67" s="67"/>
+      <c r="F67" s="65"/>
       <c r="G67" s="55"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="51">
         <v>34</v>
       </c>
-      <c r="B68" s="57" t="s">
+      <c r="B68" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C68" s="8">
@@ -8906,31 +8923,31 @@
       <c r="E68" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F68" s="67" t="str" cm="1">
+      <c r="F68" s="65" t="str" cm="1">
         <f t="array" ref="F68">_xll.DUCKDB.EXEC($D$2,C68:C69,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G68" s="53" t="str">
+      <c r="G68" s="54" t="str">
         <f>IF(ISNA(E68),IF(ISNA(F68),"PASS","FAIL"),IFERROR(IF(E68=LEFT(F68,LEN(E68)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="51"/>
-      <c r="B69" s="57"/>
+      <c r="B69" s="53"/>
       <c r="C69" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="51"/>
-      <c r="F69" s="67"/>
+      <c r="F69" s="65"/>
       <c r="G69" s="55"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="51">
         <v>35</v>
       </c>
-      <c r="B70" s="57" t="s">
+      <c r="B70" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C70" s="8" t="b">
@@ -8940,31 +8957,31 @@
       <c r="E70" s="51" t="b">
         <v>0</v>
       </c>
-      <c r="F70" s="66" t="b" cm="1">
+      <c r="F70" s="69" t="b" cm="1">
         <f t="array" ref="F70">INDEX(_xll.DUCKDB.EXEC($D$2,C70:C71,#REF!),3)</f>
         <v>0</v>
       </c>
-      <c r="G70" s="53" t="str">
+      <c r="G70" s="54" t="str">
         <f>IF(E70=F70,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="51"/>
-      <c r="B71" s="57"/>
+      <c r="B71" s="53"/>
       <c r="C71" s="27" t="b">
         <v>0</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="51"/>
-      <c r="F71" s="66"/>
+      <c r="F71" s="69"/>
       <c r="G71" s="55"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="51">
         <v>36</v>
       </c>
-      <c r="B72" s="57" t="s">
+      <c r="B72" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C72" s="8" t="b">
@@ -8974,31 +8991,31 @@
       <c r="E72" s="51" t="b">
         <v>0</v>
       </c>
-      <c r="F72" s="66" t="b" cm="1">
+      <c r="F72" s="69" t="b" cm="1">
         <f t="array" ref="F72">INDEX(_xll.DUCKDB.EXEC($D$2,C72:C73,#REF!),3)</f>
         <v>0</v>
       </c>
-      <c r="G72" s="53" t="str">
+      <c r="G72" s="54" t="str">
         <f>IF(E72=F72,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="51"/>
-      <c r="B73" s="57"/>
+      <c r="B73" s="53"/>
       <c r="C73" s="31" t="s">
         <v>71</v>
       </c>
       <c r="D73" s="52"/>
       <c r="E73" s="51"/>
-      <c r="F73" s="66"/>
+      <c r="F73" s="69"/>
       <c r="G73" s="55"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="51">
         <v>37</v>
       </c>
-      <c r="B74" s="57" t="s">
+      <c r="B74" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C74" s="8" t="b">
@@ -9008,31 +9025,31 @@
       <c r="E74" s="51" t="b">
         <v>0</v>
       </c>
-      <c r="F74" s="66" t="b" cm="1">
+      <c r="F74" s="69" t="b" cm="1">
         <f t="array" ref="F74">INDEX(_xll.DUCKDB.EXEC($D$2,C74:C75,#REF!),3)</f>
         <v>0</v>
       </c>
-      <c r="G74" s="53" t="str">
+      <c r="G74" s="54" t="str">
         <f>IF(E74=F74,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="51"/>
-      <c r="B75" s="57"/>
+      <c r="B75" s="53"/>
       <c r="C75" s="31" t="s">
         <v>73</v>
       </c>
       <c r="D75" s="52"/>
       <c r="E75" s="51"/>
-      <c r="F75" s="66"/>
+      <c r="F75" s="69"/>
       <c r="G75" s="55"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="51">
         <v>38</v>
       </c>
-      <c r="B76" s="57" t="s">
+      <c r="B76" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C76" s="8" t="b">
@@ -9042,31 +9059,31 @@
       <c r="E76" s="51" t="b">
         <v>0</v>
       </c>
-      <c r="F76" s="66" t="b" cm="1">
+      <c r="F76" s="69" t="b" cm="1">
         <f t="array" ref="F76">INDEX(_xll.DUCKDB.EXEC($D$2,C76:C77,#REF!),3)</f>
         <v>0</v>
       </c>
-      <c r="G76" s="53" t="str">
+      <c r="G76" s="54" t="str">
         <f>IF(E76=F76,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="51"/>
-      <c r="B77" s="57"/>
+      <c r="B77" s="53"/>
       <c r="C77" s="31" t="s">
         <v>77</v>
       </c>
       <c r="D77" s="52"/>
       <c r="E77" s="51"/>
-      <c r="F77" s="66"/>
+      <c r="F77" s="69"/>
       <c r="G77" s="55"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="51">
         <v>39</v>
       </c>
-      <c r="B78" s="57" t="s">
+      <c r="B78" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C78" s="8" t="b">
@@ -9076,31 +9093,31 @@
       <c r="E78" s="51" t="b">
         <v>0</v>
       </c>
-      <c r="F78" s="66" t="b" cm="1">
+      <c r="F78" s="69" t="b" cm="1">
         <f t="array" ref="F78">INDEX(_xll.DUCKDB.EXEC($D$2,C78:C79,#REF!),3)</f>
         <v>0</v>
       </c>
-      <c r="G78" s="53" t="str">
+      <c r="G78" s="54" t="str">
         <f>IF(E78=F78,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="51"/>
-      <c r="B79" s="57"/>
+      <c r="B79" s="53"/>
       <c r="C79" s="31" t="s">
         <v>79</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="51"/>
-      <c r="F79" s="66"/>
+      <c r="F79" s="69"/>
       <c r="G79" s="55"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="51">
         <v>40</v>
       </c>
-      <c r="B80" s="57" t="s">
+      <c r="B80" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C80" s="8" t="b">
@@ -9110,31 +9127,31 @@
       <c r="E80" s="51" t="b">
         <v>1</v>
       </c>
-      <c r="F80" s="66" t="b" cm="1">
+      <c r="F80" s="69" t="b" cm="1">
         <f t="array" ref="F80">INDEX(_xll.DUCKDB.EXEC($D$2,C80:C81,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G80" s="53" t="str">
+      <c r="G80" s="54" t="str">
         <f>IF(E80=F80,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="51"/>
-      <c r="B81" s="57"/>
+      <c r="B81" s="53"/>
       <c r="C81" s="31" t="s">
         <v>178</v>
       </c>
       <c r="D81" s="52"/>
       <c r="E81" s="51"/>
-      <c r="F81" s="66"/>
+      <c r="F81" s="69"/>
       <c r="G81" s="55"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="51">
         <v>41</v>
       </c>
-      <c r="B82" s="57" t="s">
+      <c r="B82" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C82" s="8" t="b">
@@ -9144,31 +9161,31 @@
       <c r="E82" s="51" t="b">
         <v>1</v>
       </c>
-      <c r="F82" s="66" t="b" cm="1">
+      <c r="F82" s="69" t="b" cm="1">
         <f t="array" ref="F82">INDEX(_xll.DUCKDB.EXEC($D$2,C82:C83,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G82" s="53" t="str">
+      <c r="G82" s="54" t="str">
         <f>IF(E82=F82,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="51"/>
-      <c r="B83" s="57"/>
+      <c r="B83" s="53"/>
       <c r="C83" s="31" t="s">
         <v>188</v>
       </c>
       <c r="D83" s="52"/>
       <c r="E83" s="51"/>
-      <c r="F83" s="66"/>
+      <c r="F83" s="69"/>
       <c r="G83" s="55"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="51">
         <v>42</v>
       </c>
-      <c r="B84" s="57" t="s">
+      <c r="B84" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C84" s="8" t="b">
@@ -9178,31 +9195,31 @@
       <c r="E84" s="51" t="b">
         <v>0</v>
       </c>
-      <c r="F84" s="66" t="b" cm="1">
+      <c r="F84" s="69" t="b" cm="1">
         <f t="array" ref="F84">INDEX(_xll.DUCKDB.EXEC($D$2,C84:C85,#REF!),3)</f>
         <v>0</v>
       </c>
-      <c r="G84" s="53" t="str">
+      <c r="G84" s="54" t="str">
         <f>IF(E84=F84,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="51"/>
-      <c r="B85" s="57"/>
+      <c r="B85" s="53"/>
       <c r="C85" s="32">
         <v>0</v>
       </c>
       <c r="D85" s="52"/>
       <c r="E85" s="51"/>
-      <c r="F85" s="66"/>
+      <c r="F85" s="69"/>
       <c r="G85" s="55"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="51">
         <v>43</v>
       </c>
-      <c r="B86" s="57" t="s">
+      <c r="B86" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C86" s="8" t="b">
@@ -9212,31 +9229,31 @@
       <c r="E86" s="51" t="b">
         <v>1</v>
       </c>
-      <c r="F86" s="66" t="b" cm="1">
+      <c r="F86" s="69" t="b" cm="1">
         <f t="array" ref="F86">INDEX(_xll.DUCKDB.EXEC($D$2,C86:C87,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G86" s="53" t="str">
+      <c r="G86" s="54" t="str">
         <f>IF(E86=F86,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="51"/>
-      <c r="B87" s="57"/>
+      <c r="B87" s="53"/>
       <c r="C87" s="31" t="s">
         <v>62</v>
       </c>
       <c r="D87" s="52"/>
       <c r="E87" s="51"/>
-      <c r="F87" s="66"/>
+      <c r="F87" s="69"/>
       <c r="G87" s="55"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="51">
         <v>44</v>
       </c>
-      <c r="B88" s="57" t="s">
+      <c r="B88" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C88" s="8" t="b">
@@ -9246,31 +9263,31 @@
       <c r="E88" s="51" t="b">
         <v>1</v>
       </c>
-      <c r="F88" s="66" t="b" cm="1">
+      <c r="F88" s="69" t="b" cm="1">
         <f t="array" ref="F88">INDEX(_xll.DUCKDB.EXEC($D$2,C88:C89,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G88" s="53" t="str">
+      <c r="G88" s="54" t="str">
         <f>IF(E88=F88,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="51"/>
-      <c r="B89" s="57"/>
+      <c r="B89" s="53"/>
       <c r="C89" s="31" t="s">
         <v>63</v>
       </c>
       <c r="D89" s="52"/>
       <c r="E89" s="51"/>
-      <c r="F89" s="66"/>
+      <c r="F89" s="69"/>
       <c r="G89" s="55"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="51">
         <v>45</v>
       </c>
-      <c r="B90" s="57" t="s">
+      <c r="B90" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C90" s="8" t="b">
@@ -9280,31 +9297,31 @@
       <c r="E90" s="51" t="b">
         <v>1</v>
       </c>
-      <c r="F90" s="66" t="b" cm="1">
+      <c r="F90" s="69" t="b" cm="1">
         <f t="array" ref="F90">INDEX(_xll.DUCKDB.EXEC($D$2,C90:C91,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G90" s="53" t="str">
+      <c r="G90" s="54" t="str">
         <f>IF(E90=F90,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="51"/>
-      <c r="B91" s="57"/>
+      <c r="B91" s="53"/>
       <c r="C91" s="31" t="s">
         <v>190</v>
       </c>
       <c r="D91" s="52"/>
       <c r="E91" s="51"/>
-      <c r="F91" s="66"/>
+      <c r="F91" s="69"/>
       <c r="G91" s="55"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="51">
         <v>46</v>
       </c>
-      <c r="B92" s="57" t="s">
+      <c r="B92" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C92" s="8" t="b">
@@ -9314,31 +9331,31 @@
       <c r="E92" s="51" t="b">
         <v>1</v>
       </c>
-      <c r="F92" s="66" t="b" cm="1">
+      <c r="F92" s="69" t="b" cm="1">
         <f t="array" ref="F92">INDEX(_xll.DUCKDB.EXEC($D$2,C92:C93,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G92" s="53" t="str">
+      <c r="G92" s="54" t="str">
         <f>IF(E92=F92,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="51"/>
-      <c r="B93" s="57"/>
+      <c r="B93" s="53"/>
       <c r="C93" s="31" t="s">
         <v>191</v>
       </c>
       <c r="D93" s="52"/>
       <c r="E93" s="51"/>
-      <c r="F93" s="66"/>
+      <c r="F93" s="69"/>
       <c r="G93" s="55"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="51">
         <v>47</v>
       </c>
-      <c r="B94" s="57" t="s">
+      <c r="B94" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C94" s="8" t="b">
@@ -9348,31 +9365,31 @@
       <c r="E94" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F94" s="67" t="str" cm="1">
+      <c r="F94" s="65" t="str" cm="1">
         <f t="array" ref="F94">_xll.DUCKDB.EXEC($D$2,C94:C95,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G94" s="53" t="str">
+      <c r="G94" s="54" t="str">
         <f t="shared" ref="G94" si="0">IF(ISNA(E94),IF(ISNA(F94),"PASS","FAIL"),IFERROR(IF(E94=LEFT(F94,LEN(E94)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="51"/>
-      <c r="B95" s="57"/>
+      <c r="B95" s="53"/>
       <c r="C95" s="32">
         <v>2</v>
       </c>
       <c r="D95" s="52"/>
       <c r="E95" s="51"/>
-      <c r="F95" s="67"/>
+      <c r="F95" s="65"/>
       <c r="G95" s="55"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="51">
         <v>48</v>
       </c>
-      <c r="B96" s="57" t="s">
+      <c r="B96" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C96" s="8" t="b">
@@ -9382,31 +9399,31 @@
       <c r="E96" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F96" s="67" t="str" cm="1">
+      <c r="F96" s="65" t="str" cm="1">
         <f t="array" ref="F96">_xll.DUCKDB.EXEC($D$2,C96:C97,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G96" s="53" t="str">
+      <c r="G96" s="54" t="str">
         <f t="shared" ref="G96" si="1">IF(ISNA(E96),IF(ISNA(F96),"PASS","FAIL"),IFERROR(IF(E96=LEFT(F96,LEN(E96)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="51"/>
-      <c r="B97" s="57"/>
+      <c r="B97" s="53"/>
       <c r="C97" s="31" t="s">
         <v>189</v>
       </c>
       <c r="D97" s="52"/>
       <c r="E97" s="51"/>
-      <c r="F97" s="67"/>
+      <c r="F97" s="65"/>
       <c r="G97" s="55"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="51">
         <v>49</v>
       </c>
-      <c r="B98" s="57" t="s">
+      <c r="B98" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C98" s="8" t="b">
@@ -9416,31 +9433,31 @@
       <c r="E98" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F98" s="67" t="str" cm="1">
+      <c r="F98" s="65" t="str" cm="1">
         <f t="array" ref="F98">_xll.DUCKDB.EXEC($D$2,C98:C99,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G98" s="53" t="str">
+      <c r="G98" s="54" t="str">
         <f t="shared" ref="G98" si="2">IF(ISNA(E98),IF(ISNA(F98),"PASS","FAIL"),IFERROR(IF(E98=LEFT(F98,LEN(E98)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="51"/>
-      <c r="B99" s="57"/>
+      <c r="B99" s="53"/>
       <c r="C99" s="31" t="s">
         <v>192</v>
       </c>
       <c r="D99" s="52"/>
       <c r="E99" s="51"/>
-      <c r="F99" s="67"/>
+      <c r="F99" s="65"/>
       <c r="G99" s="55"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="51">
         <v>50</v>
       </c>
-      <c r="B100" s="57" t="s">
+      <c r="B100" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C100" s="8" t="b">
@@ -9450,31 +9467,31 @@
       <c r="E100" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F100" s="67" t="str" cm="1">
+      <c r="F100" s="65" t="str" cm="1">
         <f t="array" ref="F100">_xll.DUCKDB.EXEC($D$2,C100:C101,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G100" s="53" t="str">
+      <c r="G100" s="54" t="str">
         <f t="shared" ref="G100" si="3">IF(ISNA(E100),IF(ISNA(F100),"PASS","FAIL"),IFERROR(IF(E100=LEFT(F100,LEN(E100)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="51"/>
-      <c r="B101" s="57"/>
+      <c r="B101" s="53"/>
       <c r="C101" s="31" t="s">
         <v>193</v>
       </c>
       <c r="D101" s="52"/>
       <c r="E101" s="51"/>
-      <c r="F101" s="67"/>
+      <c r="F101" s="65"/>
       <c r="G101" s="55"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="51">
         <v>51</v>
       </c>
-      <c r="B102" s="57" t="s">
+      <c r="B102" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C102" s="8" t="b">
@@ -9484,31 +9501,31 @@
       <c r="E102" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F102" s="67" t="str" cm="1">
+      <c r="F102" s="65" t="str" cm="1">
         <f t="array" ref="F102">_xll.DUCKDB.EXEC($D$2,C102:C103,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G102" s="53" t="str">
+      <c r="G102" s="54" t="str">
         <f t="shared" ref="G102" si="4">IF(ISNA(E102),IF(ISNA(F102),"PASS","FAIL"),IFERROR(IF(E102=LEFT(F102,LEN(E102)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="51"/>
-      <c r="B103" s="57"/>
+      <c r="B103" s="53"/>
       <c r="C103" s="31" t="s">
         <v>194</v>
       </c>
       <c r="D103" s="52"/>
       <c r="E103" s="51"/>
-      <c r="F103" s="67"/>
+      <c r="F103" s="65"/>
       <c r="G103" s="55"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="51">
         <v>52</v>
       </c>
-      <c r="B104" s="57" t="s">
+      <c r="B104" s="53" t="s">
         <v>187</v>
       </c>
       <c r="C104" s="8" t="b">
@@ -9518,31 +9535,31 @@
       <c r="E104" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F104" s="67" t="str" cm="1">
+      <c r="F104" s="65" t="str" cm="1">
         <f t="array" ref="F104">_xll.DUCKDB.EXEC($D$2,C104:C105,#REF!)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G104" s="53" t="str">
+      <c r="G104" s="54" t="str">
         <f t="shared" ref="G104" si="5">IF(ISNA(E104),IF(ISNA(F104),"PASS","FAIL"),IFERROR(IF(E104=LEFT(F104,LEN(E104)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="51"/>
-      <c r="B105" s="57"/>
+      <c r="B105" s="53"/>
       <c r="C105" s="32" t="s">
         <v>45</v>
       </c>
       <c r="D105" s="52"/>
       <c r="E105" s="51"/>
-      <c r="F105" s="67"/>
+      <c r="F105" s="65"/>
       <c r="G105" s="55"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="51">
         <v>53</v>
       </c>
-      <c r="B106" s="57" t="s">
+      <c r="B106" s="53" t="s">
         <v>195</v>
       </c>
       <c r="C106" s="8" t="s">
@@ -9552,162 +9569,355 @@
       <c r="E106" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="F106" s="66" t="str" cm="1">
+      <c r="F106" s="69" t="str" cm="1">
         <f t="array" ref="F106">INDEX(_xll.DUCKDB.EXEC($D$2,C106:C107,#REF!),3)</f>
         <v>def</v>
       </c>
-      <c r="G106" s="53" t="str">
+      <c r="G106" s="54" t="str">
         <f>IF(E106=F106,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="51"/>
-      <c r="B107" s="57"/>
+      <c r="B107" s="53"/>
       <c r="C107" s="32" t="s">
         <v>196</v>
       </c>
       <c r="D107" s="52"/>
       <c r="E107" s="51"/>
-      <c r="F107" s="66"/>
+      <c r="F107" s="69"/>
       <c r="G107" s="55"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="51">
         <v>54</v>
       </c>
-      <c r="B108" s="57" t="s">
+      <c r="B108" s="53" t="s">
         <v>195</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D108" s="52"/>
-      <c r="E108" s="65" t="s">
+      <c r="E108" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="F108" s="66" t="str" cm="1">
+      <c r="F108" s="69" t="str" cm="1">
         <f t="array" ref="F108">INDEX(_xll.DUCKDB.EXEC($D$2,C108:C109,#REF!),3)</f>
         <v>1</v>
       </c>
-      <c r="G108" s="53" t="str">
+      <c r="G108" s="54" t="str">
         <f>IF(E108=F108,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="51"/>
-      <c r="B109" s="57"/>
+      <c r="B109" s="53"/>
       <c r="C109" s="32">
         <v>1</v>
       </c>
       <c r="D109" s="52"/>
-      <c r="E109" s="65"/>
-      <c r="F109" s="66"/>
+      <c r="E109" s="70"/>
+      <c r="F109" s="69"/>
       <c r="G109" s="55"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="51">
         <v>55</v>
       </c>
-      <c r="B110" s="57" t="s">
+      <c r="B110" s="53" t="s">
         <v>195</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D110" s="52"/>
-      <c r="E110" s="65" t="s">
+      <c r="E110" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="F110" s="66" t="str" cm="1">
+      <c r="F110" s="69" t="str" cm="1">
         <f t="array" ref="F110">INDEX(_xll.DUCKDB.EXEC($D$2,C110:C111,#REF!),3)</f>
         <v>1.2</v>
       </c>
-      <c r="G110" s="53" t="str">
+      <c r="G110" s="54" t="str">
         <f>IF(E110=F110,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="51"/>
-      <c r="B111" s="57"/>
+      <c r="B111" s="53"/>
       <c r="C111" s="32">
         <v>1.2</v>
       </c>
       <c r="D111" s="52"/>
-      <c r="E111" s="65"/>
-      <c r="F111" s="66"/>
+      <c r="E111" s="70"/>
+      <c r="F111" s="69"/>
       <c r="G111" s="55"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="51">
         <v>56</v>
       </c>
-      <c r="B112" s="57" t="s">
+      <c r="B112" s="53" t="s">
         <v>195</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D112" s="52"/>
-      <c r="E112" s="65" t="s">
+      <c r="E112" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="F112" s="66" t="str" cm="1">
+      <c r="F112" s="69" t="str" cm="1">
         <f t="array" ref="F112">INDEX(_xll.DUCKDB.EXEC($D$2,C112:C113,#REF!),3)</f>
         <v>TRUE</v>
       </c>
-      <c r="G112" s="53" t="str">
+      <c r="G112" s="54" t="str">
         <f>IF(E112=F112,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="51"/>
-      <c r="B113" s="57"/>
+      <c r="B113" s="53"/>
       <c r="C113" s="32" t="b">
         <v>1</v>
       </c>
       <c r="D113" s="52"/>
-      <c r="E113" s="65"/>
-      <c r="F113" s="66"/>
+      <c r="E113" s="70"/>
+      <c r="F113" s="69"/>
       <c r="G113" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="281">
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="E112:E113"/>
+    <mergeCell ref="F112:F113"/>
+    <mergeCell ref="G112:G113"/>
+    <mergeCell ref="D2:D113"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="E110:E111"/>
+    <mergeCell ref="F110:F111"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="E108:E109"/>
+    <mergeCell ref="F108:F109"/>
+    <mergeCell ref="G108:G109"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="F106:F107"/>
+    <mergeCell ref="G106:G107"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="F104:F105"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="E102:E103"/>
+    <mergeCell ref="F102:F103"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="E100:E101"/>
+    <mergeCell ref="F100:F101"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="E92:E93"/>
+    <mergeCell ref="F92:F93"/>
+    <mergeCell ref="G92:G93"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="F88:F89"/>
+    <mergeCell ref="G88:G89"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="E98:E99"/>
+    <mergeCell ref="F98:F99"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="F96:F97"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="E94:E95"/>
+    <mergeCell ref="F94:F95"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:F85"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="F82:F83"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="F78:F79"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="F76:F77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="F74:F75"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="E4:E5"/>
@@ -9732,231 +9942,38 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="F68:F69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="F66:F67"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="F64:F65"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="F74:F75"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="F76:F77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="E86:E87"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:F85"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="F88:F89"/>
-    <mergeCell ref="G88:G89"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="E98:E99"/>
-    <mergeCell ref="F98:F99"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="F96:F97"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="E94:E95"/>
-    <mergeCell ref="F94:F95"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="E100:E101"/>
-    <mergeCell ref="F100:F101"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="E92:E93"/>
-    <mergeCell ref="F92:F93"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="E112:E113"/>
-    <mergeCell ref="F112:F113"/>
-    <mergeCell ref="G112:G113"/>
-    <mergeCell ref="D2:D113"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="E110:E111"/>
-    <mergeCell ref="F110:F111"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="E108:E109"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="G108:G109"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="E106:E107"/>
-    <mergeCell ref="F106:F107"/>
-    <mergeCell ref="G106:G107"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="F104:F105"/>
-    <mergeCell ref="G104:G105"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="E102:E103"/>
-    <mergeCell ref="F102:F103"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
   </mergeCells>
   <conditionalFormatting sqref="G14">
     <cfRule type="cellIs" dxfId="151" priority="137" stopIfTrue="1" operator="equal">
@@ -10567,10 +10584,10 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="53">
-        <v>1</v>
-      </c>
-      <c r="B7" s="57" t="s">
+      <c r="A7" s="54">
+        <v>1</v>
+      </c>
+      <c r="B7" s="53" t="s">
         <v>198</v>
       </c>
       <c r="C7" s="52" t="s">
@@ -10587,14 +10604,14 @@
         <f t="shared" ref="F7:F41" si="0">IF(E7=D7,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="G7" s="53" t="str">
+      <c r="G7" s="54" t="str">
         <f>IF(COUNTA(F7:F13)=COUNTIF(F7:F13,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="54"/>
-      <c r="B8" s="57"/>
+      <c r="A8" s="59"/>
+      <c r="B8" s="53"/>
       <c r="C8" s="52"/>
       <c r="D8" s="34" t="s">
         <v>4</v>
@@ -10606,11 +10623,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G8" s="54"/>
+      <c r="G8" s="59"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="54"/>
-      <c r="B9" s="57"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="52"/>
       <c r="D9" s="34" t="s">
         <v>12</v>
@@ -10622,11 +10639,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G9" s="54"/>
+      <c r="G9" s="59"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="54"/>
-      <c r="B10" s="57"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="53"/>
       <c r="C10" s="52"/>
       <c r="D10" s="34" t="s">
         <v>7</v>
@@ -10638,11 +10655,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G10" s="54"/>
+      <c r="G10" s="59"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="54"/>
-      <c r="B11" s="57"/>
+      <c r="A11" s="59"/>
+      <c r="B11" s="53"/>
       <c r="C11" s="52"/>
       <c r="D11" s="34" t="s">
         <v>8</v>
@@ -10654,11 +10671,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G11" s="54"/>
+      <c r="G11" s="59"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="57"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="53"/>
       <c r="C12" s="52"/>
       <c r="D12" s="34" t="s">
         <v>8</v>
@@ -10670,11 +10687,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G12" s="54"/>
+      <c r="G12" s="59"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="55"/>
-      <c r="B13" s="57"/>
+      <c r="B13" s="53"/>
       <c r="C13" s="52"/>
       <c r="D13" s="34" t="s">
         <v>8</v>
@@ -10689,10 +10706,10 @@
       <c r="G13" s="55"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="53">
+      <c r="A14" s="54">
         <v>2</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="53" t="s">
         <v>207</v>
       </c>
       <c r="C14" s="52" t="s">
@@ -10709,14 +10726,14 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G14" s="53" t="str">
+      <c r="G14" s="54" t="str">
         <f>IF(COUNTA(F14:F20)=COUNTIF(F14:F20,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="54"/>
-      <c r="B15" s="57"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="52"/>
       <c r="D15" s="34" t="s">
         <v>12</v>
@@ -10728,11 +10745,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G15" s="54"/>
+      <c r="G15" s="59"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="54"/>
-      <c r="B16" s="57"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="53"/>
       <c r="C16" s="52"/>
       <c r="D16" s="34" t="s">
         <v>8</v>
@@ -10744,11 +10761,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G16" s="54"/>
+      <c r="G16" s="59"/>
     </row>
     <row r="17" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54"/>
-      <c r="B17" s="57"/>
+      <c r="A17" s="59"/>
+      <c r="B17" s="53"/>
       <c r="C17" s="52"/>
       <c r="D17" s="34" t="s">
         <v>8</v>
@@ -10760,11 +10777,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G17" s="54"/>
+      <c r="G17" s="59"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="54"/>
-      <c r="B18" s="57"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="53"/>
       <c r="C18" s="52"/>
       <c r="D18" s="34" t="s">
         <v>8</v>
@@ -10776,11 +10793,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G18" s="54"/>
+      <c r="G18" s="59"/>
     </row>
     <row r="19" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="54"/>
-      <c r="B19" s="57"/>
+      <c r="A19" s="59"/>
+      <c r="B19" s="53"/>
       <c r="C19" s="52"/>
       <c r="D19" s="34" t="s">
         <v>8</v>
@@ -10792,11 +10809,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G19" s="54"/>
+      <c r="G19" s="59"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="55"/>
-      <c r="B20" s="57"/>
+      <c r="B20" s="53"/>
       <c r="C20" s="52"/>
       <c r="D20" s="34" t="s">
         <v>8</v>
@@ -10811,10 +10828,10 @@
       <c r="G20" s="55"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="53">
+      <c r="A21" s="54">
         <v>3</v>
       </c>
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="53" t="s">
         <v>209</v>
       </c>
       <c r="C21" s="52" t="s">
@@ -10831,14 +10848,14 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G21" s="53" t="str">
+      <c r="G21" s="54" t="str">
         <f>IF(COUNTA(F21:F27)=COUNTIF(F21:F27,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="54"/>
-      <c r="B22" s="57"/>
+      <c r="A22" s="59"/>
+      <c r="B22" s="53"/>
       <c r="C22" s="52"/>
       <c r="D22" s="34" t="s">
         <v>8</v>
@@ -10850,11 +10867,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G22" s="54"/>
+      <c r="G22" s="59"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="54"/>
-      <c r="B23" s="57"/>
+      <c r="A23" s="59"/>
+      <c r="B23" s="53"/>
       <c r="C23" s="52"/>
       <c r="D23" s="34" t="s">
         <v>8</v>
@@ -10866,11 +10883,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G23" s="54"/>
+      <c r="G23" s="59"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="54"/>
-      <c r="B24" s="57"/>
+      <c r="A24" s="59"/>
+      <c r="B24" s="53"/>
       <c r="C24" s="52"/>
       <c r="D24" s="34" t="s">
         <v>8</v>
@@ -10882,11 +10899,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G24" s="54"/>
+      <c r="G24" s="59"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="54"/>
-      <c r="B25" s="57"/>
+      <c r="A25" s="59"/>
+      <c r="B25" s="53"/>
       <c r="C25" s="52"/>
       <c r="D25" s="34" t="s">
         <v>8</v>
@@ -10898,11 +10915,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G25" s="54"/>
+      <c r="G25" s="59"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="54"/>
-      <c r="B26" s="57"/>
+      <c r="A26" s="59"/>
+      <c r="B26" s="53"/>
       <c r="C26" s="52"/>
       <c r="D26" s="34" t="s">
         <v>8</v>
@@ -10914,11 +10931,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G26" s="54"/>
+      <c r="G26" s="59"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="55"/>
-      <c r="B27" s="57"/>
+      <c r="B27" s="53"/>
       <c r="C27" s="52"/>
       <c r="D27" s="34" t="s">
         <v>8</v>
@@ -10933,10 +10950,10 @@
       <c r="G27" s="55"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="53">
+      <c r="A28" s="54">
         <v>4</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="53" t="s">
         <v>211</v>
       </c>
       <c r="C28" s="52" t="s">
@@ -10953,14 +10970,14 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G28" s="53" t="str">
+      <c r="G28" s="54" t="str">
         <f>IF(COUNTA(F28:F34)=COUNTIF(F28:F34,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="54"/>
-      <c r="B29" s="57"/>
+      <c r="A29" s="59"/>
+      <c r="B29" s="53"/>
       <c r="C29" s="52"/>
       <c r="D29" s="34" t="s">
         <v>8</v>
@@ -10972,11 +10989,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G29" s="54"/>
+      <c r="G29" s="59"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="54"/>
-      <c r="B30" s="57"/>
+      <c r="A30" s="59"/>
+      <c r="B30" s="53"/>
       <c r="C30" s="52"/>
       <c r="D30" s="34" t="s">
         <v>8</v>
@@ -10988,11 +11005,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G30" s="54"/>
+      <c r="G30" s="59"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="54"/>
-      <c r="B31" s="57"/>
+      <c r="A31" s="59"/>
+      <c r="B31" s="53"/>
       <c r="C31" s="52"/>
       <c r="D31" s="34" t="s">
         <v>8</v>
@@ -11004,11 +11021,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G31" s="54"/>
+      <c r="G31" s="59"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="54"/>
-      <c r="B32" s="57"/>
+      <c r="A32" s="59"/>
+      <c r="B32" s="53"/>
       <c r="C32" s="52"/>
       <c r="D32" s="34" t="s">
         <v>8</v>
@@ -11020,11 +11037,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G32" s="54"/>
+      <c r="G32" s="59"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="54"/>
-      <c r="B33" s="57"/>
+      <c r="A33" s="59"/>
+      <c r="B33" s="53"/>
       <c r="C33" s="52"/>
       <c r="D33" s="34" t="s">
         <v>8</v>
@@ -11036,11 +11053,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G33" s="54"/>
+      <c r="G33" s="59"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="55"/>
-      <c r="B34" s="57"/>
+      <c r="B34" s="53"/>
       <c r="C34" s="52"/>
       <c r="D34" s="34" t="s">
         <v>8</v>
@@ -11055,10 +11072,10 @@
       <c r="G34" s="55"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="53">
+      <c r="A35" s="54">
         <v>5</v>
       </c>
-      <c r="B35" s="57" t="s">
+      <c r="B35" s="53" t="s">
         <v>213</v>
       </c>
       <c r="C35" s="52" t="s">
@@ -11075,14 +11092,14 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G35" s="53" t="str">
+      <c r="G35" s="54" t="str">
         <f>IF(COUNTA(F35:F41)=COUNTIF(F35:F41,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="54"/>
-      <c r="B36" s="57"/>
+      <c r="A36" s="59"/>
+      <c r="B36" s="53"/>
       <c r="C36" s="52"/>
       <c r="D36" s="34" t="s">
         <v>197</v>
@@ -11094,11 +11111,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G36" s="54"/>
+      <c r="G36" s="59"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="54"/>
-      <c r="B37" s="57"/>
+      <c r="A37" s="59"/>
+      <c r="B37" s="53"/>
       <c r="C37" s="52"/>
       <c r="D37" s="34" t="s">
         <v>216</v>
@@ -11110,11 +11127,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G37" s="54"/>
+      <c r="G37" s="59"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="54"/>
-      <c r="B38" s="57"/>
+      <c r="A38" s="59"/>
+      <c r="B38" s="53"/>
       <c r="C38" s="52"/>
       <c r="D38" s="34" t="s">
         <v>217</v>
@@ -11126,11 +11143,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G38" s="54"/>
+      <c r="G38" s="59"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="54"/>
-      <c r="B39" s="57"/>
+      <c r="A39" s="59"/>
+      <c r="B39" s="53"/>
       <c r="C39" s="52"/>
       <c r="D39" s="34" t="s">
         <v>218</v>
@@ -11142,11 +11159,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G39" s="54"/>
+      <c r="G39" s="59"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="54"/>
-      <c r="B40" s="57"/>
+      <c r="A40" s="59"/>
+      <c r="B40" s="53"/>
       <c r="C40" s="52"/>
       <c r="D40" s="34" t="s">
         <v>219</v>
@@ -11158,11 +11175,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G40" s="54"/>
+      <c r="G40" s="59"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="55"/>
-      <c r="B41" s="57"/>
+      <c r="B41" s="53"/>
       <c r="C41" s="52"/>
       <c r="D41" s="34" t="s">
         <v>220</v>
@@ -11205,10 +11222,10 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="53">
+      <c r="A43" s="54">
         <v>7</v>
       </c>
-      <c r="B43" s="57" t="s">
+      <c r="B43" s="53" t="s">
         <v>227</v>
       </c>
       <c r="C43" s="52" t="s">
@@ -11225,14 +11242,14 @@
         <f t="shared" ref="F43:F49" si="1">IF(E43=D43,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="G43" s="53" t="str">
+      <c r="G43" s="54" t="str">
         <f>IF(COUNTA(F43:F49)=COUNTIF(F43:F49,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="54"/>
-      <c r="B44" s="57"/>
+      <c r="A44" s="59"/>
+      <c r="B44" s="53"/>
       <c r="C44" s="52"/>
       <c r="D44" s="34" t="s">
         <v>223</v>
@@ -11244,11 +11261,11 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="G44" s="54"/>
+      <c r="G44" s="59"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="54"/>
-      <c r="B45" s="57"/>
+      <c r="A45" s="59"/>
+      <c r="B45" s="53"/>
       <c r="C45" s="52"/>
       <c r="D45" s="34" t="s">
         <v>229</v>
@@ -11260,11 +11277,11 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="G45" s="54"/>
+      <c r="G45" s="59"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="54"/>
-      <c r="B46" s="57"/>
+      <c r="A46" s="59"/>
+      <c r="B46" s="53"/>
       <c r="C46" s="52"/>
       <c r="D46" s="34" t="s">
         <v>230</v>
@@ -11276,11 +11293,11 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="G46" s="54"/>
+      <c r="G46" s="59"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="54"/>
-      <c r="B47" s="57"/>
+      <c r="A47" s="59"/>
+      <c r="B47" s="53"/>
       <c r="C47" s="52"/>
       <c r="D47" s="34" t="s">
         <v>231</v>
@@ -11292,11 +11309,11 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="G47" s="54"/>
+      <c r="G47" s="59"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="54"/>
-      <c r="B48" s="57"/>
+      <c r="A48" s="59"/>
+      <c r="B48" s="53"/>
       <c r="C48" s="52"/>
       <c r="D48" s="34" t="s">
         <v>224</v>
@@ -11308,11 +11325,11 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="G48" s="54"/>
+      <c r="G48" s="59"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="55"/>
-      <c r="B49" s="57"/>
+      <c r="B49" s="53"/>
       <c r="C49" s="52"/>
       <c r="D49" s="34" t="s">
         <v>222</v>
@@ -11353,10 +11370,10 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="53">
+      <c r="A51" s="54">
         <v>9</v>
       </c>
-      <c r="B51" s="62" t="s">
+      <c r="B51" s="56" t="s">
         <v>233</v>
       </c>
       <c r="C51" s="71" t="s">
@@ -11373,14 +11390,14 @@
         <f>IF(ISNA(D51),IF(ISNA(E51),"PASS","FAIL"),IFERROR(IF(D51=E51,"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="G51" s="53" t="str">
+      <c r="G51" s="54" t="str">
         <f>IF(COUNTA(F51:F54)=COUNTIF(F51:F54,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="54"/>
-      <c r="B52" s="63"/>
+      <c r="A52" s="59"/>
+      <c r="B52" s="57"/>
       <c r="C52" s="72"/>
       <c r="D52" s="8">
         <v>1</v>
@@ -11392,11 +11409,11 @@
         <f t="shared" ref="F52:F54" si="2">IF(ISNA(D52),IF(ISNA(E52),"PASS","FAIL"),IFERROR(IF(D52=E52,"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="G52" s="54"/>
+      <c r="G52" s="59"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="54"/>
-      <c r="B53" s="63"/>
+      <c r="A53" s="59"/>
+      <c r="B53" s="57"/>
       <c r="C53" s="72"/>
       <c r="D53" s="8" t="e">
         <v>#N/A</v>
@@ -11408,11 +11425,11 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-      <c r="G53" s="54"/>
+      <c r="G53" s="59"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="55"/>
-      <c r="B54" s="64"/>
+      <c r="B54" s="58"/>
       <c r="C54" s="73"/>
       <c r="D54" s="8" t="e">
         <v>#N/A</v>
@@ -11428,18 +11445,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A43:A49"/>
-    <mergeCell ref="C7:C13"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="G7:G13"/>
-    <mergeCell ref="G14:G20"/>
-    <mergeCell ref="G21:G27"/>
-    <mergeCell ref="C14:C20"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="B14:B20"/>
     <mergeCell ref="G43:G49"/>
     <mergeCell ref="G51:G54"/>
     <mergeCell ref="A35:A41"/>
@@ -11456,6 +11461,18 @@
     <mergeCell ref="B51:B54"/>
     <mergeCell ref="C51:C54"/>
     <mergeCell ref="A51:A54"/>
+    <mergeCell ref="G7:G13"/>
+    <mergeCell ref="G14:G20"/>
+    <mergeCell ref="G21:G27"/>
+    <mergeCell ref="C14:C20"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="A43:A49"/>
+    <mergeCell ref="C7:C13"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="B14:B20"/>
   </mergeCells>
   <conditionalFormatting sqref="F7:F50">
     <cfRule type="cellIs" dxfId="43" priority="145" stopIfTrue="1" operator="equal">

--- a/examples/test_cases.xlsx
+++ b/examples/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\src\DuckDBExcelAddin\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D275DFB5-6163-4B34-908B-DCDE1CC44997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE4EC1E-E554-4308-82BE-68C2E83E1354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{16A29E05-5294-4C93-91C1-6C3B8F27AE65}"/>
   </bookViews>
@@ -1166,23 +1166,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1193,20 +1196,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1214,11 +1208,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3547,8 +3547,8 @@
     <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" ref="A1">_xll.DUCKDB.INFO()</f>
-        <v>Add-in version: v1.8.0
-DuckDB version: v1.5.6</v>
+        <v>Add-in version: 1.9.0
+DuckDB version: v2.0.0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3709,7 +3709,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5358680-0ED5-4EFA-AB03-B446D1F523DD}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
@@ -4486,6 +4486,17 @@
       <c r="F35" s="9" t="str">
         <f>IF(ISNA(D35),IF(ISNA(E35),"PASS","FAIL"),IFERROR(IF(D35=LEFT(E35,LEN(D35)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C39" s="2" t="str" cm="1">
+        <f t="array" ref="C39:C40">_xll.DUCKDB.EXEC(C34)</f>
+        <v>NULL</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C40" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -7301,13 +7312,13 @@
       <c r="A2" s="52">
         <v>1</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="54" t="s">
         <v>104</v>
       </c>
       <c r="C2" s="8">
         <v>1</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="63" t="s">
         <v>233</v>
       </c>
       <c r="E2" s="52" t="s">
@@ -7317,16 +7328,16 @@
         <f t="array" ref="F2">INDEX(_xll.DUCKDB.EXEC($D$2,C2:C3),2)</f>
         <v>INTEGER</v>
       </c>
-      <c r="G2" s="54" t="str">
+      <c r="G2" s="55" t="str">
         <f>IF(E2=F2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="52"/>
-      <c r="B3" s="58"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="62"/>
+      <c r="D3" s="63"/>
       <c r="E3" s="52"/>
       <c r="F3" s="52"/>
       <c r="G3" s="56"/>
@@ -7335,11 +7346,11 @@
       <c r="A4" s="52">
         <v>2</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="54" t="s">
         <v>104</v>
       </c>
       <c r="C4" s="8"/>
-      <c r="D4" s="62"/>
+      <c r="D4" s="63"/>
       <c r="E4" s="52" t="s">
         <v>4</v>
       </c>
@@ -7347,67 +7358,67 @@
         <f t="array" ref="F4">INDEX(_xll.DUCKDB.EXEC($D$2,C4:C5),2)</f>
         <v>INTEGER</v>
       </c>
-      <c r="G4" s="54" t="str">
+      <c r="G4" s="55" t="str">
         <f>IF(E4=F4,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="52"/>
-      <c r="B5" s="58"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="26">
         <v>1</v>
       </c>
-      <c r="D5" s="62"/>
+      <c r="D5" s="63"/>
       <c r="E5" s="52"/>
       <c r="F5" s="52"/>
       <c r="G5" s="56"/>
     </row>
     <row r="6" spans="1:7" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="57">
+      <c r="A6" s="65">
         <v>3</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="64" t="s">
         <v>104</v>
       </c>
       <c r="C6" s="26">
         <v>1</v>
       </c>
-      <c r="D6" s="62"/>
-      <c r="E6" s="57" t="s">
+      <c r="D6" s="63"/>
+      <c r="E6" s="65" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="52" t="str" cm="1">
         <f t="array" ref="F6">INDEX(_xll.DUCKDB.EXEC($D$2,C6:C7),2)</f>
         <v>INTEGER</v>
       </c>
-      <c r="G6" s="60" t="str">
+      <c r="G6" s="61" t="str">
         <f>IF(E6=F6,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="57"/>
-      <c r="B7" s="59"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="64"/>
       <c r="C7" s="26">
         <v>2</v>
       </c>
-      <c r="D7" s="62"/>
-      <c r="E7" s="57"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="65"/>
       <c r="F7" s="52"/>
-      <c r="G7" s="61"/>
+      <c r="G7" s="62"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="52">
         <v>4</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="54" t="s">
         <v>107</v>
       </c>
       <c r="C8" s="8">
         <v>1.2</v>
       </c>
-      <c r="D8" s="62"/>
+      <c r="D8" s="63"/>
       <c r="E8" s="52" t="s">
         <v>12</v>
       </c>
@@ -7415,16 +7426,16 @@
         <f t="array" ref="F8">INDEX(_xll.DUCKDB.EXEC($D$2,C8:C9),2)</f>
         <v>DOUBLE</v>
       </c>
-      <c r="G8" s="54" t="str">
+      <c r="G8" s="55" t="str">
         <f>IF(E8=F8,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="52"/>
-      <c r="B9" s="58"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="62"/>
+      <c r="D9" s="63"/>
       <c r="E9" s="52"/>
       <c r="F9" s="52"/>
       <c r="G9" s="56"/>
@@ -7433,11 +7444,11 @@
       <c r="A10" s="52">
         <v>5</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="54" t="s">
         <v>107</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="62"/>
+      <c r="D10" s="63"/>
       <c r="E10" s="52" t="s">
         <v>12</v>
       </c>
@@ -7445,18 +7456,18 @@
         <f t="array" ref="F10">INDEX(_xll.DUCKDB.EXEC($D$2,C10:C11),2)</f>
         <v>DOUBLE</v>
       </c>
-      <c r="G10" s="54" t="str">
+      <c r="G10" s="55" t="str">
         <f>IF(E10=F10,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="52"/>
-      <c r="B11" s="58"/>
+      <c r="B11" s="54"/>
       <c r="C11" s="8">
         <v>1.2</v>
       </c>
-      <c r="D11" s="62"/>
+      <c r="D11" s="63"/>
       <c r="E11" s="52"/>
       <c r="F11" s="52"/>
       <c r="G11" s="56"/>
@@ -7465,13 +7476,13 @@
       <c r="A12" s="52">
         <v>6</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="54" t="s">
         <v>107</v>
       </c>
       <c r="C12" s="8">
         <v>1.2</v>
       </c>
-      <c r="D12" s="62"/>
+      <c r="D12" s="63"/>
       <c r="E12" s="52" t="s">
         <v>12</v>
       </c>
@@ -7479,18 +7490,18 @@
         <f t="array" ref="F12">INDEX(_xll.DUCKDB.EXEC($D$2,C12:C13),2)</f>
         <v>DOUBLE</v>
       </c>
-      <c r="G12" s="54" t="str">
+      <c r="G12" s="55" t="str">
         <f>IF(E12=F12,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="52"/>
-      <c r="B13" s="58"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="8">
         <v>3.4</v>
       </c>
-      <c r="D13" s="62"/>
+      <c r="D13" s="63"/>
       <c r="E13" s="52"/>
       <c r="F13" s="52"/>
       <c r="G13" s="56"/>
@@ -7499,13 +7510,13 @@
       <c r="A14" s="52">
         <v>7</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="54" t="s">
         <v>163</v>
       </c>
       <c r="C14" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="D14" s="62"/>
+      <c r="D14" s="63"/>
       <c r="E14" s="52" t="s">
         <v>7</v>
       </c>
@@ -7513,16 +7524,16 @@
         <f t="array" ref="F14">INDEX(_xll.DUCKDB.EXEC($D$2,C14:C15),2)</f>
         <v>BOOLEAN</v>
       </c>
-      <c r="G14" s="54" t="str">
+      <c r="G14" s="55" t="str">
         <f>IF(E14=F14,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="52"/>
-      <c r="B15" s="58"/>
+      <c r="B15" s="54"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="62"/>
+      <c r="D15" s="63"/>
       <c r="E15" s="52"/>
       <c r="F15" s="52"/>
       <c r="G15" s="56"/>
@@ -7531,13 +7542,13 @@
       <c r="A16" s="52">
         <v>8</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="54" t="s">
         <v>163</v>
       </c>
       <c r="C16" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D16" s="62"/>
+      <c r="D16" s="63"/>
       <c r="E16" s="52" t="s">
         <v>7</v>
       </c>
@@ -7545,16 +7556,16 @@
         <f t="array" ref="F16">INDEX(_xll.DUCKDB.EXEC($D$2,C16:C17),2)</f>
         <v>BOOLEAN</v>
       </c>
-      <c r="G16" s="54" t="str">
+      <c r="G16" s="55" t="str">
         <f>IF(E16=F16,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="52"/>
-      <c r="B17" s="58"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="62"/>
+      <c r="D17" s="63"/>
       <c r="E17" s="52"/>
       <c r="F17" s="52"/>
       <c r="G17" s="56"/>
@@ -7563,13 +7574,13 @@
       <c r="A18" s="52">
         <v>9</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="54" t="s">
         <v>163</v>
       </c>
       <c r="C18" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="D18" s="62"/>
+      <c r="D18" s="63"/>
       <c r="E18" s="52" t="s">
         <v>7</v>
       </c>
@@ -7577,18 +7588,18 @@
         <f t="array" ref="F18">INDEX(_xll.DUCKDB.EXEC($D$2,C18:C19),2)</f>
         <v>BOOLEAN</v>
       </c>
-      <c r="G18" s="54" t="str">
+      <c r="G18" s="55" t="str">
         <f>IF(E18=F18,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="52"/>
-      <c r="B19" s="58"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D19" s="62"/>
+      <c r="D19" s="63"/>
       <c r="E19" s="52"/>
       <c r="F19" s="52"/>
       <c r="G19" s="56"/>
@@ -7597,13 +7608,13 @@
       <c r="A20" s="52">
         <v>10</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="54" t="s">
         <v>163</v>
       </c>
       <c r="C20" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="D20" s="62"/>
+      <c r="D20" s="63"/>
       <c r="E20" s="52" t="s">
         <v>7</v>
       </c>
@@ -7611,18 +7622,18 @@
         <f t="array" ref="F20">INDEX(_xll.DUCKDB.EXEC($D$2,C20:C21),2)</f>
         <v>BOOLEAN</v>
       </c>
-      <c r="G20" s="54" t="str">
+      <c r="G20" s="55" t="str">
         <f>IF(E20=F20,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="52"/>
-      <c r="B21" s="58"/>
+      <c r="B21" s="54"/>
       <c r="C21" s="24">
         <v>1</v>
       </c>
-      <c r="D21" s="62"/>
+      <c r="D21" s="63"/>
       <c r="E21" s="52"/>
       <c r="F21" s="52"/>
       <c r="G21" s="56"/>
@@ -7631,13 +7642,13 @@
       <c r="A22" s="52">
         <v>11</v>
       </c>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="54" t="s">
         <v>163</v>
       </c>
       <c r="C22" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D22" s="62"/>
+      <c r="D22" s="63"/>
       <c r="E22" s="52" t="s">
         <v>7</v>
       </c>
@@ -7645,18 +7656,18 @@
         <f t="array" ref="F22">INDEX(_xll.DUCKDB.EXEC($D$2,C22:C23),2)</f>
         <v>BOOLEAN</v>
       </c>
-      <c r="G22" s="54" t="str">
+      <c r="G22" s="55" t="str">
         <f>IF(E22=F22,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="52"/>
-      <c r="B23" s="58"/>
+      <c r="B23" s="54"/>
       <c r="C23" s="24">
         <v>0</v>
       </c>
-      <c r="D23" s="62"/>
+      <c r="D23" s="63"/>
       <c r="E23" s="52"/>
       <c r="F23" s="52"/>
       <c r="G23" s="56"/>
@@ -7665,13 +7676,13 @@
       <c r="A24" s="52">
         <v>12</v>
       </c>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="54" t="s">
         <v>164</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="62"/>
+      <c r="D24" s="63"/>
       <c r="E24" s="52" t="s">
         <v>8</v>
       </c>
@@ -7679,16 +7690,16 @@
         <f t="array" ref="F24">INDEX(_xll.DUCKDB.EXEC($D$2,C24:C25),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G24" s="54" t="str">
+      <c r="G24" s="55" t="str">
         <f>IF(E24=F24,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="52"/>
-      <c r="B25" s="58"/>
+      <c r="B25" s="54"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="62"/>
+      <c r="D25" s="63"/>
       <c r="E25" s="52"/>
       <c r="F25" s="52"/>
       <c r="G25" s="56"/>
@@ -7697,11 +7708,11 @@
       <c r="A26" s="52">
         <v>13</v>
       </c>
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="54" t="s">
         <v>164</v>
       </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="62"/>
+      <c r="D26" s="63"/>
       <c r="E26" s="52" t="s">
         <v>8</v>
       </c>
@@ -7709,18 +7720,18 @@
         <f t="array" ref="F26">INDEX(_xll.DUCKDB.EXEC($D$2,C26:C27),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G26" s="54" t="str">
+      <c r="G26" s="55" t="str">
         <f>IF(E26=F26,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="52"/>
-      <c r="B27" s="58"/>
+      <c r="B27" s="54"/>
       <c r="C27" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="62"/>
+      <c r="D27" s="63"/>
       <c r="E27" s="52"/>
       <c r="F27" s="52"/>
       <c r="G27" s="56"/>
@@ -7729,13 +7740,13 @@
       <c r="A28" s="52">
         <v>14</v>
       </c>
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="54" t="s">
         <v>164</v>
       </c>
       <c r="C28" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="62"/>
+      <c r="D28" s="63"/>
       <c r="E28" s="52" t="s">
         <v>8</v>
       </c>
@@ -7743,33 +7754,33 @@
         <f t="array" ref="F28">INDEX(_xll.DUCKDB.EXEC($D$2,C28:C29),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G28" s="60" t="str">
+      <c r="G28" s="61" t="str">
         <f>IF(E28=F28,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="52"/>
-      <c r="B29" s="58"/>
+      <c r="B29" s="54"/>
       <c r="C29" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="62"/>
+      <c r="D29" s="63"/>
       <c r="E29" s="52"/>
       <c r="F29" s="52"/>
-      <c r="G29" s="61"/>
+      <c r="G29" s="62"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="52">
         <v>15</v>
       </c>
-      <c r="B30" s="58" t="s">
+      <c r="B30" s="54" t="s">
         <v>168</v>
       </c>
       <c r="C30" s="8">
         <v>1</v>
       </c>
-      <c r="D30" s="62"/>
+      <c r="D30" s="63"/>
       <c r="E30" s="52" t="s">
         <v>12</v>
       </c>
@@ -7777,123 +7788,123 @@
         <f t="array" ref="F30">INDEX(_xll.DUCKDB.EXEC($D$2,C30:C31),2)</f>
         <v>DOUBLE</v>
       </c>
-      <c r="G30" s="54" t="str">
+      <c r="G30" s="55" t="str">
         <f>IF(E30=F30,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="52"/>
-      <c r="B31" s="58"/>
+      <c r="B31" s="54"/>
       <c r="C31" s="10">
         <v>1.2</v>
       </c>
-      <c r="D31" s="62"/>
+      <c r="D31" s="63"/>
       <c r="E31" s="52"/>
       <c r="F31" s="52"/>
       <c r="G31" s="56"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="54">
+      <c r="A32" s="55">
         <v>16</v>
       </c>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="57" t="s">
         <v>170</v>
       </c>
       <c r="C32" s="8">
         <v>1</v>
       </c>
-      <c r="D32" s="62"/>
-      <c r="E32" s="54" t="s">
+      <c r="D32" s="63"/>
+      <c r="E32" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="54" t="str" cm="1">
+      <c r="F32" s="55" t="str" cm="1">
         <f t="array" ref="F32">INDEX(_xll.DUCKDB.EXEC($D$2,C32:C34),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G32" s="54" t="str">
+      <c r="G32" s="55" t="str">
         <f>IF(E32=F32,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="55"/>
-      <c r="B33" s="64"/>
+      <c r="A33" s="60"/>
+      <c r="B33" s="58"/>
       <c r="C33" s="10">
         <v>1.2</v>
       </c>
-      <c r="D33" s="62"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="56"/>
-      <c r="B34" s="65"/>
+      <c r="B34" s="59"/>
       <c r="C34" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="62"/>
+      <c r="D34" s="63"/>
       <c r="E34" s="56"/>
       <c r="F34" s="56"/>
-      <c r="G34" s="55"/>
+      <c r="G34" s="60"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="54">
+      <c r="A35" s="55">
         <v>17</v>
       </c>
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="57" t="s">
         <v>170</v>
       </c>
       <c r="C35" s="8">
         <v>1</v>
       </c>
-      <c r="D35" s="62"/>
-      <c r="E35" s="54" t="s">
+      <c r="D35" s="63"/>
+      <c r="E35" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="54" t="str" cm="1">
+      <c r="F35" s="55" t="str" cm="1">
         <f t="array" ref="F35">INDEX(_xll.DUCKDB.EXEC($D$2,C35:C37),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G35" s="54" t="str">
+      <c r="G35" s="55" t="str">
         <f>IF(E35=F35,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="55"/>
-      <c r="B36" s="64"/>
+      <c r="A36" s="60"/>
+      <c r="B36" s="58"/>
       <c r="C36" s="10">
         <v>1.2</v>
       </c>
-      <c r="D36" s="62"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="56"/>
-      <c r="B37" s="65"/>
+      <c r="B37" s="59"/>
       <c r="C37" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="D37" s="62"/>
+      <c r="D37" s="63"/>
       <c r="E37" s="56"/>
       <c r="F37" s="56"/>
-      <c r="G37" s="55"/>
+      <c r="G37" s="60"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="52">
         <v>18</v>
       </c>
-      <c r="B38" s="58" t="s">
+      <c r="B38" s="54" t="s">
         <v>169</v>
       </c>
       <c r="C38" s="8">
         <v>1</v>
       </c>
-      <c r="D38" s="62"/>
+      <c r="D38" s="63"/>
       <c r="E38" s="52" t="s">
         <v>8</v>
       </c>
@@ -7901,18 +7912,18 @@
         <f t="array" ref="F38">INDEX(_xll.DUCKDB.EXEC($D$2,C38:C39),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G38" s="54" t="str">
+      <c r="G38" s="55" t="str">
         <f>IF(E38=F38,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="52"/>
-      <c r="B39" s="58"/>
+      <c r="B39" s="54"/>
       <c r="C39" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D39" s="62"/>
+      <c r="D39" s="63"/>
       <c r="E39" s="52"/>
       <c r="F39" s="52"/>
       <c r="G39" s="56"/>
@@ -7921,13 +7932,13 @@
       <c r="A40" s="52">
         <v>19</v>
       </c>
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="54" t="s">
         <v>169</v>
       </c>
       <c r="C40" s="8">
         <v>1</v>
       </c>
-      <c r="D40" s="62"/>
+      <c r="D40" s="63"/>
       <c r="E40" s="52" t="s">
         <v>8</v>
       </c>
@@ -7935,18 +7946,18 @@
         <f t="array" ref="F40">INDEX(_xll.DUCKDB.EXEC($D$2,C40:C41),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G40" s="54" t="str">
+      <c r="G40" s="55" t="str">
         <f>IF(E40=F40,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="52"/>
-      <c r="B41" s="58"/>
+      <c r="B41" s="54"/>
       <c r="C41" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D41" s="62"/>
+      <c r="D41" s="63"/>
       <c r="E41" s="52"/>
       <c r="F41" s="52"/>
       <c r="G41" s="56"/>
@@ -7955,13 +7966,13 @@
       <c r="A42" s="52">
         <v>20</v>
       </c>
-      <c r="B42" s="58" t="s">
+      <c r="B42" s="54" t="s">
         <v>171</v>
       </c>
       <c r="C42" s="8">
         <v>1.2</v>
       </c>
-      <c r="D42" s="62"/>
+      <c r="D42" s="63"/>
       <c r="E42" s="52" t="s">
         <v>8</v>
       </c>
@@ -7969,18 +7980,18 @@
         <f t="array" ref="F42">INDEX(_xll.DUCKDB.EXEC($D$2,C42:C43),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G42" s="54" t="str">
+      <c r="G42" s="55" t="str">
         <f>IF(E42=F42,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="52"/>
-      <c r="B43" s="58"/>
+      <c r="B43" s="54"/>
       <c r="C43" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D43" s="62"/>
+      <c r="D43" s="63"/>
       <c r="E43" s="52"/>
       <c r="F43" s="52"/>
       <c r="G43" s="56"/>
@@ -7989,13 +8000,13 @@
       <c r="A44" s="52">
         <v>21</v>
       </c>
-      <c r="B44" s="58" t="s">
+      <c r="B44" s="54" t="s">
         <v>171</v>
       </c>
       <c r="C44" s="8">
         <v>1</v>
       </c>
-      <c r="D44" s="62"/>
+      <c r="D44" s="63"/>
       <c r="E44" s="52" t="s">
         <v>8</v>
       </c>
@@ -8003,56 +8014,74 @@
         <f t="array" ref="F44">INDEX(_xll.DUCKDB.EXEC($D$2,C44:C45),2)</f>
         <v>VARCHAR</v>
       </c>
-      <c r="G44" s="54" t="str">
+      <c r="G44" s="55" t="str">
         <f>IF(E44=F44,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="52"/>
-      <c r="B45" s="58"/>
+      <c r="B45" s="54"/>
       <c r="C45" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D45" s="62"/>
+      <c r="D45" s="63"/>
       <c r="E45" s="52"/>
       <c r="F45" s="52"/>
       <c r="G45" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="106">
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="F24:F25"/>
@@ -8077,56 +8106,38 @@
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
   </mergeCells>
   <conditionalFormatting sqref="G14">
     <cfRule type="cellIs" dxfId="265" priority="601" stopIfTrue="1" operator="equal">
@@ -8342,7 +8353,7 @@
       <c r="A2" s="52">
         <v>1</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C2" s="8">
@@ -8351,170 +8362,170 @@
       <c r="D2" s="53" t="s">
         <v>234</v>
       </c>
-      <c r="E2" s="69">
-        <v>1</v>
-      </c>
-      <c r="F2" s="70" cm="1">
+      <c r="E2" s="67">
+        <v>1</v>
+      </c>
+      <c r="F2" s="69" cm="1">
         <f t="array" ref="F2">INDEX(_xll.DUCKDB.EXEC($D$2,C2:C3),3)</f>
         <v>1</v>
       </c>
-      <c r="G2" s="54" t="str">
+      <c r="G2" s="55" t="str">
         <f>IF(E2=F2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="52"/>
-      <c r="B3" s="58"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="8">
         <v>1</v>
       </c>
       <c r="D3" s="53"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="70"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="69"/>
       <c r="G3" s="56"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="52">
         <v>2</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C4" s="8">
         <v>1</v>
       </c>
       <c r="D4" s="53"/>
-      <c r="E4" s="69">
-        <v>1</v>
-      </c>
-      <c r="F4" s="71" cm="1">
+      <c r="E4" s="67">
+        <v>1</v>
+      </c>
+      <c r="F4" s="68" cm="1">
         <f t="array" ref="F4">INDEX(_xll.DUCKDB.EXEC($D$2,C4:C5),3)</f>
         <v>1</v>
       </c>
-      <c r="G4" s="54" t="str">
+      <c r="G4" s="55" t="str">
         <f>IF(E4=F4,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="52"/>
-      <c r="B5" s="58"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="11" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="53"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="71"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="68"/>
       <c r="G5" s="56"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="52">
         <v>3</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C6" s="8">
         <v>1</v>
       </c>
       <c r="D6" s="53"/>
-      <c r="E6" s="69">
-        <v>1</v>
-      </c>
-      <c r="F6" s="71" cm="1">
+      <c r="E6" s="67">
+        <v>1</v>
+      </c>
+      <c r="F6" s="68" cm="1">
         <f t="array" ref="F6">INDEX(_xll.DUCKDB.EXEC($D$2,C6:C7),3)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="54" t="str">
+      <c r="G6" s="55" t="str">
         <f>IF(E6=F6,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="52"/>
-      <c r="B7" s="58"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D7" s="53"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="71"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="68"/>
       <c r="G7" s="56"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="52">
         <v>4</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C8" s="8">
         <v>1</v>
       </c>
       <c r="D8" s="53"/>
-      <c r="E8" s="69">
+      <c r="E8" s="67">
         <v>10</v>
       </c>
-      <c r="F8" s="71" cm="1">
+      <c r="F8" s="68" cm="1">
         <f t="array" ref="F8">INDEX(_xll.DUCKDB.EXEC($D$2,C8:C9),3)</f>
         <v>10</v>
       </c>
-      <c r="G8" s="54" t="str">
+      <c r="G8" s="55" t="str">
         <f>IF(E8=F8,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="52"/>
-      <c r="B9" s="58"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="11" t="s">
         <v>132</v>
       </c>
       <c r="D9" s="53"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="71"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="68"/>
       <c r="G9" s="56"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="52">
         <v>5</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C10" s="8">
         <v>1</v>
       </c>
       <c r="D10" s="53"/>
-      <c r="E10" s="69">
+      <c r="E10" s="67">
         <v>10</v>
       </c>
-      <c r="F10" s="71" cm="1">
+      <c r="F10" s="68" cm="1">
         <f t="array" ref="F10">INDEX(_xll.DUCKDB.EXEC($D$2,C10:C11),3)</f>
         <v>10</v>
       </c>
-      <c r="G10" s="54" t="str">
+      <c r="G10" s="55" t="str">
         <f>IF(E10=F10,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="52"/>
-      <c r="B11" s="58"/>
+      <c r="B11" s="54"/>
       <c r="C11" s="11" t="s">
         <v>180</v>
       </c>
       <c r="D11" s="53"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="71"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="68"/>
       <c r="G11" s="56"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="52">
         <v>6</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C12" s="8">
@@ -8524,31 +8535,31 @@
       <c r="E12" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F12" s="68" t="str" cm="1">
+      <c r="F12" s="66" t="str" cm="1">
         <f t="array" ref="F12">_xll.DUCKDB.EXEC($D$2,C12:C13)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G12" s="54" t="str">
+      <c r="G12" s="55" t="str">
         <f>IF(ISNA(E12),IF(ISNA(F12),"PASS","FAIL"),IFERROR(IF(E12=LEFT(F12,LEN(E12)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="52"/>
-      <c r="B13" s="58"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="53"/>
       <c r="E13" s="52"/>
-      <c r="F13" s="68"/>
+      <c r="F13" s="66"/>
       <c r="G13" s="56"/>
     </row>
     <row r="14" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="52">
         <v>7</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C14" s="8">
@@ -8558,31 +8569,31 @@
       <c r="E14" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F14" s="68" t="str" cm="1">
+      <c r="F14" s="66" t="str" cm="1">
         <f t="array" ref="F14">_xll.DUCKDB.EXEC($D$2,C14:C15)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G14" s="54" t="str">
+      <c r="G14" s="55" t="str">
         <f>IF(ISNA(E14),IF(ISNA(F14),"PASS","FAIL"),IFERROR(IF(E14=LEFT(F14,LEN(E14)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="52"/>
-      <c r="B15" s="58"/>
+      <c r="B15" s="54"/>
       <c r="C15" s="8">
         <v>1.2</v>
       </c>
       <c r="D15" s="53"/>
       <c r="E15" s="52"/>
-      <c r="F15" s="68"/>
+      <c r="F15" s="66"/>
       <c r="G15" s="56"/>
     </row>
     <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="52">
         <v>8</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C16" s="8">
@@ -8592,31 +8603,31 @@
       <c r="E16" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F16" s="68" t="str" cm="1">
+      <c r="F16" s="66" t="str" cm="1">
         <f t="array" ref="F16">_xll.DUCKDB.EXEC($D$2,C16:C17)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G16" s="54" t="str">
+      <c r="G16" s="55" t="str">
         <f>IF(ISNA(E16),IF(ISNA(F16),"PASS","FAIL"),IFERROR(IF(E16=LEFT(F16,LEN(E16)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="52"/>
-      <c r="B17" s="58"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="11" t="s">
         <v>67</v>
       </c>
       <c r="D17" s="53"/>
       <c r="E17" s="52"/>
-      <c r="F17" s="68"/>
+      <c r="F17" s="66"/>
       <c r="G17" s="56"/>
     </row>
     <row r="18" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52">
         <v>9</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C18" s="8">
@@ -8626,31 +8637,31 @@
       <c r="E18" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F18" s="68" t="str" cm="1">
+      <c r="F18" s="66" t="str" cm="1">
         <f t="array" ref="F18">_xll.DUCKDB.EXEC($D$2,C18:C19)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G18" s="54" t="str">
+      <c r="G18" s="55" t="str">
         <f>IF(ISNA(E18),IF(ISNA(F18),"PASS","FAIL"),IFERROR(IF(E18=LEFT(F18,LEN(E18)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="52"/>
-      <c r="B19" s="58"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="11" t="s">
         <v>177</v>
       </c>
       <c r="D19" s="53"/>
       <c r="E19" s="52"/>
-      <c r="F19" s="68"/>
+      <c r="F19" s="66"/>
       <c r="G19" s="56"/>
     </row>
     <row r="20" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="52">
         <v>10</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C20" s="8">
@@ -8660,31 +8671,31 @@
       <c r="E20" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F20" s="68" t="str" cm="1">
+      <c r="F20" s="66" t="str" cm="1">
         <f t="array" ref="F20">_xll.DUCKDB.EXEC($D$2,C20:C21)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G20" s="54" t="str">
+      <c r="G20" s="55" t="str">
         <f>IF(ISNA(E20),IF(ISNA(F20),"PASS","FAIL"),IFERROR(IF(E20=LEFT(F20,LEN(E20)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="52"/>
-      <c r="B21" s="58"/>
+      <c r="B21" s="54"/>
       <c r="C21" s="11" t="s">
         <v>181</v>
       </c>
       <c r="D21" s="53"/>
       <c r="E21" s="52"/>
-      <c r="F21" s="68"/>
+      <c r="F21" s="66"/>
       <c r="G21" s="56"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="52">
         <v>11</v>
       </c>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C22" s="8">
@@ -8694,31 +8705,31 @@
       <c r="E22" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="68" t="str" cm="1">
+      <c r="F22" s="66" t="str" cm="1">
         <f t="array" ref="F22">_xll.DUCKDB.EXEC($D$2,C22:C23)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G22" s="54" t="str">
+      <c r="G22" s="55" t="str">
         <f>IF(ISNA(E22),IF(ISNA(F22),"PASS","FAIL"),IFERROR(IF(E22=LEFT(F22,LEN(E22)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="52"/>
-      <c r="B23" s="58"/>
+      <c r="B23" s="54"/>
       <c r="C23" s="8" t="b">
         <v>1</v>
       </c>
       <c r="D23" s="53"/>
       <c r="E23" s="52"/>
-      <c r="F23" s="68"/>
+      <c r="F23" s="66"/>
       <c r="G23" s="56"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="52">
         <v>12</v>
       </c>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C24" s="8">
@@ -8728,31 +8739,31 @@
       <c r="E24" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F24" s="68" t="str" cm="1">
+      <c r="F24" s="66" t="str" cm="1">
         <f t="array" ref="F24">_xll.DUCKDB.EXEC($D$2,C24:C25)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G24" s="54" t="str">
+      <c r="G24" s="55" t="str">
         <f>IF(ISNA(E24),IF(ISNA(F24),"PASS","FAIL"),IFERROR(IF(E24=LEFT(F24,LEN(E24)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="52"/>
-      <c r="B25" s="58"/>
+      <c r="B25" s="54"/>
       <c r="C25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="D25" s="53"/>
       <c r="E25" s="52"/>
-      <c r="F25" s="68"/>
+      <c r="F25" s="66"/>
       <c r="G25" s="56"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="52">
         <v>13</v>
       </c>
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C26" s="8">
@@ -8762,31 +8773,31 @@
       <c r="E26" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F26" s="68" t="str" cm="1">
+      <c r="F26" s="66" t="str" cm="1">
         <f t="array" ref="F26">_xll.DUCKDB.EXEC($D$2,C26:C27)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G26" s="54" t="str">
+      <c r="G26" s="55" t="str">
         <f>IF(ISNA(E26),IF(ISNA(F26),"PASS","FAIL"),IFERROR(IF(E26=LEFT(F26,LEN(E26)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="52"/>
-      <c r="B27" s="58"/>
+      <c r="B27" s="54"/>
       <c r="C27" s="11" t="s">
         <v>73</v>
       </c>
       <c r="D27" s="53"/>
       <c r="E27" s="52"/>
-      <c r="F27" s="68"/>
+      <c r="F27" s="66"/>
       <c r="G27" s="56"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="52">
         <v>14</v>
       </c>
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C28" s="8">
@@ -8796,31 +8807,31 @@
       <c r="E28" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F28" s="68" t="str" cm="1">
+      <c r="F28" s="66" t="str" cm="1">
         <f t="array" ref="F28">_xll.DUCKDB.EXEC($D$2,C28:C29)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G28" s="54" t="str">
+      <c r="G28" s="55" t="str">
         <f>IF(ISNA(E28),IF(ISNA(F28),"PASS","FAIL"),IFERROR(IF(E28=LEFT(F28,LEN(E28)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="52"/>
-      <c r="B29" s="58"/>
+      <c r="B29" s="54"/>
       <c r="C29" s="11" t="s">
         <v>76</v>
       </c>
       <c r="D29" s="53"/>
       <c r="E29" s="52"/>
-      <c r="F29" s="68"/>
+      <c r="F29" s="66"/>
       <c r="G29" s="56"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="52">
         <v>15</v>
       </c>
-      <c r="B30" s="58" t="s">
+      <c r="B30" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C30" s="8">
@@ -8830,31 +8841,31 @@
       <c r="E30" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F30" s="68" t="str" cm="1">
+      <c r="F30" s="66" t="str" cm="1">
         <f t="array" ref="F30">_xll.DUCKDB.EXEC($D$2,C30:C31)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G30" s="54" t="str">
+      <c r="G30" s="55" t="str">
         <f>IF(ISNA(E30),IF(ISNA(F30),"PASS","FAIL"),IFERROR(IF(E30=LEFT(F30,LEN(E30)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="52"/>
-      <c r="B31" s="58"/>
+      <c r="B31" s="54"/>
       <c r="C31" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D31" s="53"/>
       <c r="E31" s="52"/>
-      <c r="F31" s="68"/>
+      <c r="F31" s="66"/>
       <c r="G31" s="56"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="52">
         <v>16</v>
       </c>
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C32" s="8">
@@ -8864,31 +8875,31 @@
       <c r="E32" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F32" s="68" t="str" cm="1">
+      <c r="F32" s="66" t="str" cm="1">
         <f t="array" ref="F32">_xll.DUCKDB.EXEC($D$2,C32:C33)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G32" s="54" t="str">
+      <c r="G32" s="55" t="str">
         <f>IF(ISNA(E32),IF(ISNA(F32),"PASS","FAIL"),IFERROR(IF(E32=LEFT(F32,LEN(E32)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="52"/>
-      <c r="B33" s="58"/>
+      <c r="B33" s="54"/>
       <c r="C33" s="11" t="s">
         <v>178</v>
       </c>
       <c r="D33" s="53"/>
       <c r="E33" s="52"/>
-      <c r="F33" s="68"/>
+      <c r="F33" s="66"/>
       <c r="G33" s="56"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="52">
         <v>17</v>
       </c>
-      <c r="B34" s="58" t="s">
+      <c r="B34" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C34" s="8">
@@ -8898,31 +8909,31 @@
       <c r="E34" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F34" s="68" t="str" cm="1">
+      <c r="F34" s="66" t="str" cm="1">
         <f t="array" ref="F34">_xll.DUCKDB.EXEC($D$2,C34:C35)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G34" s="54" t="str">
+      <c r="G34" s="55" t="str">
         <f>IF(ISNA(E34),IF(ISNA(F34),"PASS","FAIL"),IFERROR(IF(E34=LEFT(F34,LEN(E34)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="52"/>
-      <c r="B35" s="58"/>
+      <c r="B35" s="54"/>
       <c r="C35" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D35" s="53"/>
       <c r="E35" s="52"/>
-      <c r="F35" s="68"/>
+      <c r="F35" s="66"/>
       <c r="G35" s="56"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="52">
         <v>18</v>
       </c>
-      <c r="B36" s="58" t="s">
+      <c r="B36" s="54" t="s">
         <v>179</v>
       </c>
       <c r="C36" s="8">
@@ -8932,269 +8943,269 @@
       <c r="E36" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F36" s="68" t="str" cm="1">
+      <c r="F36" s="66" t="str" cm="1">
         <f t="array" ref="F36">_xll.DUCKDB.EXEC($D$2,C36:C37)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to INTEGER.</v>
       </c>
-      <c r="G36" s="54" t="str">
+      <c r="G36" s="55" t="str">
         <f>IF(ISNA(E36),IF(ISNA(F36),"PASS","FAIL"),IFERROR(IF(E36=LEFT(F36,LEN(E36)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="52"/>
-      <c r="B37" s="58"/>
+      <c r="B37" s="54"/>
       <c r="C37" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D37" s="53"/>
       <c r="E37" s="52"/>
-      <c r="F37" s="68"/>
+      <c r="F37" s="66"/>
       <c r="G37" s="56"/>
     </row>
     <row r="38" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="52">
         <v>19</v>
       </c>
-      <c r="B38" s="58" t="s">
+      <c r="B38" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C38" s="8">
         <v>1.2</v>
       </c>
       <c r="D38" s="53"/>
-      <c r="E38" s="69">
+      <c r="E38" s="67">
         <v>3.4</v>
       </c>
-      <c r="F38" s="70" cm="1">
+      <c r="F38" s="69" cm="1">
         <f t="array" ref="F38">INDEX(_xll.DUCKDB.EXEC($D$2,C38:C39),3)</f>
         <v>3.4</v>
       </c>
-      <c r="G38" s="54" t="str">
+      <c r="G38" s="55" t="str">
         <f>IF(E38=F38,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="52"/>
-      <c r="B39" s="58"/>
+      <c r="B39" s="54"/>
       <c r="C39" s="8">
         <v>3.4</v>
       </c>
       <c r="D39" s="53"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="70"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="69"/>
       <c r="G39" s="56"/>
     </row>
     <row r="40" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="52">
         <v>20</v>
       </c>
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C40" s="8">
         <v>1.2</v>
       </c>
       <c r="D40" s="53"/>
-      <c r="E40" s="69">
-        <v>1</v>
-      </c>
-      <c r="F40" s="70" cm="1">
+      <c r="E40" s="67">
+        <v>1</v>
+      </c>
+      <c r="F40" s="69" cm="1">
         <f t="array" ref="F40">INDEX(_xll.DUCKDB.EXEC($D$2,C40:C41),3)</f>
         <v>1</v>
       </c>
-      <c r="G40" s="54" t="str">
+      <c r="G40" s="55" t="str">
         <f>IF(E40=F40,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="52"/>
-      <c r="B41" s="58"/>
+      <c r="B41" s="54"/>
       <c r="C41" s="8">
         <v>1</v>
       </c>
       <c r="D41" s="53"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="70"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="69"/>
       <c r="G41" s="56"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="52">
         <v>21</v>
       </c>
-      <c r="B42" s="58" t="s">
+      <c r="B42" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C42" s="8">
         <v>1.2</v>
       </c>
       <c r="D42" s="53"/>
-      <c r="E42" s="69">
-        <v>1</v>
-      </c>
-      <c r="F42" s="71" cm="1">
+      <c r="E42" s="67">
+        <v>1</v>
+      </c>
+      <c r="F42" s="68" cm="1">
         <f t="array" ref="F42">INDEX(_xll.DUCKDB.EXEC($D$2,C42:C43),3)</f>
         <v>1</v>
       </c>
-      <c r="G42" s="54" t="str">
+      <c r="G42" s="55" t="str">
         <f>IF(E42=F42,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="52"/>
-      <c r="B43" s="58"/>
+      <c r="B43" s="54"/>
       <c r="C43" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D43" s="53"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="71"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="68"/>
       <c r="G43" s="56"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="52">
         <v>22</v>
       </c>
-      <c r="B44" s="58" t="s">
+      <c r="B44" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C44" s="8">
         <v>1.2</v>
       </c>
       <c r="D44" s="53"/>
-      <c r="E44" s="69">
+      <c r="E44" s="67">
         <v>3.4</v>
       </c>
-      <c r="F44" s="71" cm="1">
+      <c r="F44" s="68" cm="1">
         <f t="array" ref="F44">INDEX(_xll.DUCKDB.EXEC($D$2,C44:C45),3)</f>
         <v>3.4</v>
       </c>
-      <c r="G44" s="54" t="str">
+      <c r="G44" s="55" t="str">
         <f>IF(E44=F44,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="52"/>
-      <c r="B45" s="58"/>
+      <c r="B45" s="54"/>
       <c r="C45" s="11" t="s">
         <v>184</v>
       </c>
       <c r="D45" s="53"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="71"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="68"/>
       <c r="G45" s="56"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="52">
         <v>23</v>
       </c>
-      <c r="B46" s="58" t="s">
+      <c r="B46" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C46" s="8">
         <v>1.2</v>
       </c>
       <c r="D46" s="53"/>
-      <c r="E46" s="69">
+      <c r="E46" s="67">
         <v>10</v>
       </c>
-      <c r="F46" s="71" cm="1">
+      <c r="F46" s="68" cm="1">
         <f t="array" ref="F46">INDEX(_xll.DUCKDB.EXEC($D$2,C46:C47),3)</f>
         <v>10</v>
       </c>
-      <c r="G46" s="54" t="str">
+      <c r="G46" s="55" t="str">
         <f>IF(E46=F46,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="52"/>
-      <c r="B47" s="58"/>
+      <c r="B47" s="54"/>
       <c r="C47" s="11" t="s">
         <v>132</v>
       </c>
       <c r="D47" s="53"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="71"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="68"/>
       <c r="G47" s="56"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="52">
         <v>24</v>
       </c>
-      <c r="B48" s="58" t="s">
+      <c r="B48" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C48" s="8">
         <v>1.2</v>
       </c>
       <c r="D48" s="53"/>
-      <c r="E48" s="69">
+      <c r="E48" s="67">
         <v>0.1</v>
       </c>
-      <c r="F48" s="71" cm="1">
+      <c r="F48" s="68" cm="1">
         <f t="array" ref="F48">INDEX(_xll.DUCKDB.EXEC($D$2,C48:C49),3)</f>
         <v>0.1</v>
       </c>
-      <c r="G48" s="54" t="str">
+      <c r="G48" s="55" t="str">
         <f>IF(E48=F48,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="52"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="54"/>
       <c r="C49" s="11" t="s">
         <v>185</v>
       </c>
       <c r="D49" s="53"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="71"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="68"/>
       <c r="G49" s="56"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="52">
         <v>25</v>
       </c>
-      <c r="B50" s="58" t="s">
+      <c r="B50" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C50" s="8">
         <v>1.2</v>
       </c>
       <c r="D50" s="53"/>
-      <c r="E50" s="69">
+      <c r="E50" s="67">
         <v>0.1</v>
       </c>
-      <c r="F50" s="71" cm="1">
+      <c r="F50" s="68" cm="1">
         <f t="array" ref="F50">INDEX(_xll.DUCKDB.EXEC($D$2,C50:C51),3)</f>
         <v>0.1</v>
       </c>
-      <c r="G50" s="54" t="str">
+      <c r="G50" s="55" t="str">
         <f>IF(E50=F50,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="52"/>
-      <c r="B51" s="58"/>
+      <c r="B51" s="54"/>
       <c r="C51" s="11" t="s">
         <v>186</v>
       </c>
       <c r="D51" s="53"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="71"/>
+      <c r="E51" s="67"/>
+      <c r="F51" s="68"/>
       <c r="G51" s="56"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="52">
         <v>26</v>
       </c>
-      <c r="B52" s="58" t="s">
+      <c r="B52" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C52" s="8">
@@ -9204,31 +9215,31 @@
       <c r="E52" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F52" s="68" t="str" cm="1">
+      <c r="F52" s="66" t="str" cm="1">
         <f t="array" ref="F52">_xll.DUCKDB.EXEC($D$2,C52:C53)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G52" s="54" t="str">
+      <c r="G52" s="55" t="str">
         <f>IF(ISNA(E52),IF(ISNA(F52),"PASS","FAIL"),IFERROR(IF(E52=LEFT(F52,LEN(E52)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="52"/>
-      <c r="B53" s="58"/>
+      <c r="B53" s="54"/>
       <c r="C53" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D53" s="53"/>
       <c r="E53" s="52"/>
-      <c r="F53" s="68"/>
+      <c r="F53" s="66"/>
       <c r="G53" s="56"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="52">
         <v>27</v>
       </c>
-      <c r="B54" s="58" t="s">
+      <c r="B54" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C54" s="8">
@@ -9238,31 +9249,31 @@
       <c r="E54" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F54" s="68" t="str" cm="1">
+      <c r="F54" s="66" t="str" cm="1">
         <f t="array" ref="F54">_xll.DUCKDB.EXEC($D$2,C54:C55)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G54" s="54" t="str">
+      <c r="G54" s="55" t="str">
         <f>IF(ISNA(E54),IF(ISNA(F54),"PASS","FAIL"),IFERROR(IF(E54=LEFT(F54,LEN(E54)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="52"/>
-      <c r="B55" s="58"/>
+      <c r="B55" s="54"/>
       <c r="C55" s="8" t="b">
         <v>1</v>
       </c>
       <c r="D55" s="53"/>
       <c r="E55" s="52"/>
-      <c r="F55" s="68"/>
+      <c r="F55" s="66"/>
       <c r="G55" s="56"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="52">
         <v>28</v>
       </c>
-      <c r="B56" s="58" t="s">
+      <c r="B56" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C56" s="8">
@@ -9272,31 +9283,31 @@
       <c r="E56" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F56" s="68" t="str" cm="1">
+      <c r="F56" s="66" t="str" cm="1">
         <f t="array" ref="F56">_xll.DUCKDB.EXEC($D$2,C56:C57)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G56" s="54" t="str">
+      <c r="G56" s="55" t="str">
         <f>IF(ISNA(E56),IF(ISNA(F56),"PASS","FAIL"),IFERROR(IF(E56=LEFT(F56,LEN(E56)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="52"/>
-      <c r="B57" s="58"/>
+      <c r="B57" s="54"/>
       <c r="C57" s="11" t="s">
         <v>70</v>
       </c>
       <c r="D57" s="53"/>
       <c r="E57" s="52"/>
-      <c r="F57" s="68"/>
+      <c r="F57" s="66"/>
       <c r="G57" s="56"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="52">
         <v>29</v>
       </c>
-      <c r="B58" s="58" t="s">
+      <c r="B58" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C58" s="8">
@@ -9306,31 +9317,31 @@
       <c r="E58" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F58" s="68" t="str" cm="1">
+      <c r="F58" s="66" t="str" cm="1">
         <f t="array" ref="F58">_xll.DUCKDB.EXEC($D$2,C58:C59)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G58" s="54" t="str">
+      <c r="G58" s="55" t="str">
         <f>IF(ISNA(E58),IF(ISNA(F58),"PASS","FAIL"),IFERROR(IF(E58=LEFT(F58,LEN(E58)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="52"/>
-      <c r="B59" s="58"/>
+      <c r="B59" s="54"/>
       <c r="C59" s="11" t="s">
         <v>73</v>
       </c>
       <c r="D59" s="53"/>
       <c r="E59" s="52"/>
-      <c r="F59" s="68"/>
+      <c r="F59" s="66"/>
       <c r="G59" s="56"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="52">
         <v>30</v>
       </c>
-      <c r="B60" s="58" t="s">
+      <c r="B60" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C60" s="8">
@@ -9340,31 +9351,31 @@
       <c r="E60" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F60" s="68" t="str" cm="1">
+      <c r="F60" s="66" t="str" cm="1">
         <f t="array" ref="F60">_xll.DUCKDB.EXEC($D$2,C60:C61)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G60" s="54" t="str">
+      <c r="G60" s="55" t="str">
         <f>IF(ISNA(E60),IF(ISNA(F60),"PASS","FAIL"),IFERROR(IF(E60=LEFT(F60,LEN(E60)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="52"/>
-      <c r="B61" s="58"/>
+      <c r="B61" s="54"/>
       <c r="C61" s="11" t="s">
         <v>76</v>
       </c>
       <c r="D61" s="53"/>
       <c r="E61" s="52"/>
-      <c r="F61" s="68"/>
+      <c r="F61" s="66"/>
       <c r="G61" s="56"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="52">
         <v>31</v>
       </c>
-      <c r="B62" s="58" t="s">
+      <c r="B62" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C62" s="8">
@@ -9374,31 +9385,31 @@
       <c r="E62" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F62" s="68" t="str" cm="1">
+      <c r="F62" s="66" t="str" cm="1">
         <f t="array" ref="F62">_xll.DUCKDB.EXEC($D$2,C62:C63)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G62" s="54" t="str">
+      <c r="G62" s="55" t="str">
         <f>IF(ISNA(E62),IF(ISNA(F62),"PASS","FAIL"),IFERROR(IF(E62=LEFT(F62,LEN(E62)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="52"/>
-      <c r="B63" s="58"/>
+      <c r="B63" s="54"/>
       <c r="C63" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D63" s="53"/>
       <c r="E63" s="52"/>
-      <c r="F63" s="68"/>
+      <c r="F63" s="66"/>
       <c r="G63" s="56"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="52">
         <v>32</v>
       </c>
-      <c r="B64" s="58" t="s">
+      <c r="B64" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C64" s="8">
@@ -9408,31 +9419,31 @@
       <c r="E64" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F64" s="68" t="str" cm="1">
+      <c r="F64" s="66" t="str" cm="1">
         <f t="array" ref="F64">_xll.DUCKDB.EXEC($D$2,C64:C65)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G64" s="54" t="str">
+      <c r="G64" s="55" t="str">
         <f>IF(ISNA(E64),IF(ISNA(F64),"PASS","FAIL"),IFERROR(IF(E64=LEFT(F64,LEN(E64)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="52"/>
-      <c r="B65" s="58"/>
+      <c r="B65" s="54"/>
       <c r="C65" s="11" t="s">
         <v>178</v>
       </c>
       <c r="D65" s="53"/>
       <c r="E65" s="52"/>
-      <c r="F65" s="68"/>
+      <c r="F65" s="66"/>
       <c r="G65" s="56"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="52">
         <v>33</v>
       </c>
-      <c r="B66" s="58" t="s">
+      <c r="B66" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C66" s="8">
@@ -9442,31 +9453,31 @@
       <c r="E66" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F66" s="68" t="str" cm="1">
+      <c r="F66" s="66" t="str" cm="1">
         <f t="array" ref="F66">_xll.DUCKDB.EXEC($D$2,C66:C67)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G66" s="54" t="str">
+      <c r="G66" s="55" t="str">
         <f>IF(ISNA(E66),IF(ISNA(F66),"PASS","FAIL"),IFERROR(IF(E66=LEFT(F66,LEN(E66)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="52"/>
-      <c r="B67" s="58"/>
+      <c r="B67" s="54"/>
       <c r="C67" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D67" s="53"/>
       <c r="E67" s="52"/>
-      <c r="F67" s="68"/>
+      <c r="F67" s="66"/>
       <c r="G67" s="56"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="52">
         <v>34</v>
       </c>
-      <c r="B68" s="58" t="s">
+      <c r="B68" s="54" t="s">
         <v>183</v>
       </c>
       <c r="C68" s="8">
@@ -9476,31 +9487,31 @@
       <c r="E68" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F68" s="68" t="str" cm="1">
+      <c r="F68" s="66" t="str" cm="1">
         <f t="array" ref="F68">_xll.DUCKDB.EXEC($D$2,C68:C69)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to DOUBLE.</v>
       </c>
-      <c r="G68" s="54" t="str">
+      <c r="G68" s="55" t="str">
         <f>IF(ISNA(E68),IF(ISNA(F68),"PASS","FAIL"),IFERROR(IF(E68=LEFT(F68,LEN(E68)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="52"/>
-      <c r="B69" s="58"/>
+      <c r="B69" s="54"/>
       <c r="C69" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D69" s="53"/>
       <c r="E69" s="52"/>
-      <c r="F69" s="68"/>
+      <c r="F69" s="66"/>
       <c r="G69" s="56"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="52">
         <v>35</v>
       </c>
-      <c r="B70" s="58" t="s">
+      <c r="B70" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C70" s="8" t="b">
@@ -9510,31 +9521,31 @@
       <c r="E70" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="F70" s="67" t="b" cm="1">
+      <c r="F70" s="70" t="b" cm="1">
         <f t="array" ref="F70">INDEX(_xll.DUCKDB.EXEC($D$2,C70:C71),3)</f>
         <v>0</v>
       </c>
-      <c r="G70" s="54" t="str">
+      <c r="G70" s="55" t="str">
         <f>IF(E70=F70,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="52"/>
-      <c r="B71" s="58"/>
+      <c r="B71" s="54"/>
       <c r="C71" s="26" t="b">
         <v>0</v>
       </c>
       <c r="D71" s="53"/>
       <c r="E71" s="52"/>
-      <c r="F71" s="67"/>
+      <c r="F71" s="70"/>
       <c r="G71" s="56"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="52">
         <v>36</v>
       </c>
-      <c r="B72" s="58" t="s">
+      <c r="B72" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C72" s="8" t="b">
@@ -9544,31 +9555,31 @@
       <c r="E72" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="F72" s="67" t="b" cm="1">
+      <c r="F72" s="70" t="b" cm="1">
         <f t="array" ref="F72">INDEX(_xll.DUCKDB.EXEC($D$2,C72:C73),3)</f>
         <v>0</v>
       </c>
-      <c r="G72" s="54" t="str">
+      <c r="G72" s="55" t="str">
         <f>IF(E72=F72,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="52"/>
-      <c r="B73" s="58"/>
+      <c r="B73" s="54"/>
       <c r="C73" s="30" t="s">
         <v>71</v>
       </c>
       <c r="D73" s="53"/>
       <c r="E73" s="52"/>
-      <c r="F73" s="67"/>
+      <c r="F73" s="70"/>
       <c r="G73" s="56"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="52">
         <v>37</v>
       </c>
-      <c r="B74" s="58" t="s">
+      <c r="B74" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C74" s="8" t="b">
@@ -9578,31 +9589,31 @@
       <c r="E74" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="F74" s="67" t="b" cm="1">
+      <c r="F74" s="70" t="b" cm="1">
         <f t="array" ref="F74">INDEX(_xll.DUCKDB.EXEC($D$2,C74:C75),3)</f>
         <v>0</v>
       </c>
-      <c r="G74" s="54" t="str">
+      <c r="G74" s="55" t="str">
         <f>IF(E74=F74,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="52"/>
-      <c r="B75" s="58"/>
+      <c r="B75" s="54"/>
       <c r="C75" s="30" t="s">
         <v>73</v>
       </c>
       <c r="D75" s="53"/>
       <c r="E75" s="52"/>
-      <c r="F75" s="67"/>
+      <c r="F75" s="70"/>
       <c r="G75" s="56"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="52">
         <v>38</v>
       </c>
-      <c r="B76" s="58" t="s">
+      <c r="B76" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C76" s="8" t="b">
@@ -9612,31 +9623,31 @@
       <c r="E76" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="F76" s="67" t="b" cm="1">
+      <c r="F76" s="70" t="b" cm="1">
         <f t="array" ref="F76">INDEX(_xll.DUCKDB.EXEC($D$2,C76:C77),3)</f>
         <v>0</v>
       </c>
-      <c r="G76" s="54" t="str">
+      <c r="G76" s="55" t="str">
         <f>IF(E76=F76,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="52"/>
-      <c r="B77" s="58"/>
+      <c r="B77" s="54"/>
       <c r="C77" s="30" t="s">
         <v>77</v>
       </c>
       <c r="D77" s="53"/>
       <c r="E77" s="52"/>
-      <c r="F77" s="67"/>
+      <c r="F77" s="70"/>
       <c r="G77" s="56"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="52">
         <v>39</v>
       </c>
-      <c r="B78" s="58" t="s">
+      <c r="B78" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C78" s="8" t="b">
@@ -9646,31 +9657,31 @@
       <c r="E78" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="F78" s="67" t="b" cm="1">
+      <c r="F78" s="70" t="b" cm="1">
         <f t="array" ref="F78">INDEX(_xll.DUCKDB.EXEC($D$2,C78:C79),3)</f>
         <v>0</v>
       </c>
-      <c r="G78" s="54" t="str">
+      <c r="G78" s="55" t="str">
         <f>IF(E78=F78,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="52"/>
-      <c r="B79" s="58"/>
+      <c r="B79" s="54"/>
       <c r="C79" s="30" t="s">
         <v>79</v>
       </c>
       <c r="D79" s="53"/>
       <c r="E79" s="52"/>
-      <c r="F79" s="67"/>
+      <c r="F79" s="70"/>
       <c r="G79" s="56"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="52">
         <v>40</v>
       </c>
-      <c r="B80" s="58" t="s">
+      <c r="B80" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C80" s="8" t="b">
@@ -9680,31 +9691,31 @@
       <c r="E80" s="52" t="b">
         <v>1</v>
       </c>
-      <c r="F80" s="67" t="b" cm="1">
+      <c r="F80" s="70" t="b" cm="1">
         <f t="array" ref="F80">INDEX(_xll.DUCKDB.EXEC($D$2,C80:C81),3)</f>
         <v>1</v>
       </c>
-      <c r="G80" s="54" t="str">
+      <c r="G80" s="55" t="str">
         <f>IF(E80=F80,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="52"/>
-      <c r="B81" s="58"/>
+      <c r="B81" s="54"/>
       <c r="C81" s="30" t="s">
         <v>178</v>
       </c>
       <c r="D81" s="53"/>
       <c r="E81" s="52"/>
-      <c r="F81" s="67"/>
+      <c r="F81" s="70"/>
       <c r="G81" s="56"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="52">
         <v>41</v>
       </c>
-      <c r="B82" s="58" t="s">
+      <c r="B82" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C82" s="8" t="b">
@@ -9714,31 +9725,31 @@
       <c r="E82" s="52" t="b">
         <v>1</v>
       </c>
-      <c r="F82" s="67" t="b" cm="1">
+      <c r="F82" s="70" t="b" cm="1">
         <f t="array" ref="F82">INDEX(_xll.DUCKDB.EXEC($D$2,C82:C83),3)</f>
         <v>1</v>
       </c>
-      <c r="G82" s="54" t="str">
+      <c r="G82" s="55" t="str">
         <f>IF(E82=F82,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="52"/>
-      <c r="B83" s="58"/>
+      <c r="B83" s="54"/>
       <c r="C83" s="30" t="s">
         <v>188</v>
       </c>
       <c r="D83" s="53"/>
       <c r="E83" s="52"/>
-      <c r="F83" s="67"/>
+      <c r="F83" s="70"/>
       <c r="G83" s="56"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="52">
         <v>42</v>
       </c>
-      <c r="B84" s="58" t="s">
+      <c r="B84" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C84" s="8" t="b">
@@ -9748,31 +9759,31 @@
       <c r="E84" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="F84" s="67" t="b" cm="1">
+      <c r="F84" s="70" t="b" cm="1">
         <f t="array" ref="F84">INDEX(_xll.DUCKDB.EXEC($D$2,C84:C85),3)</f>
         <v>0</v>
       </c>
-      <c r="G84" s="54" t="str">
+      <c r="G84" s="55" t="str">
         <f>IF(E84=F84,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="52"/>
-      <c r="B85" s="58"/>
+      <c r="B85" s="54"/>
       <c r="C85" s="31">
         <v>0</v>
       </c>
       <c r="D85" s="53"/>
       <c r="E85" s="52"/>
-      <c r="F85" s="67"/>
+      <c r="F85" s="70"/>
       <c r="G85" s="56"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="52">
         <v>43</v>
       </c>
-      <c r="B86" s="58" t="s">
+      <c r="B86" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C86" s="8" t="b">
@@ -9782,31 +9793,31 @@
       <c r="E86" s="52" t="b">
         <v>1</v>
       </c>
-      <c r="F86" s="67" t="b" cm="1">
+      <c r="F86" s="70" t="b" cm="1">
         <f t="array" ref="F86">INDEX(_xll.DUCKDB.EXEC($D$2,C86:C87),3)</f>
         <v>1</v>
       </c>
-      <c r="G86" s="54" t="str">
+      <c r="G86" s="55" t="str">
         <f>IF(E86=F86,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="52"/>
-      <c r="B87" s="58"/>
+      <c r="B87" s="54"/>
       <c r="C87" s="30" t="s">
         <v>62</v>
       </c>
       <c r="D87" s="53"/>
       <c r="E87" s="52"/>
-      <c r="F87" s="67"/>
+      <c r="F87" s="70"/>
       <c r="G87" s="56"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="52">
         <v>44</v>
       </c>
-      <c r="B88" s="58" t="s">
+      <c r="B88" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C88" s="8" t="b">
@@ -9816,31 +9827,31 @@
       <c r="E88" s="52" t="b">
         <v>1</v>
       </c>
-      <c r="F88" s="67" t="b" cm="1">
+      <c r="F88" s="70" t="b" cm="1">
         <f t="array" ref="F88">INDEX(_xll.DUCKDB.EXEC($D$2,C88:C89),3)</f>
         <v>1</v>
       </c>
-      <c r="G88" s="54" t="str">
+      <c r="G88" s="55" t="str">
         <f>IF(E88=F88,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="52"/>
-      <c r="B89" s="58"/>
+      <c r="B89" s="54"/>
       <c r="C89" s="30" t="s">
         <v>63</v>
       </c>
       <c r="D89" s="53"/>
       <c r="E89" s="52"/>
-      <c r="F89" s="67"/>
+      <c r="F89" s="70"/>
       <c r="G89" s="56"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="52">
         <v>45</v>
       </c>
-      <c r="B90" s="58" t="s">
+      <c r="B90" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C90" s="8" t="b">
@@ -9850,31 +9861,31 @@
       <c r="E90" s="52" t="b">
         <v>1</v>
       </c>
-      <c r="F90" s="67" t="b" cm="1">
+      <c r="F90" s="70" t="b" cm="1">
         <f t="array" ref="F90">INDEX(_xll.DUCKDB.EXEC($D$2,C90:C91),3)</f>
         <v>1</v>
       </c>
-      <c r="G90" s="54" t="str">
+      <c r="G90" s="55" t="str">
         <f>IF(E90=F90,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="52"/>
-      <c r="B91" s="58"/>
+      <c r="B91" s="54"/>
       <c r="C91" s="30" t="s">
         <v>190</v>
       </c>
       <c r="D91" s="53"/>
       <c r="E91" s="52"/>
-      <c r="F91" s="67"/>
+      <c r="F91" s="70"/>
       <c r="G91" s="56"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="52">
         <v>46</v>
       </c>
-      <c r="B92" s="58" t="s">
+      <c r="B92" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C92" s="8" t="b">
@@ -9884,31 +9895,31 @@
       <c r="E92" s="52" t="b">
         <v>1</v>
       </c>
-      <c r="F92" s="67" t="b" cm="1">
+      <c r="F92" s="70" t="b" cm="1">
         <f t="array" ref="F92">INDEX(_xll.DUCKDB.EXEC($D$2,C92:C93),3)</f>
         <v>1</v>
       </c>
-      <c r="G92" s="54" t="str">
+      <c r="G92" s="55" t="str">
         <f>IF(E92=F92,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="52"/>
-      <c r="B93" s="58"/>
+      <c r="B93" s="54"/>
       <c r="C93" s="30" t="s">
         <v>191</v>
       </c>
       <c r="D93" s="53"/>
       <c r="E93" s="52"/>
-      <c r="F93" s="67"/>
+      <c r="F93" s="70"/>
       <c r="G93" s="56"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="52">
         <v>47</v>
       </c>
-      <c r="B94" s="58" t="s">
+      <c r="B94" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C94" s="8" t="b">
@@ -9918,31 +9929,31 @@
       <c r="E94" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F94" s="68" t="str" cm="1">
+      <c r="F94" s="66" t="str" cm="1">
         <f t="array" ref="F94">_xll.DUCKDB.EXEC($D$2,C94:C95)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G94" s="54" t="str">
+      <c r="G94" s="55" t="str">
         <f t="shared" ref="G94" si="0">IF(ISNA(E94),IF(ISNA(F94),"PASS","FAIL"),IFERROR(IF(E94=LEFT(F94,LEN(E94)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="52"/>
-      <c r="B95" s="58"/>
+      <c r="B95" s="54"/>
       <c r="C95" s="31">
         <v>2</v>
       </c>
       <c r="D95" s="53"/>
       <c r="E95" s="52"/>
-      <c r="F95" s="68"/>
+      <c r="F95" s="66"/>
       <c r="G95" s="56"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="52">
         <v>48</v>
       </c>
-      <c r="B96" s="58" t="s">
+      <c r="B96" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C96" s="8" t="b">
@@ -9952,31 +9963,31 @@
       <c r="E96" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F96" s="68" t="str" cm="1">
+      <c r="F96" s="66" t="str" cm="1">
         <f t="array" ref="F96">_xll.DUCKDB.EXEC($D$2,C96:C97)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G96" s="54" t="str">
+      <c r="G96" s="55" t="str">
         <f t="shared" ref="G96" si="1">IF(ISNA(E96),IF(ISNA(F96),"PASS","FAIL"),IFERROR(IF(E96=LEFT(F96,LEN(E96)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="52"/>
-      <c r="B97" s="58"/>
+      <c r="B97" s="54"/>
       <c r="C97" s="30" t="s">
         <v>189</v>
       </c>
       <c r="D97" s="53"/>
       <c r="E97" s="52"/>
-      <c r="F97" s="68"/>
+      <c r="F97" s="66"/>
       <c r="G97" s="56"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="52">
         <v>49</v>
       </c>
-      <c r="B98" s="58" t="s">
+      <c r="B98" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C98" s="8" t="b">
@@ -9986,31 +9997,31 @@
       <c r="E98" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F98" s="68" t="str" cm="1">
+      <c r="F98" s="66" t="str" cm="1">
         <f t="array" ref="F98">_xll.DUCKDB.EXEC($D$2,C98:C99)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G98" s="54" t="str">
+      <c r="G98" s="55" t="str">
         <f t="shared" ref="G98" si="2">IF(ISNA(E98),IF(ISNA(F98),"PASS","FAIL"),IFERROR(IF(E98=LEFT(F98,LEN(E98)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="52"/>
-      <c r="B99" s="58"/>
+      <c r="B99" s="54"/>
       <c r="C99" s="30" t="s">
         <v>192</v>
       </c>
       <c r="D99" s="53"/>
       <c r="E99" s="52"/>
-      <c r="F99" s="68"/>
+      <c r="F99" s="66"/>
       <c r="G99" s="56"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="52">
         <v>50</v>
       </c>
-      <c r="B100" s="58" t="s">
+      <c r="B100" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C100" s="8" t="b">
@@ -10020,31 +10031,31 @@
       <c r="E100" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F100" s="68" t="str" cm="1">
+      <c r="F100" s="66" t="str" cm="1">
         <f t="array" ref="F100">_xll.DUCKDB.EXEC($D$2,C100:C101)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G100" s="54" t="str">
+      <c r="G100" s="55" t="str">
         <f t="shared" ref="G100" si="3">IF(ISNA(E100),IF(ISNA(F100),"PASS","FAIL"),IFERROR(IF(E100=LEFT(F100,LEN(E100)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="52"/>
-      <c r="B101" s="58"/>
+      <c r="B101" s="54"/>
       <c r="C101" s="30" t="s">
         <v>193</v>
       </c>
       <c r="D101" s="53"/>
       <c r="E101" s="52"/>
-      <c r="F101" s="68"/>
+      <c r="F101" s="66"/>
       <c r="G101" s="56"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="52">
         <v>51</v>
       </c>
-      <c r="B102" s="58" t="s">
+      <c r="B102" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C102" s="8" t="b">
@@ -10054,31 +10065,31 @@
       <c r="E102" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F102" s="68" t="str" cm="1">
+      <c r="F102" s="66" t="str" cm="1">
         <f t="array" ref="F102">_xll.DUCKDB.EXEC($D$2,C102:C103)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G102" s="54" t="str">
+      <c r="G102" s="55" t="str">
         <f t="shared" ref="G102" si="4">IF(ISNA(E102),IF(ISNA(F102),"PASS","FAIL"),IFERROR(IF(E102=LEFT(F102,LEN(E102)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="52"/>
-      <c r="B103" s="58"/>
+      <c r="B103" s="54"/>
       <c r="C103" s="30" t="s">
         <v>194</v>
       </c>
       <c r="D103" s="53"/>
       <c r="E103" s="52"/>
-      <c r="F103" s="68"/>
+      <c r="F103" s="66"/>
       <c r="G103" s="56"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="52">
         <v>52</v>
       </c>
-      <c r="B104" s="58" t="s">
+      <c r="B104" s="54" t="s">
         <v>187</v>
       </c>
       <c r="C104" s="8" t="b">
@@ -10088,31 +10099,31 @@
       <c r="E104" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="F104" s="68" t="str" cm="1">
+      <c r="F104" s="66" t="str" cm="1">
         <f t="array" ref="F104">_xll.DUCKDB.EXEC($D$2,C104:C105)</f>
         <v>Invalid Input Error: Error scanning xlrange: Column #1, row 2: Failed to convert value to BOOLEAN.</v>
       </c>
-      <c r="G104" s="54" t="str">
+      <c r="G104" s="55" t="str">
         <f t="shared" ref="G104" si="5">IF(ISNA(E104),IF(ISNA(F104),"PASS","FAIL"),IFERROR(IF(E104=LEFT(F104,LEN(E104)),"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="52"/>
-      <c r="B105" s="58"/>
+      <c r="B105" s="54"/>
       <c r="C105" s="31" t="s">
         <v>45</v>
       </c>
       <c r="D105" s="53"/>
       <c r="E105" s="52"/>
-      <c r="F105" s="68"/>
+      <c r="F105" s="66"/>
       <c r="G105" s="56"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="52">
         <v>53</v>
       </c>
-      <c r="B106" s="58" t="s">
+      <c r="B106" s="54" t="s">
         <v>195</v>
       </c>
       <c r="C106" s="8" t="s">
@@ -10122,162 +10133,355 @@
       <c r="E106" s="52" t="s">
         <v>196</v>
       </c>
-      <c r="F106" s="67" t="str" cm="1">
+      <c r="F106" s="70" t="str" cm="1">
         <f t="array" ref="F106">INDEX(_xll.DUCKDB.EXEC($D$2,C106:C107),3)</f>
         <v>def</v>
       </c>
-      <c r="G106" s="54" t="str">
+      <c r="G106" s="55" t="str">
         <f>IF(E106=F106,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="52"/>
-      <c r="B107" s="58"/>
+      <c r="B107" s="54"/>
       <c r="C107" s="31" t="s">
         <v>196</v>
       </c>
       <c r="D107" s="53"/>
       <c r="E107" s="52"/>
-      <c r="F107" s="67"/>
+      <c r="F107" s="70"/>
       <c r="G107" s="56"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="52">
         <v>54</v>
       </c>
-      <c r="B108" s="58" t="s">
+      <c r="B108" s="54" t="s">
         <v>195</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D108" s="53"/>
-      <c r="E108" s="66" t="s">
+      <c r="E108" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="F108" s="67" t="str" cm="1">
+      <c r="F108" s="70" t="str" cm="1">
         <f t="array" ref="F108">INDEX(_xll.DUCKDB.EXEC($D$2,C108:C109),3)</f>
         <v>1</v>
       </c>
-      <c r="G108" s="54" t="str">
+      <c r="G108" s="55" t="str">
         <f>IF(E108=F108,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="52"/>
-      <c r="B109" s="58"/>
+      <c r="B109" s="54"/>
       <c r="C109" s="31">
         <v>1</v>
       </c>
       <c r="D109" s="53"/>
-      <c r="E109" s="66"/>
-      <c r="F109" s="67"/>
+      <c r="E109" s="71"/>
+      <c r="F109" s="70"/>
       <c r="G109" s="56"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="52">
         <v>55</v>
       </c>
-      <c r="B110" s="58" t="s">
+      <c r="B110" s="54" t="s">
         <v>195</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D110" s="53"/>
-      <c r="E110" s="66" t="s">
+      <c r="E110" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="F110" s="67" t="str" cm="1">
+      <c r="F110" s="70" t="str" cm="1">
         <f t="array" ref="F110">INDEX(_xll.DUCKDB.EXEC($D$2,C110:C111),3)</f>
         <v>1.2</v>
       </c>
-      <c r="G110" s="54" t="str">
+      <c r="G110" s="55" t="str">
         <f>IF(E110=F110,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="52"/>
-      <c r="B111" s="58"/>
+      <c r="B111" s="54"/>
       <c r="C111" s="31">
         <v>1.2</v>
       </c>
       <c r="D111" s="53"/>
-      <c r="E111" s="66"/>
-      <c r="F111" s="67"/>
+      <c r="E111" s="71"/>
+      <c r="F111" s="70"/>
       <c r="G111" s="56"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="52">
         <v>56</v>
       </c>
-      <c r="B112" s="58" t="s">
+      <c r="B112" s="54" t="s">
         <v>195</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D112" s="53"/>
-      <c r="E112" s="66" t="s">
+      <c r="E112" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="F112" s="67" t="str" cm="1">
+      <c r="F112" s="70" t="str" cm="1">
         <f t="array" ref="F112">INDEX(_xll.DUCKDB.EXEC($D$2,C112:C113),3)</f>
         <v>TRUE</v>
       </c>
-      <c r="G112" s="54" t="str">
+      <c r="G112" s="55" t="str">
         <f>IF(E112=F112,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="52"/>
-      <c r="B113" s="58"/>
+      <c r="B113" s="54"/>
       <c r="C113" s="31" t="b">
         <v>1</v>
       </c>
       <c r="D113" s="53"/>
-      <c r="E113" s="66"/>
-      <c r="F113" s="67"/>
+      <c r="E113" s="71"/>
+      <c r="F113" s="70"/>
       <c r="G113" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="281">
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="E112:E113"/>
+    <mergeCell ref="F112:F113"/>
+    <mergeCell ref="G112:G113"/>
+    <mergeCell ref="D2:D113"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="E110:E111"/>
+    <mergeCell ref="F110:F111"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="E108:E109"/>
+    <mergeCell ref="F108:F109"/>
+    <mergeCell ref="G108:G109"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="F106:F107"/>
+    <mergeCell ref="G106:G107"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="F104:F105"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="E102:E103"/>
+    <mergeCell ref="F102:F103"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="E100:E101"/>
+    <mergeCell ref="F100:F101"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="E92:E93"/>
+    <mergeCell ref="F92:F93"/>
+    <mergeCell ref="G92:G93"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="F88:F89"/>
+    <mergeCell ref="G88:G89"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="E98:E99"/>
+    <mergeCell ref="F98:F99"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="F96:F97"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="E94:E95"/>
+    <mergeCell ref="F94:F95"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:F85"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="F82:F83"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="F78:F79"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="F76:F77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="F74:F75"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="E4:E5"/>
@@ -10302,231 +10506,38 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="F68:F69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="F66:F67"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="F64:F65"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="F74:F75"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="F76:F77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="E86:E87"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:F85"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="F88:F89"/>
-    <mergeCell ref="G88:G89"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="E98:E99"/>
-    <mergeCell ref="F98:F99"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="F96:F97"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="E94:E95"/>
-    <mergeCell ref="F94:F95"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="E100:E101"/>
-    <mergeCell ref="F100:F101"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="E92:E93"/>
-    <mergeCell ref="F92:F93"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="E112:E113"/>
-    <mergeCell ref="F112:F113"/>
-    <mergeCell ref="G112:G113"/>
-    <mergeCell ref="D2:D113"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="E110:E111"/>
-    <mergeCell ref="F110:F111"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="E108:E109"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="G108:G109"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="E106:E107"/>
-    <mergeCell ref="F106:F107"/>
-    <mergeCell ref="G106:G107"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="F104:F105"/>
-    <mergeCell ref="G104:G105"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="E102:E103"/>
-    <mergeCell ref="F102:F103"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
   </mergeCells>
   <conditionalFormatting sqref="G14">
     <cfRule type="cellIs" dxfId="223" priority="137" stopIfTrue="1" operator="equal">
@@ -11184,10 +11195,10 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54">
-        <v>1</v>
-      </c>
-      <c r="B12" s="68" t="s">
+      <c r="A12" s="55">
+        <v>1</v>
+      </c>
+      <c r="B12" s="66" t="s">
         <v>254</v>
       </c>
       <c r="C12" s="53" t="s">
@@ -11204,14 +11215,14 @@
         <f t="shared" ref="F12:F46" si="0">IF(E12=D12,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="G12" s="54" t="str">
+      <c r="G12" s="55" t="str">
         <f>IF(COUNTA(F12:F18)=COUNTIF(F12:F18,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="55"/>
-      <c r="B13" s="58"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="53"/>
       <c r="D13" s="33" t="s">
         <v>4</v>
@@ -11223,11 +11234,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G13" s="55"/>
+      <c r="G13" s="60"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="55"/>
-      <c r="B14" s="58"/>
+      <c r="A14" s="60"/>
+      <c r="B14" s="54"/>
       <c r="C14" s="53"/>
       <c r="D14" s="33" t="s">
         <v>12</v>
@@ -11239,11 +11250,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G14" s="55"/>
+      <c r="G14" s="60"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="55"/>
-      <c r="B15" s="58"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="54"/>
       <c r="C15" s="53"/>
       <c r="D15" s="33" t="s">
         <v>7</v>
@@ -11255,11 +11266,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G15" s="55"/>
+      <c r="G15" s="60"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="55"/>
-      <c r="B16" s="58"/>
+      <c r="A16" s="60"/>
+      <c r="B16" s="54"/>
       <c r="C16" s="53"/>
       <c r="D16" s="33" t="s">
         <v>8</v>
@@ -11271,11 +11282,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G16" s="55"/>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="55"/>
-      <c r="B17" s="58"/>
+      <c r="A17" s="60"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="53"/>
       <c r="D17" s="33" t="s">
         <v>8</v>
@@ -11287,11 +11298,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G17" s="55"/>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="56"/>
-      <c r="B18" s="58"/>
+      <c r="B18" s="54"/>
       <c r="C18" s="53"/>
       <c r="D18" s="33" t="s">
         <v>8</v>
@@ -11306,10 +11317,10 @@
       <c r="G18" s="56"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="54">
+      <c r="A19" s="55">
         <v>2</v>
       </c>
-      <c r="B19" s="68" t="s">
+      <c r="B19" s="66" t="s">
         <v>255</v>
       </c>
       <c r="C19" s="53" t="s">
@@ -11326,14 +11337,14 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G19" s="54" t="str">
+      <c r="G19" s="55" t="str">
         <f>IF(COUNTA(F19:F25)=COUNTIF(F19:F25,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="55"/>
-      <c r="B20" s="58"/>
+      <c r="A20" s="60"/>
+      <c r="B20" s="54"/>
       <c r="C20" s="53"/>
       <c r="D20" s="33" t="s">
         <v>12</v>
@@ -11345,11 +11356,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G20" s="55"/>
+      <c r="G20" s="60"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="55"/>
-      <c r="B21" s="58"/>
+      <c r="A21" s="60"/>
+      <c r="B21" s="54"/>
       <c r="C21" s="53"/>
       <c r="D21" s="33" t="s">
         <v>8</v>
@@ -11361,11 +11372,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G21" s="55"/>
+      <c r="G21" s="60"/>
     </row>
     <row r="22" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="55"/>
-      <c r="B22" s="58"/>
+      <c r="A22" s="60"/>
+      <c r="B22" s="54"/>
       <c r="C22" s="53"/>
       <c r="D22" s="33" t="s">
         <v>8</v>
@@ -11377,11 +11388,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G22" s="55"/>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="55"/>
-      <c r="B23" s="58"/>
+      <c r="A23" s="60"/>
+      <c r="B23" s="54"/>
       <c r="C23" s="53"/>
       <c r="D23" s="33" t="s">
         <v>8</v>
@@ -11393,11 +11404,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G23" s="55"/>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="55"/>
-      <c r="B24" s="58"/>
+      <c r="A24" s="60"/>
+      <c r="B24" s="54"/>
       <c r="C24" s="53"/>
       <c r="D24" s="33" t="s">
         <v>8</v>
@@ -11409,11 +11420,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G24" s="55"/>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="56"/>
-      <c r="B25" s="58"/>
+      <c r="B25" s="54"/>
       <c r="C25" s="53"/>
       <c r="D25" s="33" t="s">
         <v>8</v>
@@ -11428,10 +11439,10 @@
       <c r="G25" s="56"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="54">
+      <c r="A26" s="55">
         <v>3</v>
       </c>
-      <c r="B26" s="68" t="s">
+      <c r="B26" s="66" t="s">
         <v>256</v>
       </c>
       <c r="C26" s="53" t="s">
@@ -11448,14 +11459,14 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G26" s="54" t="str">
+      <c r="G26" s="55" t="str">
         <f>IF(COUNTA(F26:F32)=COUNTIF(F26:F32,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="55"/>
-      <c r="B27" s="58"/>
+      <c r="A27" s="60"/>
+      <c r="B27" s="54"/>
       <c r="C27" s="53"/>
       <c r="D27" s="33" t="s">
         <v>8</v>
@@ -11467,11 +11478,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G27" s="55"/>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="55"/>
-      <c r="B28" s="58"/>
+      <c r="A28" s="60"/>
+      <c r="B28" s="54"/>
       <c r="C28" s="53"/>
       <c r="D28" s="33" t="s">
         <v>8</v>
@@ -11483,11 +11494,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G28" s="55"/>
+      <c r="G28" s="60"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="55"/>
-      <c r="B29" s="58"/>
+      <c r="A29" s="60"/>
+      <c r="B29" s="54"/>
       <c r="C29" s="53"/>
       <c r="D29" s="33" t="s">
         <v>8</v>
@@ -11499,11 +11510,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G29" s="55"/>
+      <c r="G29" s="60"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="55"/>
-      <c r="B30" s="58"/>
+      <c r="A30" s="60"/>
+      <c r="B30" s="54"/>
       <c r="C30" s="53"/>
       <c r="D30" s="33" t="s">
         <v>8</v>
@@ -11515,11 +11526,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G30" s="55"/>
+      <c r="G30" s="60"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="55"/>
-      <c r="B31" s="58"/>
+      <c r="A31" s="60"/>
+      <c r="B31" s="54"/>
       <c r="C31" s="53"/>
       <c r="D31" s="33" t="s">
         <v>8</v>
@@ -11531,11 +11542,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G31" s="55"/>
+      <c r="G31" s="60"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="56"/>
-      <c r="B32" s="58"/>
+      <c r="B32" s="54"/>
       <c r="C32" s="53"/>
       <c r="D32" s="33" t="s">
         <v>8</v>
@@ -11550,10 +11561,10 @@
       <c r="G32" s="56"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="54">
+      <c r="A33" s="55">
         <v>4</v>
       </c>
-      <c r="B33" s="68" t="s">
+      <c r="B33" s="66" t="s">
         <v>257</v>
       </c>
       <c r="C33" s="53" t="s">
@@ -11570,14 +11581,14 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G33" s="54" t="str">
+      <c r="G33" s="55" t="str">
         <f>IF(COUNTA(F33:F39)=COUNTIF(F33:F39,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="55"/>
-      <c r="B34" s="58"/>
+      <c r="A34" s="60"/>
+      <c r="B34" s="54"/>
       <c r="C34" s="53"/>
       <c r="D34" s="33" t="s">
         <v>8</v>
@@ -11589,11 +11600,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G34" s="55"/>
+      <c r="G34" s="60"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="55"/>
-      <c r="B35" s="58"/>
+      <c r="A35" s="60"/>
+      <c r="B35" s="54"/>
       <c r="C35" s="53"/>
       <c r="D35" s="33" t="s">
         <v>8</v>
@@ -11605,11 +11616,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G35" s="55"/>
+      <c r="G35" s="60"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="55"/>
-      <c r="B36" s="58"/>
+      <c r="A36" s="60"/>
+      <c r="B36" s="54"/>
       <c r="C36" s="53"/>
       <c r="D36" s="33" t="s">
         <v>8</v>
@@ -11621,11 +11632,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G36" s="55"/>
+      <c r="G36" s="60"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="55"/>
-      <c r="B37" s="58"/>
+      <c r="A37" s="60"/>
+      <c r="B37" s="54"/>
       <c r="C37" s="53"/>
       <c r="D37" s="33" t="s">
         <v>8</v>
@@ -11637,11 +11648,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G37" s="55"/>
+      <c r="G37" s="60"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="55"/>
-      <c r="B38" s="58"/>
+      <c r="A38" s="60"/>
+      <c r="B38" s="54"/>
       <c r="C38" s="53"/>
       <c r="D38" s="33" t="s">
         <v>8</v>
@@ -11653,11 +11664,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G38" s="55"/>
+      <c r="G38" s="60"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
-      <c r="B39" s="58"/>
+      <c r="B39" s="54"/>
       <c r="C39" s="53"/>
       <c r="D39" s="33" t="s">
         <v>8</v>
@@ -11672,10 +11683,10 @@
       <c r="G39" s="56"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="54">
+      <c r="A40" s="55">
         <v>5</v>
       </c>
-      <c r="B40" s="68" t="s">
+      <c r="B40" s="66" t="s">
         <v>258</v>
       </c>
       <c r="C40" s="53" t="s">
@@ -11692,14 +11703,14 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G40" s="54" t="str">
+      <c r="G40" s="55" t="str">
         <f>IF(COUNTA(F40:F46)=COUNTIF(F40:F46,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="55"/>
-      <c r="B41" s="58"/>
+      <c r="A41" s="60"/>
+      <c r="B41" s="54"/>
       <c r="C41" s="53"/>
       <c r="D41" s="33" t="s">
         <v>197</v>
@@ -11711,11 +11722,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G41" s="55"/>
+      <c r="G41" s="60"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="55"/>
-      <c r="B42" s="58"/>
+      <c r="A42" s="60"/>
+      <c r="B42" s="54"/>
       <c r="C42" s="53"/>
       <c r="D42" s="33" t="s">
         <v>211</v>
@@ -11727,11 +11738,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G42" s="55"/>
+      <c r="G42" s="60"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="55"/>
-      <c r="B43" s="58"/>
+      <c r="A43" s="60"/>
+      <c r="B43" s="54"/>
       <c r="C43" s="53"/>
       <c r="D43" s="33" t="s">
         <v>212</v>
@@ -11743,11 +11754,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G43" s="55"/>
+      <c r="G43" s="60"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="55"/>
-      <c r="B44" s="58"/>
+      <c r="A44" s="60"/>
+      <c r="B44" s="54"/>
       <c r="C44" s="53"/>
       <c r="D44" s="33" t="s">
         <v>213</v>
@@ -11759,11 +11770,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G44" s="55"/>
+      <c r="G44" s="60"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="55"/>
-      <c r="B45" s="58"/>
+      <c r="A45" s="60"/>
+      <c r="B45" s="54"/>
       <c r="C45" s="53"/>
       <c r="D45" s="33" t="s">
         <v>214</v>
@@ -11775,11 +11786,11 @@
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
-      <c r="G45" s="55"/>
+      <c r="G45" s="60"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="56"/>
-      <c r="B46" s="58"/>
+      <c r="B46" s="54"/>
       <c r="C46" s="53"/>
       <c r="D46" s="33" t="s">
         <v>215</v>
@@ -11810,7 +11821,7 @@
         <f t="array" ref="E47">_xll.DUCKDB.EXEC(C47,$J$1:$O$4)</f>
         <v>Binder Error: Error binding xlrange: Column 3: Invalid column name. Column names must be non-empty and valid DuckDB identifiers.
 LINE 1: select column_name from (describe (from xlrange(1, sample=1)))
-                                                ^</v>
+                                                ^^^^^^^^^^^^^^^^^^^^</v>
       </c>
       <c r="F47" s="13" t="str">
         <f>IF(ISNA(D47),IF(ISNA(E47),"PASS","FAIL"),IFERROR(IF(D47=LEFT(E47,LEN(D47)),"PASS","FAIL"),"FAIL"))</f>
@@ -11822,10 +11833,10 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="54">
+      <c r="A48" s="55">
         <v>7</v>
       </c>
-      <c r="B48" s="68" t="s">
+      <c r="B48" s="66" t="s">
         <v>260</v>
       </c>
       <c r="C48" s="53" t="s">
@@ -11842,14 +11853,14 @@
         <f t="shared" ref="F48:F54" si="1">IF(E48=D48,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="G48" s="54" t="str">
+      <c r="G48" s="55" t="str">
         <f>IF(COUNTA(F48:F54)=COUNTIF(F48:F54,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="55"/>
-      <c r="B49" s="58"/>
+      <c r="A49" s="60"/>
+      <c r="B49" s="54"/>
       <c r="C49" s="53"/>
       <c r="D49" s="33" t="s">
         <v>218</v>
@@ -11861,11 +11872,11 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="G49" s="55"/>
+      <c r="G49" s="60"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="55"/>
-      <c r="B50" s="58"/>
+      <c r="A50" s="60"/>
+      <c r="B50" s="54"/>
       <c r="C50" s="53"/>
       <c r="D50" s="33" t="s">
         <v>222</v>
@@ -11877,11 +11888,11 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="G50" s="55"/>
+      <c r="G50" s="60"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="55"/>
-      <c r="B51" s="58"/>
+      <c r="A51" s="60"/>
+      <c r="B51" s="54"/>
       <c r="C51" s="53"/>
       <c r="D51" s="33" t="s">
         <v>223</v>
@@ -11893,11 +11904,11 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="G51" s="55"/>
+      <c r="G51" s="60"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="55"/>
-      <c r="B52" s="58"/>
+      <c r="A52" s="60"/>
+      <c r="B52" s="54"/>
       <c r="C52" s="53"/>
       <c r="D52" s="33" t="s">
         <v>224</v>
@@ -11909,11 +11920,11 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="G52" s="55"/>
+      <c r="G52" s="60"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="55"/>
-      <c r="B53" s="58"/>
+      <c r="A53" s="60"/>
+      <c r="B53" s="54"/>
       <c r="C53" s="53"/>
       <c r="D53" s="33" t="s">
         <v>219</v>
@@ -11925,11 +11936,11 @@
         <f t="shared" si="1"/>
         <v>PASS</v>
       </c>
-      <c r="G53" s="55"/>
+      <c r="G53" s="60"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="56"/>
-      <c r="B54" s="58"/>
+      <c r="B54" s="54"/>
       <c r="C54" s="53"/>
       <c r="D54" s="33" t="s">
         <v>217</v>
@@ -11970,7 +11981,7 @@
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="54">
+      <c r="A56" s="55">
         <v>9</v>
       </c>
       <c r="B56" s="72" t="s">
@@ -11990,14 +12001,14 @@
         <f>IF(ISNA(D56),IF(ISNA(E56),"PASS","FAIL"),IFERROR(IF(D56=E56,"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="G56" s="54" t="str">
+      <c r="G56" s="55" t="str">
         <f>IF(COUNTA(F56:F59)=COUNTIF(F56:F59,"PASS"),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="55"/>
-      <c r="B57" s="64"/>
+      <c r="A57" s="60"/>
+      <c r="B57" s="58"/>
       <c r="C57" s="73"/>
       <c r="D57" s="8">
         <v>1</v>
@@ -12009,11 +12020,11 @@
         <f t="shared" ref="F57:F71" si="2">IF(ISNA(D57),IF(ISNA(E57),"PASS","FAIL"),IFERROR(IF(D57=E57,"PASS","FAIL"),"FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="G57" s="55"/>
+      <c r="G57" s="60"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="55"/>
-      <c r="B58" s="64"/>
+      <c r="A58" s="60"/>
+      <c r="B58" s="58"/>
       <c r="C58" s="73"/>
       <c r="D58" s="8" t="e">
         <v>#N/A</v>
@@ -12025,11 +12036,11 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-      <c r="G58" s="55"/>
+      <c r="G58" s="60"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="56"/>
-      <c r="B59" s="65"/>
+      <c r="B59" s="59"/>
       <c r="C59" s="74"/>
       <c r="D59" s="8" t="e">
         <v>#N/A</v>
@@ -12047,7 +12058,7 @@
       <c r="A60" s="52">
         <v>10</v>
       </c>
-      <c r="B60" s="68" t="s">
+      <c r="B60" s="66" t="s">
         <v>269</v>
       </c>
       <c r="C60" s="72" t="s">
@@ -12071,7 +12082,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="52"/>
-      <c r="B61" s="68"/>
+      <c r="B61" s="66"/>
       <c r="C61" s="73"/>
       <c r="D61" s="8">
         <v>1</v>
@@ -12087,7 +12098,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="52"/>
-      <c r="B62" s="68"/>
+      <c r="B62" s="66"/>
       <c r="C62" s="74"/>
       <c r="D62" s="8">
         <v>1</v>
@@ -12105,7 +12116,7 @@
       <c r="A63" s="52">
         <v>11</v>
       </c>
-      <c r="B63" s="68" t="s">
+      <c r="B63" s="66" t="s">
         <v>270</v>
       </c>
       <c r="C63" s="72" t="s">
@@ -12129,7 +12140,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="52"/>
-      <c r="B64" s="68"/>
+      <c r="B64" s="66"/>
       <c r="C64" s="73"/>
       <c r="D64" s="8">
         <v>1.2</v>
@@ -12145,7 +12156,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="52"/>
-      <c r="B65" s="68"/>
+      <c r="B65" s="66"/>
       <c r="C65" s="74"/>
       <c r="D65" s="8">
         <v>3.4</v>
@@ -12163,7 +12174,7 @@
       <c r="A66" s="52">
         <v>12</v>
       </c>
-      <c r="B66" s="68" t="s">
+      <c r="B66" s="66" t="s">
         <v>271</v>
       </c>
       <c r="C66" s="72" t="s">
@@ -12187,7 +12198,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="52"/>
-      <c r="B67" s="68"/>
+      <c r="B67" s="66"/>
       <c r="C67" s="73"/>
       <c r="D67" s="8" t="b">
         <v>1</v>
@@ -12203,7 +12214,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="52"/>
-      <c r="B68" s="68"/>
+      <c r="B68" s="66"/>
       <c r="C68" s="74"/>
       <c r="D68" s="8" t="b">
         <v>1</v>
@@ -12221,7 +12232,7 @@
       <c r="A69" s="52">
         <v>13</v>
       </c>
-      <c r="B69" s="68" t="s">
+      <c r="B69" s="66" t="s">
         <v>272</v>
       </c>
       <c r="C69" s="72" t="s">
@@ -12245,7 +12256,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="52"/>
-      <c r="B70" s="68"/>
+      <c r="B70" s="66"/>
       <c r="C70" s="73"/>
       <c r="D70" s="8" t="s">
         <v>263</v>
@@ -12261,7 +12272,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="52"/>
-      <c r="B71" s="68"/>
+      <c r="B71" s="66"/>
       <c r="C71" s="74"/>
       <c r="D71" s="8" t="s">
         <v>62</v>
@@ -12277,34 +12288,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="C66:C68"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="B63:B65"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="G60:G62"/>
-    <mergeCell ref="G63:G65"/>
-    <mergeCell ref="G66:G68"/>
-    <mergeCell ref="G69:G71"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="C12:C18"/>
-    <mergeCell ref="B12:B18"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="B26:B32"/>
-    <mergeCell ref="B19:B25"/>
-    <mergeCell ref="G12:G18"/>
-    <mergeCell ref="G19:G25"/>
-    <mergeCell ref="G26:G32"/>
-    <mergeCell ref="C19:C25"/>
-    <mergeCell ref="C26:C32"/>
     <mergeCell ref="G48:G54"/>
     <mergeCell ref="G56:G59"/>
     <mergeCell ref="A40:A46"/>
@@ -12321,6 +12304,34 @@
     <mergeCell ref="B56:B59"/>
     <mergeCell ref="C56:C59"/>
     <mergeCell ref="A56:A59"/>
+    <mergeCell ref="G12:G18"/>
+    <mergeCell ref="G19:G25"/>
+    <mergeCell ref="G26:G32"/>
+    <mergeCell ref="C19:C25"/>
+    <mergeCell ref="C26:C32"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="C12:C18"/>
+    <mergeCell ref="B12:B18"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="B26:B32"/>
+    <mergeCell ref="B19:B25"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="G66:G68"/>
+    <mergeCell ref="G69:G71"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="C69:C71"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="B66:B68"/>
+    <mergeCell ref="B69:B71"/>
   </mergeCells>
   <conditionalFormatting sqref="F12:F55">
     <cfRule type="cellIs" dxfId="115" priority="217" stopIfTrue="1" operator="equal">
@@ -12483,290 +12494,290 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60">
-    <cfRule type="cellIs" dxfId="71" priority="69" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="70" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="69" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="70" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60">
-    <cfRule type="cellIs" dxfId="69" priority="71" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="72" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="71" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="72" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F61">
-    <cfRule type="cellIs" dxfId="67" priority="65" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="66" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="65" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="66" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F61">
-    <cfRule type="cellIs" dxfId="65" priority="67" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="68" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="67" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="68" priority="68" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62">
-    <cfRule type="cellIs" dxfId="63" priority="61" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="62" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="61" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="62" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62">
-    <cfRule type="cellIs" dxfId="61" priority="63" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="64" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="63" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="64" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="cellIs" dxfId="59" priority="57" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="58" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="57" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="58" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="cellIs" dxfId="57" priority="59" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="60" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="59" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="60" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64">
-    <cfRule type="cellIs" dxfId="55" priority="53" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="54" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="53" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="54" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64">
-    <cfRule type="cellIs" dxfId="53" priority="55" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="56" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="55" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="56" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F65">
-    <cfRule type="cellIs" dxfId="51" priority="49" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="50" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="49" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="50" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F65">
-    <cfRule type="cellIs" dxfId="49" priority="51" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="52" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="51" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="52" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F66">
-    <cfRule type="cellIs" dxfId="47" priority="45" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="46" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="45" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="50" priority="46" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F66">
-    <cfRule type="cellIs" dxfId="45" priority="47" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="48" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="47" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="48" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67">
-    <cfRule type="cellIs" dxfId="43" priority="41" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="42" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="41" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="42" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67">
-    <cfRule type="cellIs" dxfId="41" priority="43" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="44" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="43" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="44" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68">
-    <cfRule type="cellIs" dxfId="39" priority="37" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="38" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="37" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="38" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68">
-    <cfRule type="cellIs" dxfId="37" priority="39" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="40" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="39" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="40" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F69">
-    <cfRule type="cellIs" dxfId="35" priority="33" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="34" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="33" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="34" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F69">
-    <cfRule type="cellIs" dxfId="33" priority="35" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="36" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="35" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="36" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70">
-    <cfRule type="cellIs" dxfId="31" priority="29" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="30" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="29" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="30" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70">
-    <cfRule type="cellIs" dxfId="29" priority="31" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="32" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="31" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="32" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F71">
-    <cfRule type="cellIs" dxfId="27" priority="25" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="26" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="25" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="26" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F71">
-    <cfRule type="cellIs" dxfId="25" priority="27" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="28" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="27" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="28" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G60">
-    <cfRule type="cellIs" dxfId="23" priority="23" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="24" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="23" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="24" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G60">
-    <cfRule type="cellIs" dxfId="21" priority="21" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="22" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="21" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="22" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G60">
-    <cfRule type="cellIs" dxfId="19" priority="19" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="20" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="19" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="20" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G63">
-    <cfRule type="cellIs" dxfId="17" priority="17" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="18" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="17" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="18" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G63">
-    <cfRule type="cellIs" dxfId="15" priority="15" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="16" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="15" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="16" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G63">
-    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="14" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="13" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="14" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G66">
-    <cfRule type="cellIs" dxfId="11" priority="11" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="12" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G66">
-    <cfRule type="cellIs" dxfId="9" priority="9" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="9" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="10" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G66">
-    <cfRule type="cellIs" dxfId="7" priority="7" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="7" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="8" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G69">
-    <cfRule type="cellIs" dxfId="5" priority="5" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="5" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="6" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G69">
-    <cfRule type="cellIs" dxfId="3" priority="3" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="4" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G69">
-    <cfRule type="cellIs" dxfId="1" priority="1" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12889,10 +12900,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G4">
-    <cfRule type="cellIs" dxfId="75" priority="1" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13108,10 +13119,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G8">
-    <cfRule type="cellIs" dxfId="73" priority="1" stopIfTrue="1" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" stopIfTrue="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
